--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="ItemsInfo" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>ui_crystal_1</t>
+    <t>ui_crystal_1,UI</t>
   </si>
   <si>
     <t>魔晶</t>
@@ -2180,10 +2180,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="57.375" customWidth="1"/>
+    <col min="2" max="2" width="70.875" customWidth="1"/>
     <col min="3" max="3" width="22.25" customWidth="1"/>
-    <col min="4" max="4" width="8.875" customWidth="1"/>
-    <col min="5" max="5" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="18.625" customWidth="1"/>
+    <col min="5" max="5" width="30.5" customWidth="1"/>
     <col min="6" max="6" width="24.875" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="31.75" customWidth="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ItemsInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="396">
   <si>
     <t>id</t>
   </si>
@@ -56,6 +56,9 @@
     <t>attack_mode_data</t>
   </si>
   <si>
+    <t>other_data</t>
+  </si>
+  <si>
     <t>name[language]</t>
   </si>
   <si>
@@ -99,6 +102,9 @@
   </si>
   <si>
     <t>攻击模式相关数据(ShowSprite,VertexRotateAxis,VertexRotateSpeed,UVRotateSpeed,StartPosition)</t>
+  </si>
+  <si>
+    <t>其他数据</t>
   </si>
   <si>
     <t>名字</t>
@@ -2176,7 +2182,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K185"/>
+  <dimension ref="A1:L185"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
@@ -2187,12 +2193,12 @@
     <col min="6" max="6" width="24.875" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="31.75" customWidth="1"/>
-    <col min="9" max="9" width="22.375" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="42.875" customWidth="1"/>
+    <col min="9" max="10" width="110.375" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="42.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2226,78 +2232,87 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:11">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:12">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2314,16 +2329,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:11">
+        <v>28</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:12">
       <c r="A5">
         <v>100001</v>
       </c>
@@ -2339,14 +2354,14 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>100001</v>
       </c>
-      <c r="K5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:11">
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:12">
       <c r="A6">
         <v>10100001</v>
       </c>
@@ -2363,16 +2378,16 @@
         <v>1500001</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6">
+        <v>31</v>
+      </c>
+      <c r="K6">
         <v>10100001</v>
       </c>
-      <c r="K6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:11">
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:12">
       <c r="A7">
         <v>10100002</v>
       </c>
@@ -2389,16 +2404,16 @@
         <v>1500002</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7">
+        <v>33</v>
+      </c>
+      <c r="K7">
         <v>10100002</v>
       </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:11">
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:12">
       <c r="A8">
         <v>10100003</v>
       </c>
@@ -2415,16 +2430,16 @@
         <v>1500003</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
+        <v>35</v>
+      </c>
+      <c r="K8">
         <v>10100003</v>
       </c>
-      <c r="K8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:11">
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:12">
       <c r="A9">
         <v>10100004</v>
       </c>
@@ -2441,16 +2456,16 @@
         <v>1500004</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9">
+        <v>37</v>
+      </c>
+      <c r="K9">
         <v>10100004</v>
       </c>
-      <c r="K9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:11">
+      <c r="L9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:12">
       <c r="A10">
         <v>10200001</v>
       </c>
@@ -2467,16 +2482,16 @@
         <v>1510001</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10">
+        <v>39</v>
+      </c>
+      <c r="K10">
         <v>10200001</v>
       </c>
-      <c r="K10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:11">
+      <c r="L10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:12">
       <c r="A11">
         <v>10200002</v>
       </c>
@@ -2493,16 +2508,16 @@
         <v>1510002</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11">
+        <v>41</v>
+      </c>
+      <c r="K11">
         <v>10200002</v>
       </c>
-      <c r="K11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:11">
+      <c r="L11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:12">
       <c r="A12">
         <v>10200003</v>
       </c>
@@ -2519,16 +2534,16 @@
         <v>1510003</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12">
+        <v>43</v>
+      </c>
+      <c r="K12">
         <v>10200003</v>
       </c>
-      <c r="K12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:11">
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:12">
       <c r="A13">
         <v>10200004</v>
       </c>
@@ -2545,16 +2560,16 @@
         <v>1510004</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13">
+        <v>45</v>
+      </c>
+      <c r="K13">
         <v>10200004</v>
       </c>
-      <c r="K13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:11">
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:12">
       <c r="A14">
         <v>10300001</v>
       </c>
@@ -2571,16 +2586,16 @@
         <v>1520001</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14">
+        <v>47</v>
+      </c>
+      <c r="K14">
         <v>10300001</v>
       </c>
-      <c r="K14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:11">
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:12">
       <c r="A15">
         <v>10300002</v>
       </c>
@@ -2597,16 +2612,16 @@
         <v>1520002</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15">
+        <v>49</v>
+      </c>
+      <c r="K15">
         <v>10300002</v>
       </c>
-      <c r="K15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:11">
+      <c r="L15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:12">
       <c r="A16">
         <v>10300003</v>
       </c>
@@ -2623,16 +2638,16 @@
         <v>1520003</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16">
+        <v>51</v>
+      </c>
+      <c r="K16">
         <v>10300003</v>
       </c>
-      <c r="K16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:11">
+      <c r="L16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:12">
       <c r="A17">
         <v>10300004</v>
       </c>
@@ -2649,16 +2664,16 @@
         <v>1520004</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
-      </c>
-      <c r="J17">
+        <v>53</v>
+      </c>
+      <c r="K17">
         <v>10300004</v>
       </c>
-      <c r="K17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:11">
+      <c r="L17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:12">
       <c r="A18">
         <v>11000001</v>
       </c>
@@ -2678,16 +2693,16 @@
         <v>1900001</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18">
+        <v>55</v>
+      </c>
+      <c r="K18">
         <v>11000001</v>
       </c>
-      <c r="K18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" spans="1:11">
+      <c r="L18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:12">
       <c r="A19">
         <v>11000002</v>
       </c>
@@ -2707,16 +2722,16 @@
         <v>1900002</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19">
+        <v>57</v>
+      </c>
+      <c r="K19">
         <v>11000002</v>
       </c>
-      <c r="K19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" spans="1:11">
+      <c r="L19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:12">
       <c r="A20">
         <v>11000003</v>
       </c>
@@ -2736,16 +2751,16 @@
         <v>1900003</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
-      </c>
-      <c r="J20">
+        <v>59</v>
+      </c>
+      <c r="K20">
         <v>11000003</v>
       </c>
-      <c r="K20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="1:11">
+      <c r="L20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:12">
       <c r="A21">
         <v>11000004</v>
       </c>
@@ -2765,16 +2780,16 @@
         <v>1900004</v>
       </c>
       <c r="G21" t="s">
-        <v>59</v>
-      </c>
-      <c r="J21">
+        <v>61</v>
+      </c>
+      <c r="K21">
         <v>11000004</v>
       </c>
-      <c r="K21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:11">
+      <c r="L21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:12">
       <c r="A22">
         <v>11000005</v>
       </c>
@@ -2794,16 +2809,16 @@
         <v>1900005</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
-      </c>
-      <c r="J22">
+        <v>63</v>
+      </c>
+      <c r="K22">
         <v>11000005</v>
       </c>
-      <c r="K22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="1:11">
+      <c r="L22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:12">
       <c r="A23">
         <v>11000006</v>
       </c>
@@ -2823,16 +2838,16 @@
         <v>1900006</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
-      </c>
-      <c r="J23">
+        <v>65</v>
+      </c>
+      <c r="K23">
         <v>11000006</v>
       </c>
-      <c r="K23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:11">
+      <c r="L23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:12">
       <c r="A24">
         <v>11000007</v>
       </c>
@@ -2852,16 +2867,16 @@
         <v>1900007</v>
       </c>
       <c r="G24" t="s">
-        <v>65</v>
-      </c>
-      <c r="J24">
+        <v>67</v>
+      </c>
+      <c r="K24">
         <v>11000007</v>
       </c>
-      <c r="K24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:11">
+      <c r="L24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:12">
       <c r="A25">
         <v>11000008</v>
       </c>
@@ -2881,16 +2896,16 @@
         <v>1900008</v>
       </c>
       <c r="G25" t="s">
-        <v>67</v>
-      </c>
-      <c r="J25">
+        <v>69</v>
+      </c>
+      <c r="K25">
         <v>11000008</v>
       </c>
-      <c r="K25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:11">
+      <c r="L25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:12">
       <c r="A26">
         <v>11000009</v>
       </c>
@@ -2910,16 +2925,16 @@
         <v>1900009</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
-      </c>
-      <c r="J26">
+        <v>71</v>
+      </c>
+      <c r="K26">
         <v>11000009</v>
       </c>
-      <c r="K26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:11">
+      <c r="L26" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:12">
       <c r="A27">
         <v>11010001</v>
       </c>
@@ -2939,16 +2954,16 @@
         <v>1910001</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
-      </c>
-      <c r="J27">
+        <v>73</v>
+      </c>
+      <c r="K27">
         <v>11010001</v>
       </c>
-      <c r="K27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>20100001</v>
       </c>
@@ -2965,16 +2980,16 @@
         <v>2500001</v>
       </c>
       <c r="G28" t="s">
-        <v>73</v>
-      </c>
-      <c r="J28">
+        <v>75</v>
+      </c>
+      <c r="K28">
         <v>20100001</v>
       </c>
-      <c r="K28" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>20100002</v>
       </c>
@@ -2991,16 +3006,16 @@
         <v>2500002</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
-      </c>
-      <c r="J29">
+        <v>77</v>
+      </c>
+      <c r="K29">
         <v>20100002</v>
       </c>
-      <c r="K29" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>20100003</v>
       </c>
@@ -3017,16 +3032,16 @@
         <v>2500003</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
-      </c>
-      <c r="J30">
+        <v>79</v>
+      </c>
+      <c r="K30">
         <v>20100003</v>
       </c>
-      <c r="K30" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31">
         <v>20100004</v>
       </c>
@@ -3043,16 +3058,16 @@
         <v>2500004</v>
       </c>
       <c r="G31" t="s">
-        <v>79</v>
-      </c>
-      <c r="J31">
+        <v>81</v>
+      </c>
+      <c r="K31">
         <v>20100004</v>
       </c>
-      <c r="K31" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32">
         <v>20100005</v>
       </c>
@@ -3069,16 +3084,16 @@
         <v>2500005</v>
       </c>
       <c r="G32" t="s">
-        <v>81</v>
-      </c>
-      <c r="J32">
+        <v>83</v>
+      </c>
+      <c r="K32">
         <v>20100005</v>
       </c>
-      <c r="K32" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33">
         <v>20100006</v>
       </c>
@@ -3095,16 +3110,16 @@
         <v>2500006</v>
       </c>
       <c r="G33" t="s">
-        <v>83</v>
-      </c>
-      <c r="J33">
+        <v>85</v>
+      </c>
+      <c r="K33">
         <v>20100006</v>
       </c>
-      <c r="K33" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34">
         <v>20100007</v>
       </c>
@@ -3121,16 +3136,16 @@
         <v>2500007</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
-      </c>
-      <c r="J34">
+        <v>87</v>
+      </c>
+      <c r="K34">
         <v>20100007</v>
       </c>
-      <c r="K34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>20200001</v>
       </c>
@@ -3147,16 +3162,16 @@
         <v>2510001</v>
       </c>
       <c r="G35" t="s">
-        <v>87</v>
-      </c>
-      <c r="J35">
+        <v>89</v>
+      </c>
+      <c r="K35">
         <v>20200001</v>
       </c>
-      <c r="K35" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36">
         <v>20200002</v>
       </c>
@@ -3173,16 +3188,16 @@
         <v>2510002</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
-      </c>
-      <c r="J36">
+        <v>91</v>
+      </c>
+      <c r="K36">
         <v>20200002</v>
       </c>
-      <c r="K36" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" spans="1:11">
+      <c r="L36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:12">
       <c r="A37">
         <v>20200003</v>
       </c>
@@ -3199,16 +3214,16 @@
         <v>2510003</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
-      </c>
-      <c r="J37">
+        <v>93</v>
+      </c>
+      <c r="K37">
         <v>20200003</v>
       </c>
-      <c r="K37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38">
         <v>20200004</v>
       </c>
@@ -3225,16 +3240,16 @@
         <v>2510004</v>
       </c>
       <c r="G38" t="s">
-        <v>93</v>
-      </c>
-      <c r="J38">
+        <v>95</v>
+      </c>
+      <c r="K38">
         <v>20200004</v>
       </c>
-      <c r="K38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="L38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>20200005</v>
       </c>
@@ -3251,16 +3266,16 @@
         <v>2510005</v>
       </c>
       <c r="G39" t="s">
-        <v>95</v>
-      </c>
-      <c r="J39">
+        <v>97</v>
+      </c>
+      <c r="K39">
         <v>20200005</v>
       </c>
-      <c r="K39" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40">
         <v>20200006</v>
       </c>
@@ -3277,16 +3292,16 @@
         <v>2510006</v>
       </c>
       <c r="G40" t="s">
-        <v>97</v>
-      </c>
-      <c r="J40">
+        <v>99</v>
+      </c>
+      <c r="K40">
         <v>20200006</v>
       </c>
-      <c r="K40" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41">
         <v>20200007</v>
       </c>
@@ -3303,16 +3318,16 @@
         <v>2510007</v>
       </c>
       <c r="G41" t="s">
-        <v>99</v>
-      </c>
-      <c r="J41">
+        <v>101</v>
+      </c>
+      <c r="K41">
         <v>20200007</v>
       </c>
-      <c r="K41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="L41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42">
         <v>20200008</v>
       </c>
@@ -3329,16 +3344,16 @@
         <v>2510008</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
-      </c>
-      <c r="J42">
+        <v>103</v>
+      </c>
+      <c r="K42">
         <v>20200008</v>
       </c>
-      <c r="K42" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="L42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43">
         <v>20200009</v>
       </c>
@@ -3355,16 +3370,16 @@
         <v>2510009</v>
       </c>
       <c r="G43" t="s">
-        <v>103</v>
-      </c>
-      <c r="J43">
+        <v>105</v>
+      </c>
+      <c r="K43">
         <v>20200009</v>
       </c>
-      <c r="K43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="L43" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44">
         <v>20200010</v>
       </c>
@@ -3381,16 +3396,16 @@
         <v>2510010</v>
       </c>
       <c r="G44" t="s">
-        <v>105</v>
-      </c>
-      <c r="J44">
+        <v>107</v>
+      </c>
+      <c r="K44">
         <v>20200010</v>
       </c>
-      <c r="K44" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="L44" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45">
         <v>20200011</v>
       </c>
@@ -3407,16 +3422,16 @@
         <v>2510011</v>
       </c>
       <c r="G45" t="s">
-        <v>107</v>
-      </c>
-      <c r="J45">
+        <v>109</v>
+      </c>
+      <c r="K45">
         <v>20200011</v>
       </c>
-      <c r="K45" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="L45" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46">
         <v>20300001</v>
       </c>
@@ -3433,16 +3448,16 @@
         <v>2520001</v>
       </c>
       <c r="G46" t="s">
-        <v>109</v>
-      </c>
-      <c r="J46">
+        <v>111</v>
+      </c>
+      <c r="K46">
         <v>20300001</v>
       </c>
-      <c r="K46" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="L46" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47">
         <v>20300002</v>
       </c>
@@ -3459,16 +3474,16 @@
         <v>2520002</v>
       </c>
       <c r="G47" t="s">
-        <v>111</v>
-      </c>
-      <c r="J47">
+        <v>113</v>
+      </c>
+      <c r="K47">
         <v>20300002</v>
       </c>
-      <c r="K47" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="L47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48">
         <v>20300003</v>
       </c>
@@ -3485,16 +3500,16 @@
         <v>2520003</v>
       </c>
       <c r="G48" t="s">
-        <v>113</v>
-      </c>
-      <c r="J48">
+        <v>115</v>
+      </c>
+      <c r="K48">
         <v>20300003</v>
       </c>
-      <c r="K48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="L48" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49">
         <v>20300004</v>
       </c>
@@ -3511,16 +3526,16 @@
         <v>2520004</v>
       </c>
       <c r="G49" t="s">
-        <v>115</v>
-      </c>
-      <c r="J49">
+        <v>117</v>
+      </c>
+      <c r="K49">
         <v>20300004</v>
       </c>
-      <c r="K49" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="L49" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50">
         <v>20300005</v>
       </c>
@@ -3537,16 +3552,16 @@
         <v>2520005</v>
       </c>
       <c r="G50" t="s">
-        <v>117</v>
-      </c>
-      <c r="J50">
+        <v>119</v>
+      </c>
+      <c r="K50">
         <v>20300005</v>
       </c>
-      <c r="K50" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" ht="12" customHeight="1" spans="1:11">
+      <c r="L50" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" ht="12" customHeight="1" spans="1:12">
       <c r="A51">
         <v>21000001</v>
       </c>
@@ -3566,22 +3581,22 @@
         <v>2900001</v>
       </c>
       <c r="G51" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H51">
         <v>45</v>
       </c>
       <c r="I51" t="s">
-        <v>120</v>
-      </c>
-      <c r="J51">
+        <v>122</v>
+      </c>
+      <c r="K51">
         <v>21000001</v>
       </c>
-      <c r="K51" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="L51" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>21000002</v>
       </c>
@@ -3601,22 +3616,22 @@
         <v>2900002</v>
       </c>
       <c r="G52" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H52">
         <v>45</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
-      </c>
-      <c r="J52">
+        <v>125</v>
+      </c>
+      <c r="K52">
         <v>21000002</v>
       </c>
-      <c r="K52" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="L52" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53">
         <v>21000003</v>
       </c>
@@ -3636,16 +3651,16 @@
         <v>2900003</v>
       </c>
       <c r="G53" t="s">
-        <v>125</v>
-      </c>
-      <c r="J53">
+        <v>127</v>
+      </c>
+      <c r="K53">
         <v>21000003</v>
       </c>
-      <c r="K53" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="L53" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54">
         <v>21000004</v>
       </c>
@@ -3665,16 +3680,16 @@
         <v>2900004</v>
       </c>
       <c r="G54" t="s">
-        <v>127</v>
-      </c>
-      <c r="J54">
+        <v>129</v>
+      </c>
+      <c r="K54">
         <v>21000004</v>
       </c>
-      <c r="K54" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="L54" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55">
         <v>21000005</v>
       </c>
@@ -3694,16 +3709,16 @@
         <v>2900005</v>
       </c>
       <c r="G55" t="s">
-        <v>129</v>
-      </c>
-      <c r="J55">
+        <v>131</v>
+      </c>
+      <c r="K55">
         <v>21000005</v>
       </c>
-      <c r="K55" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="L55" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56">
         <v>21000006</v>
       </c>
@@ -3723,16 +3738,16 @@
         <v>2900006</v>
       </c>
       <c r="G56" t="s">
-        <v>131</v>
-      </c>
-      <c r="J56">
+        <v>133</v>
+      </c>
+      <c r="K56">
         <v>21000006</v>
       </c>
-      <c r="K56" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="L56" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57">
         <v>21000007</v>
       </c>
@@ -3752,16 +3767,16 @@
         <v>2900007</v>
       </c>
       <c r="G57" t="s">
-        <v>133</v>
-      </c>
-      <c r="J57">
+        <v>135</v>
+      </c>
+      <c r="K57">
         <v>21000007</v>
       </c>
-      <c r="K57" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="L57" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58">
         <v>21000008</v>
       </c>
@@ -3781,16 +3796,16 @@
         <v>2900008</v>
       </c>
       <c r="G58" t="s">
-        <v>135</v>
-      </c>
-      <c r="J58">
+        <v>137</v>
+      </c>
+      <c r="K58">
         <v>21000008</v>
       </c>
-      <c r="K58" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="L58" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59">
         <v>21000009</v>
       </c>
@@ -3810,16 +3825,16 @@
         <v>2900009</v>
       </c>
       <c r="G59" t="s">
-        <v>137</v>
-      </c>
-      <c r="J59">
+        <v>139</v>
+      </c>
+      <c r="K59">
         <v>21000009</v>
       </c>
-      <c r="K59" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="L59" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60">
         <v>21000010</v>
       </c>
@@ -3839,16 +3854,16 @@
         <v>2900010</v>
       </c>
       <c r="G60" t="s">
-        <v>139</v>
-      </c>
-      <c r="J60">
+        <v>141</v>
+      </c>
+      <c r="K60">
         <v>21000010</v>
       </c>
-      <c r="K60" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="L60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61">
         <v>21010001</v>
       </c>
@@ -3868,19 +3883,19 @@
         <v>2910001</v>
       </c>
       <c r="G61" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H61">
         <v>-45</v>
       </c>
-      <c r="J61">
+      <c r="K61">
         <v>21010001</v>
       </c>
-      <c r="K61" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="L61" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62">
         <v>21010002</v>
       </c>
@@ -3900,19 +3915,19 @@
         <v>2910002</v>
       </c>
       <c r="G62" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H62">
         <v>-45</v>
       </c>
-      <c r="J62">
+      <c r="K62">
         <v>21010002</v>
       </c>
-      <c r="K62" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+      <c r="L62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63">
         <v>21010003</v>
       </c>
@@ -3932,19 +3947,19 @@
         <v>2910003</v>
       </c>
       <c r="G63" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H63">
         <v>-45</v>
       </c>
-      <c r="J63">
+      <c r="K63">
         <v>21010003</v>
       </c>
-      <c r="K63" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="L63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64">
         <v>21010004</v>
       </c>
@@ -3964,19 +3979,19 @@
         <v>2910004</v>
       </c>
       <c r="G64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H64">
         <v>-45</v>
       </c>
-      <c r="J64">
+      <c r="K64">
         <v>21010004</v>
       </c>
-      <c r="K64" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="L64" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65">
         <v>21010005</v>
       </c>
@@ -3996,16 +4011,16 @@
         <v>2910005</v>
       </c>
       <c r="G65" t="s">
-        <v>149</v>
-      </c>
-      <c r="J65">
+        <v>151</v>
+      </c>
+      <c r="K65">
         <v>21010005</v>
       </c>
-      <c r="K65" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+      <c r="L65" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66">
         <v>21010006</v>
       </c>
@@ -4025,16 +4040,16 @@
         <v>2910006</v>
       </c>
       <c r="G66" t="s">
-        <v>151</v>
-      </c>
-      <c r="J66">
+        <v>153</v>
+      </c>
+      <c r="K66">
         <v>21010006</v>
       </c>
-      <c r="K66" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="L66" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67">
         <v>21010007</v>
       </c>
@@ -4054,16 +4069,16 @@
         <v>2910007</v>
       </c>
       <c r="G67" t="s">
-        <v>153</v>
-      </c>
-      <c r="J67">
+        <v>155</v>
+      </c>
+      <c r="K67">
         <v>21010007</v>
       </c>
-      <c r="K67" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="L67" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68">
         <v>21010008</v>
       </c>
@@ -4083,16 +4098,16 @@
         <v>2910008</v>
       </c>
       <c r="G68" t="s">
-        <v>155</v>
-      </c>
-      <c r="J68">
+        <v>157</v>
+      </c>
+      <c r="K68">
         <v>21010008</v>
       </c>
-      <c r="K68" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
+      <c r="L68" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69">
         <v>21010009</v>
       </c>
@@ -4112,16 +4127,16 @@
         <v>2910009</v>
       </c>
       <c r="G69" t="s">
-        <v>157</v>
-      </c>
-      <c r="J69">
+        <v>159</v>
+      </c>
+      <c r="K69">
         <v>21010009</v>
       </c>
-      <c r="K69" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="L69" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70">
         <v>21010010</v>
       </c>
@@ -4141,16 +4156,16 @@
         <v>2910010</v>
       </c>
       <c r="G70" t="s">
-        <v>159</v>
-      </c>
-      <c r="J70">
+        <v>161</v>
+      </c>
+      <c r="K70">
         <v>21010010</v>
       </c>
-      <c r="K70" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="L70" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71">
         <v>21010011</v>
       </c>
@@ -4170,19 +4185,19 @@
         <v>2910011</v>
       </c>
       <c r="G71" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H71">
         <v>-45</v>
       </c>
-      <c r="J71">
+      <c r="K71">
         <v>21010011</v>
       </c>
-      <c r="K71" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="L71" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72">
         <v>21010012</v>
       </c>
@@ -4202,19 +4217,19 @@
         <v>2910012</v>
       </c>
       <c r="G72" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H72">
         <v>-45</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>21010012</v>
       </c>
-      <c r="K72" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
+      <c r="L72" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73">
         <v>21010013</v>
       </c>
@@ -4234,16 +4249,16 @@
         <v>2910013</v>
       </c>
       <c r="G73" t="s">
-        <v>165</v>
-      </c>
-      <c r="J73">
+        <v>167</v>
+      </c>
+      <c r="K73">
         <v>21010013</v>
       </c>
-      <c r="K73" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
+      <c r="L73" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74">
         <v>21010014</v>
       </c>
@@ -4263,16 +4278,16 @@
         <v>2910014</v>
       </c>
       <c r="G74" t="s">
-        <v>167</v>
-      </c>
-      <c r="J74">
+        <v>169</v>
+      </c>
+      <c r="K74">
         <v>21010014</v>
       </c>
-      <c r="K74" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
+      <c r="L74" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75">
         <v>21010015</v>
       </c>
@@ -4292,16 +4307,16 @@
         <v>2910015</v>
       </c>
       <c r="G75" t="s">
-        <v>169</v>
-      </c>
-      <c r="J75">
+        <v>171</v>
+      </c>
+      <c r="K75">
         <v>21010015</v>
       </c>
-      <c r="K75" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
+      <c r="L75" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76">
         <v>21010016</v>
       </c>
@@ -4321,16 +4336,16 @@
         <v>2910016</v>
       </c>
       <c r="G76" t="s">
-        <v>171</v>
-      </c>
-      <c r="J76">
+        <v>173</v>
+      </c>
+      <c r="K76">
         <v>21010016</v>
       </c>
-      <c r="K76" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+      <c r="L76" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77">
         <v>21010017</v>
       </c>
@@ -4350,16 +4365,16 @@
         <v>2910017</v>
       </c>
       <c r="G77" t="s">
-        <v>173</v>
-      </c>
-      <c r="J77">
+        <v>175</v>
+      </c>
+      <c r="K77">
         <v>21010017</v>
       </c>
-      <c r="K77" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
+      <c r="L77" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78">
         <v>21010018</v>
       </c>
@@ -4379,16 +4394,16 @@
         <v>2910018</v>
       </c>
       <c r="G78" t="s">
-        <v>175</v>
-      </c>
-      <c r="J78">
+        <v>177</v>
+      </c>
+      <c r="K78">
         <v>21010018</v>
       </c>
-      <c r="K78" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+      <c r="L78" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79">
         <v>21010019</v>
       </c>
@@ -4408,16 +4423,16 @@
         <v>2910019</v>
       </c>
       <c r="G79" t="s">
-        <v>177</v>
-      </c>
-      <c r="J79">
+        <v>179</v>
+      </c>
+      <c r="K79">
         <v>21010019</v>
       </c>
-      <c r="K79" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
+      <c r="L79" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80">
         <v>21010020</v>
       </c>
@@ -4437,16 +4452,16 @@
         <v>2910020</v>
       </c>
       <c r="G80" t="s">
-        <v>179</v>
-      </c>
-      <c r="J80">
+        <v>181</v>
+      </c>
+      <c r="K80">
         <v>21010020</v>
       </c>
-      <c r="K80" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
+      <c r="L80" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81">
         <v>30100001</v>
       </c>
@@ -4463,16 +4478,16 @@
         <v>3020001</v>
       </c>
       <c r="G81" t="s">
-        <v>181</v>
-      </c>
-      <c r="J81">
+        <v>183</v>
+      </c>
+      <c r="K81">
         <v>30100001</v>
       </c>
-      <c r="K81" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
+      <c r="L81" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82">
         <v>30100002</v>
       </c>
@@ -4489,16 +4504,16 @@
         <v>3020002</v>
       </c>
       <c r="G82" t="s">
-        <v>183</v>
-      </c>
-      <c r="J82">
+        <v>185</v>
+      </c>
+      <c r="K82">
         <v>30100002</v>
       </c>
-      <c r="K82" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
+      <c r="L82" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83">
         <v>30100003</v>
       </c>
@@ -4515,16 +4530,16 @@
         <v>3020003</v>
       </c>
       <c r="G83" t="s">
-        <v>185</v>
-      </c>
-      <c r="J83">
+        <v>187</v>
+      </c>
+      <c r="K83">
         <v>30100003</v>
       </c>
-      <c r="K83" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
+      <c r="L83" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
       <c r="A84">
         <v>30100004</v>
       </c>
@@ -4541,16 +4556,16 @@
         <v>3020004</v>
       </c>
       <c r="G84" t="s">
-        <v>187</v>
-      </c>
-      <c r="J84">
+        <v>189</v>
+      </c>
+      <c r="K84">
         <v>30100004</v>
       </c>
-      <c r="K84" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
+      <c r="L84" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85">
         <v>30100005</v>
       </c>
@@ -4567,16 +4582,16 @@
         <v>3020005</v>
       </c>
       <c r="G85" t="s">
-        <v>189</v>
-      </c>
-      <c r="J85">
+        <v>191</v>
+      </c>
+      <c r="K85">
         <v>30100005</v>
       </c>
-      <c r="K85" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
+      <c r="L85" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
       <c r="A86">
         <v>30100006</v>
       </c>
@@ -4593,16 +4608,16 @@
         <v>3020006</v>
       </c>
       <c r="G86" t="s">
-        <v>191</v>
-      </c>
-      <c r="J86">
+        <v>193</v>
+      </c>
+      <c r="K86">
         <v>30100006</v>
       </c>
-      <c r="K86" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
+      <c r="L86" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87">
         <v>30100007</v>
       </c>
@@ -4619,16 +4634,16 @@
         <v>3020007</v>
       </c>
       <c r="G87" t="s">
-        <v>193</v>
-      </c>
-      <c r="J87">
+        <v>195</v>
+      </c>
+      <c r="K87">
         <v>30100007</v>
       </c>
-      <c r="K87" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" spans="1:11">
+      <c r="L87" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" spans="1:12">
       <c r="A88">
         <v>30100008</v>
       </c>
@@ -4645,16 +4660,16 @@
         <v>3020008</v>
       </c>
       <c r="G88" t="s">
-        <v>195</v>
-      </c>
-      <c r="J88">
+        <v>197</v>
+      </c>
+      <c r="K88">
         <v>30100008</v>
       </c>
-      <c r="K88" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" spans="1:11">
+      <c r="L88" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" spans="1:12">
       <c r="A89">
         <v>30100009</v>
       </c>
@@ -4671,16 +4686,16 @@
         <v>3020009</v>
       </c>
       <c r="G89" t="s">
-        <v>197</v>
-      </c>
-      <c r="J89">
+        <v>199</v>
+      </c>
+      <c r="K89">
         <v>30100009</v>
       </c>
-      <c r="K89" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1" spans="1:11">
+      <c r="L89" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" spans="1:12">
       <c r="A90">
         <v>30100010</v>
       </c>
@@ -4697,16 +4712,16 @@
         <v>3020010</v>
       </c>
       <c r="G90" t="s">
-        <v>199</v>
-      </c>
-      <c r="J90">
+        <v>201</v>
+      </c>
+      <c r="K90">
         <v>30100010</v>
       </c>
-      <c r="K90" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" spans="1:11">
+      <c r="L90" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1" spans="1:12">
       <c r="A91">
         <v>30100011</v>
       </c>
@@ -4723,16 +4738,16 @@
         <v>3020011</v>
       </c>
       <c r="G91" t="s">
-        <v>201</v>
-      </c>
-      <c r="J91">
+        <v>203</v>
+      </c>
+      <c r="K91">
         <v>30100011</v>
       </c>
-      <c r="K91" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1" spans="1:11">
+      <c r="L91" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1" spans="1:12">
       <c r="A92">
         <v>30100012</v>
       </c>
@@ -4749,16 +4764,16 @@
         <v>3020012</v>
       </c>
       <c r="G92" t="s">
-        <v>203</v>
-      </c>
-      <c r="J92">
+        <v>205</v>
+      </c>
+      <c r="K92">
         <v>30100012</v>
       </c>
-      <c r="K92" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1" spans="1:11">
+      <c r="L92" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1" spans="1:12">
       <c r="A93">
         <v>30100013</v>
       </c>
@@ -4775,16 +4790,16 @@
         <v>3020013</v>
       </c>
       <c r="G93" t="s">
-        <v>205</v>
-      </c>
-      <c r="J93">
+        <v>207</v>
+      </c>
+      <c r="K93">
         <v>30100013</v>
       </c>
-      <c r="K93" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1" spans="1:11">
+      <c r="L93" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" spans="1:12">
       <c r="A94">
         <v>30100014</v>
       </c>
@@ -4801,16 +4816,16 @@
         <v>3020014</v>
       </c>
       <c r="G94" t="s">
-        <v>207</v>
-      </c>
-      <c r="J94">
+        <v>209</v>
+      </c>
+      <c r="K94">
         <v>30100014</v>
       </c>
-      <c r="K94" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" spans="1:11">
+      <c r="L94" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" spans="1:12">
       <c r="A95">
         <v>30100015</v>
       </c>
@@ -4827,16 +4842,16 @@
         <v>3020015</v>
       </c>
       <c r="G95" t="s">
-        <v>209</v>
-      </c>
-      <c r="J95">
+        <v>211</v>
+      </c>
+      <c r="K95">
         <v>30100015</v>
       </c>
-      <c r="K95" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1" spans="1:11">
+      <c r="L95" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" spans="1:12">
       <c r="A96">
         <v>30100016</v>
       </c>
@@ -4853,16 +4868,16 @@
         <v>3020016</v>
       </c>
       <c r="G96" t="s">
-        <v>211</v>
-      </c>
-      <c r="J96">
+        <v>213</v>
+      </c>
+      <c r="K96">
         <v>30100016</v>
       </c>
-      <c r="K96" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" spans="1:11">
+      <c r="L96" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" spans="1:12">
       <c r="A97">
         <v>30100017</v>
       </c>
@@ -4879,16 +4894,16 @@
         <v>3020017</v>
       </c>
       <c r="G97" t="s">
-        <v>213</v>
-      </c>
-      <c r="J97">
+        <v>215</v>
+      </c>
+      <c r="K97">
         <v>30100017</v>
       </c>
-      <c r="K97" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" spans="1:11">
+      <c r="L97" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1" spans="1:12">
       <c r="A98">
         <v>30100018</v>
       </c>
@@ -4905,16 +4920,16 @@
         <v>3020018</v>
       </c>
       <c r="G98" t="s">
-        <v>215</v>
-      </c>
-      <c r="J98">
+        <v>217</v>
+      </c>
+      <c r="K98">
         <v>30100018</v>
       </c>
-      <c r="K98" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
+      <c r="L98" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
       <c r="A99">
         <v>30100019</v>
       </c>
@@ -4931,16 +4946,16 @@
         <v>3020019</v>
       </c>
       <c r="G99" t="s">
-        <v>217</v>
-      </c>
-      <c r="J99">
+        <v>219</v>
+      </c>
+      <c r="K99">
         <v>30100019</v>
       </c>
-      <c r="K99" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11">
+      <c r="L99" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
       <c r="A100">
         <v>30100020</v>
       </c>
@@ -4957,16 +4972,16 @@
         <v>3020020</v>
       </c>
       <c r="G100" t="s">
-        <v>219</v>
-      </c>
-      <c r="J100">
+        <v>221</v>
+      </c>
+      <c r="K100">
         <v>30100020</v>
       </c>
-      <c r="K100" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
+      <c r="L100" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
       <c r="A101">
         <v>40100001</v>
       </c>
@@ -4983,16 +4998,16 @@
         <v>4500003</v>
       </c>
       <c r="G101" t="s">
-        <v>221</v>
-      </c>
-      <c r="J101">
+        <v>223</v>
+      </c>
+      <c r="K101">
         <v>40100001</v>
       </c>
-      <c r="K101" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="102" ht="12" customHeight="1" spans="1:11">
+      <c r="L101" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="102" ht="12" customHeight="1" spans="1:12">
       <c r="A102">
         <v>40200001</v>
       </c>
@@ -5009,16 +5024,16 @@
         <v>4510001</v>
       </c>
       <c r="G102" t="s">
-        <v>223</v>
-      </c>
-      <c r="J102">
+        <v>225</v>
+      </c>
+      <c r="K102">
         <v>40200001</v>
       </c>
-      <c r="K102" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11">
+      <c r="L102" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
       <c r="A103">
         <v>40200002</v>
       </c>
@@ -5035,16 +5050,16 @@
         <v>4510002</v>
       </c>
       <c r="G103" t="s">
-        <v>225</v>
-      </c>
-      <c r="J103">
+        <v>227</v>
+      </c>
+      <c r="K103">
         <v>40200002</v>
       </c>
-      <c r="K103" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11">
+      <c r="L103" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
       <c r="A104">
         <v>40200003</v>
       </c>
@@ -5061,16 +5076,16 @@
         <v>4510003</v>
       </c>
       <c r="G104" t="s">
-        <v>227</v>
-      </c>
-      <c r="J104">
+        <v>229</v>
+      </c>
+      <c r="K104">
         <v>40200003</v>
       </c>
-      <c r="K104" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11">
+      <c r="L104" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
       <c r="A105">
         <v>40200004</v>
       </c>
@@ -5087,16 +5102,16 @@
         <v>4510004</v>
       </c>
       <c r="G105" t="s">
-        <v>229</v>
-      </c>
-      <c r="J105">
+        <v>231</v>
+      </c>
+      <c r="K105">
         <v>40200004</v>
       </c>
-      <c r="K105" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11">
+      <c r="L105" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
       <c r="A106">
         <v>40200005</v>
       </c>
@@ -5113,16 +5128,16 @@
         <v>4510005</v>
       </c>
       <c r="G106" t="s">
-        <v>231</v>
-      </c>
-      <c r="J106">
+        <v>233</v>
+      </c>
+      <c r="K106">
         <v>40200005</v>
       </c>
-      <c r="K106" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11">
+      <c r="L106" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
       <c r="A107">
         <v>40200006</v>
       </c>
@@ -5139,16 +5154,16 @@
         <v>4510006</v>
       </c>
       <c r="G107" t="s">
-        <v>233</v>
-      </c>
-      <c r="J107">
+        <v>235</v>
+      </c>
+      <c r="K107">
         <v>40200006</v>
       </c>
-      <c r="K107" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11">
+      <c r="L107" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
       <c r="A108">
         <v>40300001</v>
       </c>
@@ -5165,16 +5180,16 @@
         <v>4520001</v>
       </c>
       <c r="G108" t="s">
-        <v>235</v>
-      </c>
-      <c r="J108">
+        <v>237</v>
+      </c>
+      <c r="K108">
         <v>40300001</v>
       </c>
-      <c r="K108" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11">
+      <c r="L108" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
       <c r="A109">
         <v>40300002</v>
       </c>
@@ -5191,16 +5206,16 @@
         <v>4520002</v>
       </c>
       <c r="G109" t="s">
-        <v>237</v>
-      </c>
-      <c r="J109">
+        <v>239</v>
+      </c>
+      <c r="K109">
         <v>40300002</v>
       </c>
-      <c r="K109" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11">
+      <c r="L109" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
       <c r="A110">
         <v>40300003</v>
       </c>
@@ -5217,16 +5232,16 @@
         <v>4520003</v>
       </c>
       <c r="G110" t="s">
-        <v>239</v>
-      </c>
-      <c r="J110">
+        <v>241</v>
+      </c>
+      <c r="K110">
         <v>40300003</v>
       </c>
-      <c r="K110" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11">
+      <c r="L110" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
       <c r="A111">
         <v>40300004</v>
       </c>
@@ -5243,16 +5258,16 @@
         <v>4520004</v>
       </c>
       <c r="G111" t="s">
-        <v>241</v>
-      </c>
-      <c r="J111">
+        <v>243</v>
+      </c>
+      <c r="K111">
         <v>40300004</v>
       </c>
-      <c r="K111" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
+      <c r="L111" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
       <c r="A112">
         <v>41000001</v>
       </c>
@@ -5272,16 +5287,16 @@
         <v>4900001</v>
       </c>
       <c r="G112" t="s">
-        <v>243</v>
-      </c>
-      <c r="J112">
+        <v>245</v>
+      </c>
+      <c r="K112">
         <v>41000001</v>
       </c>
-      <c r="K112" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
+      <c r="L112" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
       <c r="A113">
         <v>41000002</v>
       </c>
@@ -5301,16 +5316,16 @@
         <v>4900002</v>
       </c>
       <c r="G113" t="s">
-        <v>245</v>
-      </c>
-      <c r="J113">
+        <v>247</v>
+      </c>
+      <c r="K113">
         <v>41000002</v>
       </c>
-      <c r="K113" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
+      <c r="L113" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
       <c r="A114">
         <v>41000003</v>
       </c>
@@ -5330,16 +5345,16 @@
         <v>4900003</v>
       </c>
       <c r="G114" t="s">
-        <v>247</v>
-      </c>
-      <c r="J114">
+        <v>249</v>
+      </c>
+      <c r="K114">
         <v>41000003</v>
       </c>
-      <c r="K114" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
+      <c r="L114" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
       <c r="A115">
         <v>41000004</v>
       </c>
@@ -5359,16 +5374,16 @@
         <v>4900004</v>
       </c>
       <c r="G115" t="s">
-        <v>249</v>
-      </c>
-      <c r="J115">
+        <v>251</v>
+      </c>
+      <c r="K115">
         <v>41000004</v>
       </c>
-      <c r="K115" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
+      <c r="L115" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
       <c r="A116">
         <v>41000005</v>
       </c>
@@ -5388,16 +5403,16 @@
         <v>4900005</v>
       </c>
       <c r="G116" t="s">
-        <v>251</v>
-      </c>
-      <c r="J116">
+        <v>253</v>
+      </c>
+      <c r="K116">
         <v>41000005</v>
       </c>
-      <c r="K116" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="117" customFormat="1" spans="1:11">
+      <c r="L116" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="117" customFormat="1" spans="1:12">
       <c r="A117">
         <v>50100001</v>
       </c>
@@ -5414,16 +5429,16 @@
         <v>5500001</v>
       </c>
       <c r="G117" t="s">
-        <v>253</v>
-      </c>
-      <c r="J117">
+        <v>255</v>
+      </c>
+      <c r="K117">
         <v>50100001</v>
       </c>
-      <c r="K117" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
+      <c r="L117" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
       <c r="A118">
         <v>50100002</v>
       </c>
@@ -5440,16 +5455,16 @@
         <v>5500002</v>
       </c>
       <c r="G118" t="s">
-        <v>255</v>
-      </c>
-      <c r="J118">
+        <v>257</v>
+      </c>
+      <c r="K118">
         <v>50100002</v>
       </c>
-      <c r="K118" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
+      <c r="L118" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
       <c r="A119">
         <v>50100003</v>
       </c>
@@ -5466,16 +5481,16 @@
         <v>5500003</v>
       </c>
       <c r="G119" t="s">
-        <v>257</v>
-      </c>
-      <c r="J119">
+        <v>259</v>
+      </c>
+      <c r="K119">
         <v>50100003</v>
       </c>
-      <c r="K119" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="120" customFormat="1" spans="1:11">
+      <c r="L119" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="120" customFormat="1" spans="1:12">
       <c r="A120">
         <v>50200001</v>
       </c>
@@ -5492,16 +5507,16 @@
         <v>5510001</v>
       </c>
       <c r="G120" t="s">
-        <v>259</v>
-      </c>
-      <c r="J120">
+        <v>261</v>
+      </c>
+      <c r="K120">
         <v>50200001</v>
       </c>
-      <c r="K120" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
+      <c r="L120" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
       <c r="A121">
         <v>50200002</v>
       </c>
@@ -5518,16 +5533,16 @@
         <v>5510002</v>
       </c>
       <c r="G121" t="s">
-        <v>261</v>
-      </c>
-      <c r="J121">
+        <v>263</v>
+      </c>
+      <c r="K121">
         <v>50200002</v>
       </c>
-      <c r="K121" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
+      <c r="L121" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
       <c r="A122">
         <v>50200003</v>
       </c>
@@ -5544,16 +5559,16 @@
         <v>5510003</v>
       </c>
       <c r="G122" t="s">
-        <v>263</v>
-      </c>
-      <c r="J122">
+        <v>265</v>
+      </c>
+      <c r="K122">
         <v>50200003</v>
       </c>
-      <c r="K122" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="123" customFormat="1" ht="12" customHeight="1" spans="1:11">
+      <c r="L122" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="123" customFormat="1" ht="12" customHeight="1" spans="1:12">
       <c r="A123">
         <v>50300001</v>
       </c>
@@ -5570,16 +5585,16 @@
         <v>5520001</v>
       </c>
       <c r="G123" t="s">
-        <v>265</v>
-      </c>
-      <c r="J123">
+        <v>267</v>
+      </c>
+      <c r="K123">
         <v>50300001</v>
       </c>
-      <c r="K123" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
+      <c r="L123" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
       <c r="A124">
         <v>50300002</v>
       </c>
@@ -5596,16 +5611,16 @@
         <v>5520002</v>
       </c>
       <c r="G124" t="s">
-        <v>267</v>
-      </c>
-      <c r="J124">
+        <v>269</v>
+      </c>
+      <c r="K124">
         <v>50300002</v>
       </c>
-      <c r="K124" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
+      <c r="L124" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
       <c r="A125">
         <v>50500001</v>
       </c>
@@ -5622,16 +5637,16 @@
         <v>5090001</v>
       </c>
       <c r="G125" t="s">
-        <v>269</v>
-      </c>
-      <c r="J125">
+        <v>271</v>
+      </c>
+      <c r="K125">
         <v>50500001</v>
       </c>
-      <c r="K125" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
+      <c r="L125" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
       <c r="A126">
         <v>50500002</v>
       </c>
@@ -5648,16 +5663,16 @@
         <v>5090002</v>
       </c>
       <c r="G126" t="s">
-        <v>271</v>
-      </c>
-      <c r="J126">
+        <v>273</v>
+      </c>
+      <c r="K126">
         <v>50500002</v>
       </c>
-      <c r="K126" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
+      <c r="L126" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
       <c r="A127">
         <v>50500003</v>
       </c>
@@ -5674,16 +5689,16 @@
         <v>5090003</v>
       </c>
       <c r="G127" t="s">
-        <v>273</v>
-      </c>
-      <c r="J127">
+        <v>275</v>
+      </c>
+      <c r="K127">
         <v>50500003</v>
       </c>
-      <c r="K127" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
+      <c r="L127" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
       <c r="A128">
         <v>50500004</v>
       </c>
@@ -5700,16 +5715,16 @@
         <v>5090004</v>
       </c>
       <c r="G128" t="s">
-        <v>275</v>
-      </c>
-      <c r="J128">
+        <v>277</v>
+      </c>
+      <c r="K128">
         <v>50500004</v>
       </c>
-      <c r="K128" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11">
+      <c r="L128" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
       <c r="A129">
         <v>50500005</v>
       </c>
@@ -5726,16 +5741,16 @@
         <v>5090005</v>
       </c>
       <c r="G129" t="s">
-        <v>277</v>
-      </c>
-      <c r="J129">
+        <v>279</v>
+      </c>
+      <c r="K129">
         <v>50500005</v>
       </c>
-      <c r="K129" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="130" customFormat="1" spans="1:11">
+      <c r="L129" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="130" customFormat="1" spans="1:12">
       <c r="A130">
         <v>51010001</v>
       </c>
@@ -5755,19 +5770,19 @@
         <v>5910001</v>
       </c>
       <c r="G130" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I130" t="s">
-        <v>280</v>
-      </c>
-      <c r="J130">
+        <v>282</v>
+      </c>
+      <c r="K130">
         <v>51010001</v>
       </c>
-      <c r="K130" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="131" customFormat="1" spans="1:11">
+      <c r="L130" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="131" customFormat="1" spans="1:12">
       <c r="A131">
         <v>51010002</v>
       </c>
@@ -5787,19 +5802,19 @@
         <v>5910002</v>
       </c>
       <c r="G131" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I131" t="s">
-        <v>283</v>
-      </c>
-      <c r="J131">
+        <v>285</v>
+      </c>
+      <c r="K131">
         <v>51010002</v>
       </c>
-      <c r="K131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="132" customFormat="1" spans="1:11">
+      <c r="L131" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="132" customFormat="1" spans="1:12">
       <c r="A132">
         <v>51010003</v>
       </c>
@@ -5819,19 +5834,19 @@
         <v>5910003</v>
       </c>
       <c r="G132" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I132" t="s">
-        <v>285</v>
-      </c>
-      <c r="J132">
+        <v>287</v>
+      </c>
+      <c r="K132">
         <v>51010003</v>
       </c>
-      <c r="K132" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="133" customFormat="1" spans="1:11">
+      <c r="L132" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="133" customFormat="1" spans="1:12">
       <c r="A133">
         <v>60100001</v>
       </c>
@@ -5848,16 +5863,16 @@
         <v>6500001</v>
       </c>
       <c r="G133" t="s">
-        <v>287</v>
-      </c>
-      <c r="J133">
+        <v>289</v>
+      </c>
+      <c r="K133">
         <v>60100001</v>
       </c>
-      <c r="K133" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11">
+      <c r="L133" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
       <c r="A134">
         <v>60100002</v>
       </c>
@@ -5874,16 +5889,16 @@
         <v>6500002</v>
       </c>
       <c r="G134" t="s">
-        <v>289</v>
-      </c>
-      <c r="J134">
+        <v>291</v>
+      </c>
+      <c r="K134">
         <v>60100002</v>
       </c>
-      <c r="K134" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11">
+      <c r="L134" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
       <c r="A135">
         <v>60100003</v>
       </c>
@@ -5900,16 +5915,16 @@
         <v>6500003</v>
       </c>
       <c r="G135" t="s">
-        <v>291</v>
-      </c>
-      <c r="J135">
+        <v>293</v>
+      </c>
+      <c r="K135">
         <v>60100003</v>
       </c>
-      <c r="K135" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11">
+      <c r="L135" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
       <c r="A136">
         <v>60100004</v>
       </c>
@@ -5926,16 +5941,16 @@
         <v>6500004</v>
       </c>
       <c r="G136" t="s">
-        <v>293</v>
-      </c>
-      <c r="J136">
+        <v>295</v>
+      </c>
+      <c r="K136">
         <v>60100004</v>
       </c>
-      <c r="K136" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11">
+      <c r="L136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
       <c r="A137">
         <v>60100005</v>
       </c>
@@ -5952,16 +5967,16 @@
         <v>6500005</v>
       </c>
       <c r="G137" t="s">
-        <v>294</v>
-      </c>
-      <c r="J137">
+        <v>296</v>
+      </c>
+      <c r="K137">
         <v>60100005</v>
       </c>
-      <c r="K137" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="138" ht="12" customHeight="1" spans="1:11">
+      <c r="L137" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="138" ht="12" customHeight="1" spans="1:12">
       <c r="A138">
         <v>60100006</v>
       </c>
@@ -5978,16 +5993,16 @@
         <v>6500006</v>
       </c>
       <c r="G138" t="s">
-        <v>296</v>
-      </c>
-      <c r="J138">
+        <v>298</v>
+      </c>
+      <c r="K138">
         <v>60100006</v>
       </c>
-      <c r="K138" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="139" ht="12" customHeight="1" spans="1:11">
+      <c r="L138" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="139" ht="12" customHeight="1" spans="1:12">
       <c r="A139">
         <v>60100007</v>
       </c>
@@ -6004,16 +6019,16 @@
         <v>6500007</v>
       </c>
       <c r="G139" t="s">
-        <v>298</v>
-      </c>
-      <c r="J139">
+        <v>300</v>
+      </c>
+      <c r="K139">
         <v>60100007</v>
       </c>
-      <c r="K139" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="140" ht="12" customHeight="1" spans="1:11">
+      <c r="L139" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="140" ht="12" customHeight="1" spans="1:12">
       <c r="A140">
         <v>60100008</v>
       </c>
@@ -6030,16 +6045,16 @@
         <v>6500008</v>
       </c>
       <c r="G140" t="s">
-        <v>300</v>
-      </c>
-      <c r="J140">
+        <v>302</v>
+      </c>
+      <c r="K140">
         <v>60100008</v>
       </c>
-      <c r="K140" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="141" ht="12" customHeight="1" spans="1:11">
+      <c r="L140" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="141" ht="12" customHeight="1" spans="1:12">
       <c r="A141">
         <v>60100009</v>
       </c>
@@ -6056,16 +6071,16 @@
         <v>6500009</v>
       </c>
       <c r="G141" t="s">
-        <v>302</v>
-      </c>
-      <c r="J141">
+        <v>304</v>
+      </c>
+      <c r="K141">
         <v>60100009</v>
       </c>
-      <c r="K141" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="142" ht="12" customHeight="1" spans="1:11">
+      <c r="L141" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="142" ht="12" customHeight="1" spans="1:12">
       <c r="A142">
         <v>60100010</v>
       </c>
@@ -6082,16 +6097,16 @@
         <v>6500010</v>
       </c>
       <c r="G142" t="s">
-        <v>304</v>
-      </c>
-      <c r="J142">
+        <v>306</v>
+      </c>
+      <c r="K142">
         <v>60100010</v>
       </c>
-      <c r="K142" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="143" customFormat="1" ht="12" customHeight="1" spans="1:11">
+      <c r="L142" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="143" customFormat="1" ht="12" customHeight="1" spans="1:12">
       <c r="A143">
         <v>60200001</v>
       </c>
@@ -6108,16 +6123,16 @@
         <v>6510001</v>
       </c>
       <c r="G143" t="s">
-        <v>306</v>
-      </c>
-      <c r="J143">
+        <v>308</v>
+      </c>
+      <c r="K143">
         <v>60200001</v>
       </c>
-      <c r="K143" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="144" ht="12" customHeight="1" spans="1:11">
+      <c r="L143" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="144" ht="12" customHeight="1" spans="1:12">
       <c r="A144">
         <v>60200002</v>
       </c>
@@ -6134,16 +6149,16 @@
         <v>6510002</v>
       </c>
       <c r="G144" t="s">
-        <v>307</v>
-      </c>
-      <c r="J144">
+        <v>309</v>
+      </c>
+      <c r="K144">
         <v>60200002</v>
       </c>
-      <c r="K144" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="145" customFormat="1" spans="1:11">
+      <c r="L144" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="145" customFormat="1" spans="1:12">
       <c r="A145">
         <v>60300001</v>
       </c>
@@ -6160,16 +6175,16 @@
         <v>6520001</v>
       </c>
       <c r="G145" t="s">
-        <v>309</v>
-      </c>
-      <c r="J145">
+        <v>311</v>
+      </c>
+      <c r="K145">
         <v>60300001</v>
       </c>
-      <c r="K145" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11">
+      <c r="L145" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12">
       <c r="A146">
         <v>60300002</v>
       </c>
@@ -6186,16 +6201,16 @@
         <v>6520002</v>
       </c>
       <c r="G146" t="s">
-        <v>311</v>
-      </c>
-      <c r="J146">
+        <v>313</v>
+      </c>
+      <c r="K146">
         <v>60300002</v>
       </c>
-      <c r="K146" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11">
+      <c r="L146" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12">
       <c r="A147">
         <v>60300003</v>
       </c>
@@ -6212,16 +6227,16 @@
         <v>6520003</v>
       </c>
       <c r="G147" t="s">
-        <v>313</v>
-      </c>
-      <c r="J147">
+        <v>315</v>
+      </c>
+      <c r="K147">
         <v>60300003</v>
       </c>
-      <c r="K147" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11">
+      <c r="L147" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12">
       <c r="A148">
         <v>60300004</v>
       </c>
@@ -6238,16 +6253,16 @@
         <v>6520004</v>
       </c>
       <c r="G148" t="s">
-        <v>315</v>
-      </c>
-      <c r="J148">
+        <v>317</v>
+      </c>
+      <c r="K148">
         <v>60300004</v>
       </c>
-      <c r="K148" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11">
+      <c r="L148" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12">
       <c r="A149">
         <v>60300005</v>
       </c>
@@ -6264,16 +6279,16 @@
         <v>6520005</v>
       </c>
       <c r="G149" t="s">
-        <v>317</v>
-      </c>
-      <c r="J149">
+        <v>319</v>
+      </c>
+      <c r="K149">
         <v>60300005</v>
       </c>
-      <c r="K149" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="150" customFormat="1" spans="1:11">
+      <c r="L149" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" spans="1:12">
       <c r="A150">
         <v>61010001</v>
       </c>
@@ -6293,17 +6308,17 @@
         <v>6910001</v>
       </c>
       <c r="G150" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H150"/>
-      <c r="J150">
+      <c r="K150">
         <v>61010001</v>
       </c>
-      <c r="K150" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11">
+      <c r="L150" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12">
       <c r="A151">
         <v>61010002</v>
       </c>
@@ -6323,19 +6338,19 @@
         <v>6910002</v>
       </c>
       <c r="G151" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I151" t="s">
-        <v>322</v>
-      </c>
-      <c r="J151">
+        <v>324</v>
+      </c>
+      <c r="K151">
         <v>61010002</v>
       </c>
-      <c r="K151" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11">
+      <c r="L151" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12">
       <c r="A152">
         <v>61010003</v>
       </c>
@@ -6355,16 +6370,16 @@
         <v>6910003</v>
       </c>
       <c r="G152" t="s">
-        <v>324</v>
-      </c>
-      <c r="J152">
+        <v>326</v>
+      </c>
+      <c r="K152">
         <v>61010003</v>
       </c>
-      <c r="K152" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11">
+      <c r="L152" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12">
       <c r="A153">
         <v>61010004</v>
       </c>
@@ -6384,19 +6399,19 @@
         <v>6910004</v>
       </c>
       <c r="G153" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H153">
         <v>-45</v>
       </c>
-      <c r="J153">
+      <c r="K153">
         <v>61010004</v>
       </c>
-      <c r="K153" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11">
+      <c r="L153" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12">
       <c r="A154">
         <v>61010005</v>
       </c>
@@ -6416,19 +6431,19 @@
         <v>6910005</v>
       </c>
       <c r="G154" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H154">
         <v>-45</v>
       </c>
-      <c r="J154">
+      <c r="K154">
         <v>61010005</v>
       </c>
-      <c r="K154" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11">
+      <c r="L154" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12">
       <c r="A155">
         <v>61010006</v>
       </c>
@@ -6448,19 +6463,19 @@
         <v>6910006</v>
       </c>
       <c r="G155" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H155">
         <v>-45</v>
       </c>
-      <c r="J155">
+      <c r="K155">
         <v>61010006</v>
       </c>
-      <c r="K155" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11">
+      <c r="L155" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12">
       <c r="A156">
         <v>61010007</v>
       </c>
@@ -6480,16 +6495,16 @@
         <v>6910007</v>
       </c>
       <c r="G156" t="s">
-        <v>332</v>
-      </c>
-      <c r="J156">
+        <v>334</v>
+      </c>
+      <c r="K156">
         <v>61010007</v>
       </c>
-      <c r="K156" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11">
+      <c r="L156" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12">
       <c r="A157">
         <v>61010008</v>
       </c>
@@ -6509,16 +6524,16 @@
         <v>6910008</v>
       </c>
       <c r="G157" t="s">
-        <v>334</v>
-      </c>
-      <c r="J157">
+        <v>336</v>
+      </c>
+      <c r="K157">
         <v>61010008</v>
       </c>
-      <c r="K157" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11">
+      <c r="L157" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12">
       <c r="A158">
         <v>61010009</v>
       </c>
@@ -6538,16 +6553,16 @@
         <v>6910009</v>
       </c>
       <c r="G158" t="s">
-        <v>336</v>
-      </c>
-      <c r="J158">
+        <v>338</v>
+      </c>
+      <c r="K158">
         <v>61010009</v>
       </c>
-      <c r="K158" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11">
+      <c r="L158" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12">
       <c r="A159">
         <v>61010010</v>
       </c>
@@ -6567,16 +6582,16 @@
         <v>6910010</v>
       </c>
       <c r="G159" t="s">
-        <v>338</v>
-      </c>
-      <c r="J159">
+        <v>340</v>
+      </c>
+      <c r="K159">
         <v>61010010</v>
       </c>
-      <c r="K159" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11">
+      <c r="L159" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12">
       <c r="A160">
         <v>61010011</v>
       </c>
@@ -6596,16 +6611,16 @@
         <v>6910011</v>
       </c>
       <c r="G160" t="s">
-        <v>340</v>
-      </c>
-      <c r="J160">
+        <v>342</v>
+      </c>
+      <c r="K160">
         <v>61010011</v>
       </c>
-      <c r="K160" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11">
+      <c r="L160" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12">
       <c r="A161">
         <v>61010012</v>
       </c>
@@ -6625,16 +6640,16 @@
         <v>6910012</v>
       </c>
       <c r="G161" t="s">
-        <v>342</v>
-      </c>
-      <c r="J161">
+        <v>344</v>
+      </c>
+      <c r="K161">
         <v>61010012</v>
       </c>
-      <c r="K161" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11">
+      <c r="L161" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
       <c r="A162">
         <v>61010013</v>
       </c>
@@ -6654,19 +6669,19 @@
         <v>6910013</v>
       </c>
       <c r="G162" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I162" t="s">
-        <v>322</v>
-      </c>
-      <c r="J162">
+        <v>324</v>
+      </c>
+      <c r="K162">
         <v>61010013</v>
       </c>
-      <c r="K162" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11">
+      <c r="L162" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12">
       <c r="A163">
         <v>61010014</v>
       </c>
@@ -6686,19 +6701,19 @@
         <v>6910014</v>
       </c>
       <c r="G163" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I163" t="s">
-        <v>322</v>
-      </c>
-      <c r="J163">
+        <v>324</v>
+      </c>
+      <c r="K163">
         <v>61010014</v>
       </c>
-      <c r="K163" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11">
+      <c r="L163" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
       <c r="A164">
         <v>61010015</v>
       </c>
@@ -6718,19 +6733,19 @@
         <v>6910015</v>
       </c>
       <c r="G164" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I164" t="s">
-        <v>322</v>
-      </c>
-      <c r="J164">
+        <v>324</v>
+      </c>
+      <c r="K164">
         <v>61010015</v>
       </c>
-      <c r="K164" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11">
+      <c r="L164" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12">
       <c r="A165">
         <v>61010016</v>
       </c>
@@ -6750,19 +6765,19 @@
         <v>6910016</v>
       </c>
       <c r="G165" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I165" t="s">
-        <v>322</v>
-      </c>
-      <c r="J165">
+        <v>324</v>
+      </c>
+      <c r="K165">
         <v>61010016</v>
       </c>
-      <c r="K165" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11">
+      <c r="L165" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
       <c r="A166">
         <v>61010017</v>
       </c>
@@ -6782,16 +6797,16 @@
         <v>6910017</v>
       </c>
       <c r="G166" t="s">
-        <v>352</v>
-      </c>
-      <c r="J166">
+        <v>354</v>
+      </c>
+      <c r="K166">
         <v>61010017</v>
       </c>
-      <c r="K166" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11">
+      <c r="L166" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
       <c r="A167">
         <v>61010018</v>
       </c>
@@ -6811,16 +6826,16 @@
         <v>6910018</v>
       </c>
       <c r="G167" t="s">
-        <v>354</v>
-      </c>
-      <c r="J167">
+        <v>356</v>
+      </c>
+      <c r="K167">
         <v>61010018</v>
       </c>
-      <c r="K167" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11">
+      <c r="L167" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12">
       <c r="A168">
         <v>61010019</v>
       </c>
@@ -6840,16 +6855,16 @@
         <v>6910019</v>
       </c>
       <c r="G168" t="s">
-        <v>356</v>
-      </c>
-      <c r="J168">
+        <v>358</v>
+      </c>
+      <c r="K168">
         <v>61010019</v>
       </c>
-      <c r="K168" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11">
+      <c r="L168" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
       <c r="A169">
         <v>61010020</v>
       </c>
@@ -6869,16 +6884,16 @@
         <v>6910020</v>
       </c>
       <c r="G169" t="s">
-        <v>358</v>
-      </c>
-      <c r="J169">
+        <v>360</v>
+      </c>
+      <c r="K169">
         <v>61010020</v>
       </c>
-      <c r="K169" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11">
+      <c r="L169" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
       <c r="A170">
         <v>70100001</v>
       </c>
@@ -6895,16 +6910,16 @@
         <v>7500001</v>
       </c>
       <c r="G170" t="s">
-        <v>360</v>
-      </c>
-      <c r="J170">
+        <v>362</v>
+      </c>
+      <c r="K170">
         <v>70100001</v>
       </c>
-      <c r="K170" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11">
+      <c r="L170" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12">
       <c r="A171">
         <v>70200001</v>
       </c>
@@ -6921,16 +6936,16 @@
         <v>7510001</v>
       </c>
       <c r="G171" t="s">
-        <v>362</v>
-      </c>
-      <c r="J171">
+        <v>364</v>
+      </c>
+      <c r="K171">
         <v>70200001</v>
       </c>
-      <c r="K171" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11">
+      <c r="L171" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12">
       <c r="A172">
         <v>70200002</v>
       </c>
@@ -6947,16 +6962,16 @@
         <v>7510002</v>
       </c>
       <c r="G172" t="s">
-        <v>364</v>
-      </c>
-      <c r="J172">
+        <v>366</v>
+      </c>
+      <c r="K172">
         <v>70200002</v>
       </c>
-      <c r="K172" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11">
+      <c r="L172" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12">
       <c r="A173">
         <v>70300001</v>
       </c>
@@ -6973,16 +6988,16 @@
         <v>7520001</v>
       </c>
       <c r="G173" t="s">
-        <v>365</v>
-      </c>
-      <c r="J173">
+        <v>367</v>
+      </c>
+      <c r="K173">
         <v>70300001</v>
       </c>
-      <c r="K173" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11">
+      <c r="L173" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12">
       <c r="A174">
         <v>70300002</v>
       </c>
@@ -6999,16 +7014,16 @@
         <v>7520002</v>
       </c>
       <c r="G174" t="s">
-        <v>367</v>
-      </c>
-      <c r="J174">
+        <v>369</v>
+      </c>
+      <c r="K174">
         <v>70300002</v>
       </c>
-      <c r="K174" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11">
+      <c r="L174" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12">
       <c r="A175">
         <v>70300003</v>
       </c>
@@ -7025,16 +7040,16 @@
         <v>7520003</v>
       </c>
       <c r="G175" t="s">
-        <v>369</v>
-      </c>
-      <c r="J175">
+        <v>371</v>
+      </c>
+      <c r="K175">
         <v>70300003</v>
       </c>
-      <c r="K175" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11">
+      <c r="L175" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12">
       <c r="A176">
         <v>70300004</v>
       </c>
@@ -7051,16 +7066,16 @@
         <v>7520004</v>
       </c>
       <c r="G176" t="s">
-        <v>371</v>
-      </c>
-      <c r="J176">
+        <v>373</v>
+      </c>
+      <c r="K176">
         <v>70300004</v>
       </c>
-      <c r="K176" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11">
+      <c r="L176" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12">
       <c r="A177">
         <v>71000001</v>
       </c>
@@ -7080,19 +7095,19 @@
         <v>7900001</v>
       </c>
       <c r="G177" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I177" t="s">
-        <v>374</v>
-      </c>
-      <c r="J177">
+        <v>376</v>
+      </c>
+      <c r="K177">
         <v>71000001</v>
       </c>
-      <c r="K177" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11">
+      <c r="L177" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12">
       <c r="A178">
         <v>71000002</v>
       </c>
@@ -7112,19 +7127,19 @@
         <v>7900002</v>
       </c>
       <c r="G178" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I178" t="s">
-        <v>377</v>
-      </c>
-      <c r="J178">
+        <v>379</v>
+      </c>
+      <c r="K178">
         <v>71000002</v>
       </c>
-      <c r="K178" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11">
+      <c r="L178" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12">
       <c r="A179">
         <v>71000003</v>
       </c>
@@ -7144,19 +7159,19 @@
         <v>7900003</v>
       </c>
       <c r="G179" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I179" t="s">
-        <v>380</v>
-      </c>
-      <c r="J179">
+        <v>382</v>
+      </c>
+      <c r="K179">
         <v>71000003</v>
       </c>
-      <c r="K179" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11">
+      <c r="L179" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12">
       <c r="A180">
         <v>71010001</v>
       </c>
@@ -7176,16 +7191,16 @@
         <v>7910001</v>
       </c>
       <c r="G180" t="s">
-        <v>382</v>
-      </c>
-      <c r="J180">
+        <v>384</v>
+      </c>
+      <c r="K180">
         <v>71010001</v>
       </c>
-      <c r="K180" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11">
+      <c r="L180" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12">
       <c r="A181">
         <v>71010002</v>
       </c>
@@ -7205,16 +7220,16 @@
         <v>7910002</v>
       </c>
       <c r="G181" t="s">
-        <v>384</v>
-      </c>
-      <c r="J181">
+        <v>386</v>
+      </c>
+      <c r="K181">
         <v>71010002</v>
       </c>
-      <c r="K181" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11">
+      <c r="L181" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12">
       <c r="A182">
         <v>71010003</v>
       </c>
@@ -7234,16 +7249,16 @@
         <v>7910003</v>
       </c>
       <c r="G182" t="s">
-        <v>386</v>
-      </c>
-      <c r="J182">
+        <v>388</v>
+      </c>
+      <c r="K182">
         <v>71010003</v>
       </c>
-      <c r="K182" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11">
+      <c r="L182" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12">
       <c r="A183">
         <v>71010004</v>
       </c>
@@ -7263,16 +7278,16 @@
         <v>7910004</v>
       </c>
       <c r="G183" t="s">
-        <v>388</v>
-      </c>
-      <c r="J183">
+        <v>390</v>
+      </c>
+      <c r="K183">
         <v>71010004</v>
       </c>
-      <c r="K183" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11">
+      <c r="L183" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12">
       <c r="A184">
         <v>71010005</v>
       </c>
@@ -7292,16 +7307,16 @@
         <v>7910005</v>
       </c>
       <c r="G184" t="s">
-        <v>390</v>
-      </c>
-      <c r="J184">
+        <v>392</v>
+      </c>
+      <c r="K184">
         <v>71010005</v>
       </c>
-      <c r="K184" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11">
+      <c r="L184" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12">
       <c r="A185">
         <v>71010006</v>
       </c>
@@ -7321,17 +7336,17 @@
         <v>7910006</v>
       </c>
       <c r="G185" t="s">
-        <v>392</v>
-      </c>
-      <c r="J185">
+        <v>394</v>
+      </c>
+      <c r="K185">
         <v>71010006</v>
       </c>
-      <c r="K185" t="s">
-        <v>393</v>
+      <c r="L185" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A4:L88">
+  <sortState ref="A4:M88">
     <sortCondition ref="A4"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="ItemsInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="481">
   <si>
     <t>id</t>
   </si>
@@ -125,139 +125,400 @@
     <t>Human_Atlas_Hat_Hat_1</t>
   </si>
   <si>
-    <t>人类-帽子-铁头盔</t>
+    <t>钢头盔-------------------------------</t>
   </si>
   <si>
     <t>Human_Atlas_Hat_Hat_2</t>
   </si>
   <si>
-    <t>人类-帽子-钢头盔</t>
+    <t>大魔法师帽</t>
   </si>
   <si>
     <t>Human_Atlas_Hat_Hat_3</t>
   </si>
   <si>
-    <t>人类-帽子-战斗魔法师帽</t>
+    <t>铁头盔</t>
   </si>
   <si>
     <t>Human_Atlas_Hat_Hat_4</t>
   </si>
   <si>
-    <t>人类-帽子-射手兜帽</t>
+    <t>射手兜帽</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_5</t>
+  </si>
+  <si>
+    <t>魔法师帽</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_7</t>
+  </si>
+  <si>
+    <t>精英魔法师兜帽</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_8</t>
+  </si>
+  <si>
+    <t>暗杀者兜帽</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_10</t>
+  </si>
+  <si>
+    <t>骑士头盔</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_12</t>
+  </si>
+  <si>
+    <t>死灵师面具</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_13</t>
+  </si>
+  <si>
+    <t>金骑士头盔</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_14</t>
+  </si>
+  <si>
+    <t>勇者头盔</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_15</t>
+  </si>
+  <si>
+    <t>魔力帽</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_16</t>
+  </si>
+  <si>
+    <t>暗黑骑士头盔</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Hat_Hat_17</t>
+  </si>
+  <si>
+    <t>银色骑士头盔</t>
   </si>
   <si>
     <t>Human_Atlas_Clothes_Clothes_1</t>
   </si>
   <si>
-    <t>人类-衣服-战士上衣</t>
+    <t>钢盔甲上衣---------------------------</t>
   </si>
   <si>
     <t>Human_Atlas_Clothes_Clothes_2</t>
   </si>
   <si>
-    <t>人类-衣服-战斗魔法师上衣</t>
+    <t>大魔法师上衣</t>
   </si>
   <si>
     <t>Human_Atlas_Clothes_Clothes_3</t>
   </si>
   <si>
-    <t>人类-衣服-冒险者上衣</t>
+    <t>冒险者上衣</t>
   </si>
   <si>
     <t>Human_Atlas_Clothes_Clothes_4</t>
   </si>
   <si>
-    <t>人类-衣服-射手上衣</t>
+    <t>射手上衣</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_5</t>
+  </si>
+  <si>
+    <t>魔法师上衣</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_6</t>
+  </si>
+  <si>
+    <t>狩猎者上衣</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_7</t>
+  </si>
+  <si>
+    <t>精英魔法师上衣</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_8</t>
+  </si>
+  <si>
+    <t>暗杀者上衣</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_9</t>
+  </si>
+  <si>
+    <t>竞技者上衣</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_10</t>
+  </si>
+  <si>
+    <t>骑士盔甲</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_11</t>
+  </si>
+  <si>
+    <t>治疗师长袍</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_12</t>
+  </si>
+  <si>
+    <t>死灵师长袍</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_13</t>
+  </si>
+  <si>
+    <t>金骑士盔甲</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_14</t>
+  </si>
+  <si>
+    <t>勇者上衣</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_15</t>
+  </si>
+  <si>
+    <t>魔力法师上衣</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_16</t>
+  </si>
+  <si>
+    <t>暗黑骑士盔甲</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Clothes_Clothes_17</t>
+  </si>
+  <si>
+    <t>银色骑士盔甲</t>
   </si>
   <si>
     <t>Human_Atlas_Pants_Pants_1</t>
   </si>
   <si>
-    <t>人类-裤子-战士裤子</t>
+    <t>钢盔甲裤--------------------------</t>
   </si>
   <si>
     <t>Human_Atlas_Pants_Pants_2</t>
   </si>
   <si>
-    <t>人类-裤子-战斗魔法师裤子</t>
+    <t>大魔法师裤</t>
   </si>
   <si>
     <t>Human_Atlas_Pants_Pants_3</t>
   </si>
   <si>
-    <t>人类-裤子-冒险者裤子</t>
+    <t>冒险者裤子</t>
   </si>
   <si>
     <t>Human_Atlas_Pants_Pants_4</t>
   </si>
   <si>
-    <t>人类-裤子-射手裤子</t>
+    <t>射手裤子</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_5</t>
+  </si>
+  <si>
+    <t>魔法师裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_6</t>
+  </si>
+  <si>
+    <t>狩猎者裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_7</t>
+  </si>
+  <si>
+    <t>精英魔法师裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_8</t>
+  </si>
+  <si>
+    <t>暗杀者裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_9</t>
+  </si>
+  <si>
+    <t>竞技者裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_10</t>
+  </si>
+  <si>
+    <t>骑士裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_11</t>
+  </si>
+  <si>
+    <t>治疗师裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_12</t>
+  </si>
+  <si>
+    <t>死灵师裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_13</t>
+  </si>
+  <si>
+    <t>金骑士裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_14</t>
+  </si>
+  <si>
+    <t>勇者裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_15</t>
+  </si>
+  <si>
+    <t>魔力法师裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_16</t>
+  </si>
+  <si>
+    <t>暗黑骑士裤</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Pants_Pants_17</t>
+  </si>
+  <si>
+    <t>银色骑士裤</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_L_1</t>
   </si>
   <si>
-    <t>人类-武器-钢剑</t>
+    <t>钢剑----------------------------</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_L_2</t>
   </si>
   <si>
-    <t>人类-武器-铁剑</t>
+    <t>铁剑</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_L_3</t>
   </si>
   <si>
-    <t>人类-武器-火法杖</t>
+    <t>火法杖</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_L_4</t>
   </si>
   <si>
-    <t>人类-武器-冰法杖</t>
+    <t>冰法杖</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_L_5</t>
   </si>
   <si>
-    <t>人类-武器-残破剑</t>
+    <t>残破剑</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_L_6</t>
   </si>
   <si>
-    <t>人类-武器-短刀</t>
+    <t>短刀</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_L_7</t>
   </si>
   <si>
-    <t>人类-武器-绿宝石法杖</t>
+    <t>绿宝石法杖</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_L_8</t>
   </si>
   <si>
-    <t>人类-武器-魔力法杖</t>
+    <t>魔力法杖</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_L_9</t>
   </si>
   <si>
-    <t>人类-武器-星之法杖</t>
+    <t>星之法杖</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Weapon_Weapon_L_10</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Weapon_Weapon_L_11</t>
+  </si>
+  <si>
+    <t>电法杖</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Weapon_Weapon_L_12</t>
+  </si>
+  <si>
+    <t>大剑</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Weapon_Weapon_L_13</t>
+  </si>
+  <si>
+    <t>死灵法杖</t>
   </si>
   <si>
     <t>Human_Atlas_Weapon_Weapon_R_1</t>
   </si>
   <si>
-    <t>人类-武器-木弓</t>
+    <t>木弓</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Weapon_Weapon_R_2</t>
+  </si>
+  <si>
+    <t>钢弓</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Weapon_Weapon_R_3</t>
+  </si>
+  <si>
+    <t>红木弓</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Weapon_Weapon_LR_21</t>
+  </si>
+  <si>
+    <t>冒险者盾剑</t>
+  </si>
+  <si>
+    <t>Human_Atlas_Weapon_Weapon_LR_22</t>
+  </si>
+  <si>
+    <t>勇者盾剑</t>
   </si>
   <si>
     <t>Skeleton_Atlas_Hat_Hat_1</t>
   </si>
   <si>
-    <t>骷髅-帽子-皇冠</t>
+    <t>骷髅-帽子-皇冠-------------------</t>
   </si>
   <si>
     <t>Skeleton_Atlas_Hat_Hat_2</t>
@@ -1004,9 +1265,6 @@
     <t>ShowSprite:Goblin_Atlas_Other_Arrow_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
   </si>
   <si>
-    <t>木弓</t>
-  </si>
-  <si>
     <t>Goblin_Atlas_Weapon_Weapon_R_3</t>
   </si>
   <si>
@@ -1044,9 +1302,6 @@
   </si>
   <si>
     <t>Goblin_Atlas_Weapon_Weapon_R_9</t>
-  </si>
-  <si>
-    <t>铁剑</t>
   </si>
   <si>
     <t>Goblin_Atlas_Weapon_Weapon_R_10</t>
@@ -1830,8 +2085,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2182,18 +2440,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L185"/>
+  <dimension ref="A1:L229"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="70.875" customWidth="1"/>
-    <col min="3" max="3" width="22.25" customWidth="1"/>
-    <col min="4" max="4" width="18.625" customWidth="1"/>
-    <col min="5" max="5" width="30.5" customWidth="1"/>
+    <col min="2" max="2" width="64.375" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
+    <col min="4" max="4" width="8.875" customWidth="1"/>
+    <col min="5" max="5" width="19.375" customWidth="1"/>
     <col min="6" max="6" width="24.875" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="31.75" customWidth="1"/>
-    <col min="9" max="10" width="110.375" customWidth="1"/>
+    <col min="8" max="8" width="14.875" customWidth="1"/>
+    <col min="9" max="9" width="20.375" customWidth="1"/>
+    <col min="10" max="10" width="14.875" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="12" width="42.875" customWidth="1"/>
   </cols>
@@ -2383,7 +2642,7 @@
       <c r="K6">
         <v>10100001</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2409,7 +2668,7 @@
       <c r="K7">
         <v>10100002</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2435,7 +2694,7 @@
       <c r="K8">
         <v>10100003</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2461,16 +2720,16 @@
       <c r="K9">
         <v>10100004</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:12">
       <c r="A10">
-        <v>10200001</v>
+        <v>10100005</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2479,24 +2738,24 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>1510001</v>
+        <v>1500005</v>
       </c>
       <c r="G10" t="s">
         <v>39</v>
       </c>
       <c r="K10">
-        <v>10200001</v>
-      </c>
-      <c r="L10" t="s">
+        <v>10100005</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:12">
       <c r="A11">
-        <v>10200002</v>
+        <v>10100007</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2505,24 +2764,24 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>1510002</v>
+        <v>1500007</v>
       </c>
       <c r="G11" t="s">
         <v>41</v>
       </c>
       <c r="K11">
-        <v>10200002</v>
-      </c>
-      <c r="L11" t="s">
+        <v>10100007</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:12">
       <c r="A12">
-        <v>10200003</v>
+        <v>10100008</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2531,24 +2790,24 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>1510003</v>
+        <v>1500008</v>
       </c>
       <c r="G12" t="s">
         <v>43</v>
       </c>
       <c r="K12">
-        <v>10200003</v>
-      </c>
-      <c r="L12" t="s">
+        <v>10100008</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:12">
       <c r="A13">
-        <v>10200004</v>
+        <v>10100010</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2557,24 +2816,24 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>1510004</v>
+        <v>1500010</v>
       </c>
       <c r="G13" t="s">
         <v>45</v>
       </c>
       <c r="K13">
-        <v>10200004</v>
-      </c>
-      <c r="L13" t="s">
+        <v>10100010</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:12">
       <c r="A14">
-        <v>10300001</v>
+        <v>10100012</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2583,24 +2842,24 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>1520001</v>
+        <v>1500012</v>
       </c>
       <c r="G14" t="s">
         <v>47</v>
       </c>
       <c r="K14">
-        <v>10300001</v>
-      </c>
-      <c r="L14" t="s">
+        <v>10100012</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:12">
       <c r="A15">
-        <v>10300002</v>
+        <v>10100013</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2609,24 +2868,24 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>1520002</v>
+        <v>1500013</v>
       </c>
       <c r="G15" t="s">
         <v>49</v>
       </c>
       <c r="K15">
-        <v>10300002</v>
-      </c>
-      <c r="L15" t="s">
+        <v>10100013</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:12">
       <c r="A16">
-        <v>10300003</v>
+        <v>10100014</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2635,24 +2894,24 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>1520003</v>
+        <v>1500014</v>
       </c>
       <c r="G16" t="s">
         <v>51</v>
       </c>
       <c r="K16">
-        <v>10300003</v>
-      </c>
-      <c r="L16" t="s">
+        <v>10100014</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="1:12">
       <c r="A17">
-        <v>10300004</v>
+        <v>10100015</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2661,27 +2920,24 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>1520004</v>
+        <v>1500015</v>
       </c>
       <c r="G17" t="s">
         <v>53</v>
       </c>
       <c r="K17">
-        <v>10300004</v>
-      </c>
-      <c r="L17" t="s">
+        <v>10100015</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:12">
       <c r="A18">
-        <v>11000001</v>
+        <v>10100016</v>
       </c>
       <c r="B18">
-        <v>10</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2690,27 +2946,24 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>1900001</v>
+        <v>1500016</v>
       </c>
       <c r="G18" t="s">
         <v>55</v>
       </c>
       <c r="K18">
-        <v>11000001</v>
-      </c>
-      <c r="L18" t="s">
+        <v>10100016</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:12">
       <c r="A19">
-        <v>11000002</v>
+        <v>10100017</v>
       </c>
       <c r="B19">
-        <v>10</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2719,27 +2972,24 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>1900002</v>
+        <v>1500017</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
       </c>
       <c r="K19">
-        <v>11000002</v>
-      </c>
-      <c r="L19" t="s">
+        <v>10100017</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:12">
       <c r="A20">
-        <v>11000003</v>
+        <v>10200001</v>
       </c>
       <c r="B20">
-        <v>10</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2748,13 +2998,13 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>1900003</v>
+        <v>1510001</v>
       </c>
       <c r="G20" t="s">
         <v>59</v>
       </c>
       <c r="K20">
-        <v>11000003</v>
+        <v>10200001</v>
       </c>
       <c r="L20" t="s">
         <v>60</v>
@@ -2762,13 +3012,10 @@
     </row>
     <row r="21" customFormat="1" spans="1:12">
       <c r="A21">
-        <v>11000004</v>
+        <v>10200002</v>
       </c>
       <c r="B21">
-        <v>10</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2777,13 +3024,13 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>1900004</v>
+        <v>1510002</v>
       </c>
       <c r="G21" t="s">
         <v>61</v>
       </c>
       <c r="K21">
-        <v>11000004</v>
+        <v>10200002</v>
       </c>
       <c r="L21" t="s">
         <v>62</v>
@@ -2791,12 +3038,9 @@
     </row>
     <row r="22" customFormat="1" spans="1:12">
       <c r="A22">
-        <v>11000005</v>
+        <v>10200003</v>
       </c>
       <c r="B22">
-        <v>10</v>
-      </c>
-      <c r="C22">
         <v>2</v>
       </c>
       <c r="D22">
@@ -2806,13 +3050,13 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>1900005</v>
+        <v>1510003</v>
       </c>
       <c r="G22" t="s">
         <v>63</v>
       </c>
       <c r="K22">
-        <v>11000005</v>
+        <v>10200003</v>
       </c>
       <c r="L22" t="s">
         <v>64</v>
@@ -2820,12 +3064,9 @@
     </row>
     <row r="23" customFormat="1" spans="1:12">
       <c r="A23">
-        <v>11000006</v>
+        <v>10200004</v>
       </c>
       <c r="B23">
-        <v>10</v>
-      </c>
-      <c r="C23">
         <v>2</v>
       </c>
       <c r="D23">
@@ -2835,13 +3076,13 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>1900006</v>
+        <v>1510004</v>
       </c>
       <c r="G23" t="s">
         <v>65</v>
       </c>
       <c r="K23">
-        <v>11000006</v>
+        <v>10200004</v>
       </c>
       <c r="L23" t="s">
         <v>66</v>
@@ -2849,13 +3090,10 @@
     </row>
     <row r="24" customFormat="1" spans="1:12">
       <c r="A24">
-        <v>11000007</v>
+        <v>10200005</v>
       </c>
       <c r="B24">
-        <v>10</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2864,13 +3102,13 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>1900007</v>
+        <v>1510005</v>
       </c>
       <c r="G24" t="s">
         <v>67</v>
       </c>
       <c r="K24">
-        <v>11000007</v>
+        <v>10200005</v>
       </c>
       <c r="L24" t="s">
         <v>68</v>
@@ -2878,13 +3116,10 @@
     </row>
     <row r="25" customFormat="1" spans="1:12">
       <c r="A25">
-        <v>11000008</v>
+        <v>10200006</v>
       </c>
       <c r="B25">
-        <v>10</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2893,13 +3128,13 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>1900008</v>
+        <v>1510006</v>
       </c>
       <c r="G25" t="s">
         <v>69</v>
       </c>
       <c r="K25">
-        <v>11000008</v>
+        <v>10200006</v>
       </c>
       <c r="L25" t="s">
         <v>70</v>
@@ -2907,13 +3142,10 @@
     </row>
     <row r="26" customFormat="1" spans="1:12">
       <c r="A26">
-        <v>11000009</v>
+        <v>10200007</v>
       </c>
       <c r="B26">
-        <v>10</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2922,13 +3154,13 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>1900009</v>
+        <v>1510007</v>
       </c>
       <c r="G26" t="s">
         <v>71</v>
       </c>
       <c r="K26">
-        <v>11000009</v>
+        <v>10200007</v>
       </c>
       <c r="L26" t="s">
         <v>72</v>
@@ -2936,13 +3168,10 @@
     </row>
     <row r="27" customFormat="1" spans="1:12">
       <c r="A27">
-        <v>11010001</v>
+        <v>10200008</v>
       </c>
       <c r="B27">
-        <v>10</v>
-      </c>
-      <c r="C27">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2951,203 +3180,203 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>1910001</v>
+        <v>1510008</v>
       </c>
       <c r="G27" t="s">
         <v>73</v>
       </c>
       <c r="K27">
-        <v>11010001</v>
+        <v>10200008</v>
       </c>
       <c r="L27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" customFormat="1" spans="1:12">
       <c r="A28">
-        <v>20100001</v>
+        <v>10200009</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>2500001</v>
+        <v>1510009</v>
       </c>
       <c r="G28" t="s">
         <v>75</v>
       </c>
       <c r="K28">
-        <v>20100001</v>
+        <v>10200009</v>
       </c>
       <c r="L28" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" customFormat="1" spans="1:12">
       <c r="A29">
-        <v>20100002</v>
+        <v>10200010</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>2500002</v>
+        <v>1510010</v>
       </c>
       <c r="G29" t="s">
         <v>77</v>
       </c>
       <c r="K29">
-        <v>20100002</v>
+        <v>10200010</v>
       </c>
       <c r="L29" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" customFormat="1" spans="1:12">
       <c r="A30">
-        <v>20100003</v>
+        <v>10200011</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>2500003</v>
+        <v>1510011</v>
       </c>
       <c r="G30" t="s">
         <v>79</v>
       </c>
       <c r="K30">
-        <v>20100003</v>
+        <v>10200011</v>
       </c>
       <c r="L30" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" customFormat="1" spans="1:12">
       <c r="A31">
-        <v>20100004</v>
+        <v>10200012</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>2500004</v>
+        <v>1510012</v>
       </c>
       <c r="G31" t="s">
         <v>81</v>
       </c>
       <c r="K31">
-        <v>20100004</v>
+        <v>10200012</v>
       </c>
       <c r="L31" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" customFormat="1" spans="1:12">
       <c r="A32">
-        <v>20100005</v>
+        <v>10200013</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>2500005</v>
+        <v>1510013</v>
       </c>
       <c r="G32" t="s">
         <v>83</v>
       </c>
       <c r="K32">
-        <v>20100005</v>
+        <v>10200013</v>
       </c>
       <c r="L32" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" customFormat="1" spans="1:12">
       <c r="A33">
-        <v>20100006</v>
+        <v>10200014</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>2500006</v>
+        <v>1510014</v>
       </c>
       <c r="G33" t="s">
         <v>85</v>
       </c>
       <c r="K33">
-        <v>20100006</v>
+        <v>10200014</v>
       </c>
       <c r="L33" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" customFormat="1" spans="1:12">
       <c r="A34">
-        <v>20100007</v>
+        <v>10200015</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>2500007</v>
+        <v>1510015</v>
       </c>
       <c r="G34" t="s">
         <v>87</v>
       </c>
       <c r="K34">
-        <v>20100007</v>
+        <v>10200015</v>
       </c>
       <c r="L34" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" customFormat="1" spans="1:12">
       <c r="A35">
-        <v>20200001</v>
+        <v>10200016</v>
       </c>
       <c r="B35">
         <v>2</v>
@@ -3156,24 +3385,24 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>2510001</v>
+        <v>1510016</v>
       </c>
       <c r="G35" t="s">
         <v>89</v>
       </c>
       <c r="K35">
-        <v>20200001</v>
+        <v>10200016</v>
       </c>
       <c r="L35" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" customFormat="1" spans="1:12">
       <c r="A36">
-        <v>20200002</v>
+        <v>10200017</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -3182,16 +3411,16 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>2510002</v>
+        <v>1510017</v>
       </c>
       <c r="G36" t="s">
         <v>91</v>
       </c>
       <c r="K36">
-        <v>20200002</v>
+        <v>10200017</v>
       </c>
       <c r="L36" t="s">
         <v>92</v>
@@ -3199,241 +3428,241 @@
     </row>
     <row r="37" customFormat="1" spans="1:12">
       <c r="A37">
-        <v>20200003</v>
+        <v>10300001</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>2510003</v>
+        <v>1520001</v>
       </c>
       <c r="G37" t="s">
         <v>93</v>
       </c>
       <c r="K37">
-        <v>20200003</v>
+        <v>10300001</v>
       </c>
       <c r="L37" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" customFormat="1" spans="1:12">
       <c r="A38">
-        <v>20200004</v>
+        <v>10300002</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>2510004</v>
+        <v>1520002</v>
       </c>
       <c r="G38" t="s">
         <v>95</v>
       </c>
       <c r="K38">
-        <v>20200004</v>
+        <v>10300002</v>
       </c>
       <c r="L38" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" customFormat="1" spans="1:12">
       <c r="A39">
-        <v>20200005</v>
+        <v>10300003</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>2510005</v>
+        <v>1520003</v>
       </c>
       <c r="G39" t="s">
         <v>97</v>
       </c>
       <c r="K39">
-        <v>20200005</v>
+        <v>10300003</v>
       </c>
       <c r="L39" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" customFormat="1" spans="1:12">
       <c r="A40">
-        <v>20200006</v>
+        <v>10300004</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>2510006</v>
+        <v>1520004</v>
       </c>
       <c r="G40" t="s">
         <v>99</v>
       </c>
       <c r="K40">
-        <v>20200006</v>
+        <v>10300004</v>
       </c>
       <c r="L40" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" customFormat="1" spans="1:12">
       <c r="A41">
-        <v>20200007</v>
+        <v>10300005</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>2510007</v>
+        <v>1520005</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
       </c>
       <c r="K41">
-        <v>20200007</v>
+        <v>10300005</v>
       </c>
       <c r="L41" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" customFormat="1" spans="1:12">
       <c r="A42">
-        <v>20200008</v>
+        <v>10300006</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>2510008</v>
+        <v>1520006</v>
       </c>
       <c r="G42" t="s">
         <v>103</v>
       </c>
       <c r="K42">
-        <v>20200008</v>
+        <v>10300006</v>
       </c>
       <c r="L42" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" customFormat="1" spans="1:12">
       <c r="A43">
-        <v>20200009</v>
+        <v>10300007</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>2510009</v>
+        <v>1520007</v>
       </c>
       <c r="G43" t="s">
         <v>105</v>
       </c>
       <c r="K43">
-        <v>20200009</v>
+        <v>10300007</v>
       </c>
       <c r="L43" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" customFormat="1" spans="1:12">
       <c r="A44">
-        <v>20200010</v>
+        <v>10300008</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>2510010</v>
+        <v>1520008</v>
       </c>
       <c r="G44" t="s">
         <v>107</v>
       </c>
       <c r="K44">
-        <v>20200010</v>
+        <v>10300008</v>
       </c>
       <c r="L44" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" customFormat="1" spans="1:12">
       <c r="A45">
-        <v>20200011</v>
+        <v>10300009</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>2510011</v>
+        <v>1520009</v>
       </c>
       <c r="G45" t="s">
         <v>109</v>
       </c>
       <c r="K45">
-        <v>20200011</v>
+        <v>10300009</v>
       </c>
       <c r="L45" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" customFormat="1" spans="1:12">
       <c r="A46">
-        <v>20300001</v>
+        <v>10300010</v>
       </c>
       <c r="B46">
         <v>3</v>
@@ -3442,24 +3671,24 @@
         <v>1</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>2520001</v>
+        <v>1520010</v>
       </c>
       <c r="G46" t="s">
         <v>111</v>
       </c>
       <c r="K46">
-        <v>20300001</v>
+        <v>10300010</v>
       </c>
       <c r="L46" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" customFormat="1" spans="1:12">
       <c r="A47">
-        <v>20300002</v>
+        <v>10300011</v>
       </c>
       <c r="B47">
         <v>3</v>
@@ -3468,24 +3697,24 @@
         <v>1</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>2520002</v>
+        <v>1520011</v>
       </c>
       <c r="G47" t="s">
         <v>113</v>
       </c>
       <c r="K47">
-        <v>20300002</v>
+        <v>10300011</v>
       </c>
       <c r="L47" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" customFormat="1" spans="1:12">
       <c r="A48">
-        <v>20300003</v>
+        <v>10300012</v>
       </c>
       <c r="B48">
         <v>3</v>
@@ -3494,24 +3723,24 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>2520003</v>
+        <v>1520012</v>
       </c>
       <c r="G48" t="s">
         <v>115</v>
       </c>
       <c r="K48">
-        <v>20300003</v>
+        <v>10300012</v>
       </c>
       <c r="L48" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" customFormat="1" spans="1:12">
       <c r="A49">
-        <v>20300004</v>
+        <v>10300013</v>
       </c>
       <c r="B49">
         <v>3</v>
@@ -3520,24 +3749,24 @@
         <v>1</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>2520004</v>
+        <v>1520013</v>
       </c>
       <c r="G49" t="s">
         <v>117</v>
       </c>
       <c r="K49">
-        <v>20300004</v>
+        <v>10300013</v>
       </c>
       <c r="L49" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" customFormat="1" spans="1:12">
       <c r="A50">
-        <v>20300005</v>
+        <v>10300014</v>
       </c>
       <c r="B50">
         <v>3</v>
@@ -3546,358 +3775,334 @@
         <v>1</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>2520005</v>
+        <v>1520014</v>
       </c>
       <c r="G50" t="s">
         <v>119</v>
       </c>
       <c r="K50">
-        <v>20300005</v>
+        <v>10300014</v>
       </c>
       <c r="L50" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="51" ht="12" customHeight="1" spans="1:12">
+    <row r="51" customFormat="1" spans="1:12">
       <c r="A51">
-        <v>21000001</v>
+        <v>10300015</v>
       </c>
       <c r="B51">
-        <v>10</v>
-      </c>
-      <c r="C51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>2900001</v>
+        <v>1520015</v>
       </c>
       <c r="G51" t="s">
         <v>121</v>
       </c>
-      <c r="H51">
-        <v>45</v>
-      </c>
-      <c r="I51" t="s">
+      <c r="K51">
+        <v>10300015</v>
+      </c>
+      <c r="L51" t="s">
         <v>122</v>
       </c>
-      <c r="K51">
-        <v>21000001</v>
-      </c>
-      <c r="L51" t="s">
+    </row>
+    <row r="52" customFormat="1" spans="1:12">
+      <c r="A52">
+        <v>10300016</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>1520016</v>
+      </c>
+      <c r="G52" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52">
-        <v>21000002</v>
-      </c>
-      <c r="B52">
-        <v>10</v>
-      </c>
-      <c r="C52">
-        <v>8</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
-        <v>2</v>
-      </c>
-      <c r="F52">
-        <v>2900002</v>
-      </c>
-      <c r="G52" t="s">
+      <c r="K52">
+        <v>10300016</v>
+      </c>
+      <c r="L52" t="s">
         <v>124</v>
       </c>
-      <c r="H52">
-        <v>45</v>
-      </c>
-      <c r="I52" t="s">
+    </row>
+    <row r="53" customFormat="1" spans="1:12">
+      <c r="A53">
+        <v>10300017</v>
+      </c>
+      <c r="B53">
+        <v>3</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>1520017</v>
+      </c>
+      <c r="G53" t="s">
         <v>125</v>
       </c>
-      <c r="K52">
-        <v>21000002</v>
-      </c>
-      <c r="L52" t="s">
+      <c r="K53">
+        <v>10300017</v>
+      </c>
+      <c r="L53" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
-      <c r="A53">
-        <v>21000003</v>
-      </c>
-      <c r="B53">
-        <v>10</v>
-      </c>
-      <c r="C53">
-        <v>8</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53">
-        <v>2</v>
-      </c>
-      <c r="F53">
-        <v>2900003</v>
-      </c>
-      <c r="G53" t="s">
-        <v>127</v>
-      </c>
-      <c r="K53">
-        <v>21000003</v>
-      </c>
-      <c r="L53" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
+    <row r="54" customFormat="1" spans="1:12">
       <c r="A54">
-        <v>21000004</v>
+        <v>11000001</v>
       </c>
       <c r="B54">
         <v>10</v>
       </c>
       <c r="C54">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>2900004</v>
+        <v>1900001</v>
       </c>
       <c r="G54" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K54">
-        <v>21000004</v>
-      </c>
-      <c r="L54" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12">
+        <v>11000001</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:12">
       <c r="A55">
-        <v>21000005</v>
+        <v>11000002</v>
       </c>
       <c r="B55">
         <v>10</v>
       </c>
       <c r="C55">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>2900005</v>
+        <v>1900002</v>
       </c>
       <c r="G55" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K55">
-        <v>21000005</v>
-      </c>
-      <c r="L55" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12">
+        <v>11000002</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:12">
       <c r="A56">
-        <v>21000006</v>
+        <v>11000003</v>
       </c>
       <c r="B56">
         <v>10</v>
       </c>
       <c r="C56">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>2900006</v>
+        <v>1900003</v>
       </c>
       <c r="G56" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K56">
-        <v>21000006</v>
-      </c>
-      <c r="L56" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12">
+        <v>11000003</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:12">
       <c r="A57">
-        <v>21000007</v>
+        <v>11000004</v>
       </c>
       <c r="B57">
         <v>10</v>
       </c>
       <c r="C57">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>2900007</v>
+        <v>1900004</v>
       </c>
       <c r="G57" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K57">
-        <v>21000007</v>
-      </c>
-      <c r="L57" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
+        <v>11000004</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:12">
       <c r="A58">
-        <v>21000008</v>
+        <v>11000005</v>
       </c>
       <c r="B58">
         <v>10</v>
       </c>
       <c r="C58">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>2900008</v>
+        <v>1900005</v>
       </c>
       <c r="G58" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K58">
-        <v>21000008</v>
-      </c>
-      <c r="L58" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12">
+        <v>11000005</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:12">
       <c r="A59">
-        <v>21000009</v>
+        <v>11000006</v>
       </c>
       <c r="B59">
         <v>10</v>
       </c>
       <c r="C59">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>2900009</v>
+        <v>1900006</v>
       </c>
       <c r="G59" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K59">
-        <v>21000009</v>
-      </c>
-      <c r="L59" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12">
+        <v>11000006</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:12">
       <c r="A60">
-        <v>21000010</v>
+        <v>11000007</v>
       </c>
       <c r="B60">
         <v>10</v>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>2900010</v>
+        <v>1900007</v>
       </c>
       <c r="G60" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K60">
-        <v>21000010</v>
-      </c>
-      <c r="L60" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12">
+        <v>11000007</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:12">
       <c r="A61">
-        <v>21010001</v>
+        <v>11000008</v>
       </c>
       <c r="B61">
         <v>10</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>1</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>2910001</v>
+        <v>1900008</v>
       </c>
       <c r="G61" t="s">
-        <v>143</v>
-      </c>
-      <c r="H61">
-        <v>-45</v>
+        <v>141</v>
       </c>
       <c r="K61">
-        <v>21010001</v>
-      </c>
-      <c r="L61" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12">
+        <v>11000008</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:12">
       <c r="A62">
-        <v>21010002</v>
+        <v>11000009</v>
       </c>
       <c r="B62">
         <v>10</v>
@@ -3909,27 +4114,24 @@
         <v>1</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>2910002</v>
+        <v>1900009</v>
       </c>
       <c r="G62" t="s">
-        <v>145</v>
-      </c>
-      <c r="H62">
-        <v>-45</v>
+        <v>143</v>
       </c>
       <c r="K62">
-        <v>21010002</v>
-      </c>
-      <c r="L62" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12">
+        <v>11000009</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:12">
       <c r="A63">
-        <v>21010003</v>
+        <v>11000010</v>
       </c>
       <c r="B63">
         <v>10</v>
@@ -3941,270 +4143,258 @@
         <v>1</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>2910003</v>
+        <v>1900010</v>
       </c>
       <c r="G63" t="s">
-        <v>147</v>
-      </c>
-      <c r="H63">
-        <v>-45</v>
+        <v>145</v>
       </c>
       <c r="K63">
-        <v>21010003</v>
-      </c>
-      <c r="L63" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12">
+        <v>11000010</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:12">
       <c r="A64">
-        <v>21010004</v>
+        <v>11000011</v>
       </c>
       <c r="B64">
         <v>10</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>1</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>2910004</v>
+        <v>1900011</v>
       </c>
       <c r="G64" t="s">
-        <v>149</v>
-      </c>
-      <c r="H64">
-        <v>-45</v>
+        <v>146</v>
       </c>
       <c r="K64">
-        <v>21010004</v>
+        <v>11000011</v>
       </c>
       <c r="L64" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:12">
       <c r="A65">
-        <v>21010005</v>
+        <v>11000012</v>
       </c>
       <c r="B65">
         <v>10</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>2910005</v>
+        <v>1900012</v>
       </c>
       <c r="G65" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K65">
-        <v>21010005</v>
+        <v>11000012</v>
       </c>
       <c r="L65" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:12">
       <c r="A66">
-        <v>21010006</v>
+        <v>11000013</v>
       </c>
       <c r="B66">
         <v>10</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>2910006</v>
+        <v>1900013</v>
       </c>
       <c r="G66" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K66">
-        <v>21010006</v>
+        <v>11000013</v>
       </c>
       <c r="L66" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:12">
       <c r="A67">
-        <v>21010007</v>
+        <v>11010001</v>
       </c>
       <c r="B67">
         <v>10</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>2910007</v>
+        <v>1910001</v>
       </c>
       <c r="G67" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K67">
-        <v>21010007</v>
-      </c>
-      <c r="L67" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12">
+        <v>11010001</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="1:12">
       <c r="A68">
-        <v>21010008</v>
+        <v>11010002</v>
       </c>
       <c r="B68">
         <v>10</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>1</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>2910008</v>
+        <v>1910002</v>
       </c>
       <c r="G68" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K68">
-        <v>21010008</v>
-      </c>
-      <c r="L68" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12">
+        <v>11010002</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="1:12">
       <c r="A69">
-        <v>21010009</v>
+        <v>11010003</v>
       </c>
       <c r="B69">
         <v>10</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69">
-        <v>2910009</v>
+        <v>1910003</v>
       </c>
       <c r="G69" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K69">
-        <v>21010009</v>
-      </c>
-      <c r="L69" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12">
+        <v>11010003</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:12">
       <c r="A70">
-        <v>21010010</v>
+        <v>11020021</v>
       </c>
       <c r="B70">
         <v>10</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <v>1</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70">
-        <v>2910010</v>
+        <v>1920021</v>
       </c>
       <c r="G70" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K70">
-        <v>21010010</v>
-      </c>
-      <c r="L70" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12">
+        <v>11020021</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:12">
       <c r="A71">
-        <v>21010011</v>
+        <v>11020022</v>
       </c>
       <c r="B71">
         <v>10</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71">
-        <v>2910011</v>
+        <v>1920022</v>
       </c>
       <c r="G71" t="s">
-        <v>163</v>
-      </c>
-      <c r="H71">
-        <v>-45</v>
+        <v>160</v>
       </c>
       <c r="K71">
-        <v>21010011</v>
-      </c>
-      <c r="L71" t="s">
-        <v>164</v>
+        <v>11020022</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72">
-        <v>21010012</v>
+        <v>20100001</v>
       </c>
       <c r="B72">
-        <v>10</v>
-      </c>
-      <c r="C72">
         <v>1</v>
       </c>
       <c r="D72">
@@ -4214,29 +4404,23 @@
         <v>2</v>
       </c>
       <c r="F72">
-        <v>2910012</v>
+        <v>2500001</v>
       </c>
       <c r="G72" t="s">
-        <v>165</v>
-      </c>
-      <c r="H72">
-        <v>-45</v>
+        <v>162</v>
       </c>
       <c r="K72">
-        <v>21010012</v>
+        <v>20100001</v>
       </c>
       <c r="L72" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73">
-        <v>21010013</v>
+        <v>20100002</v>
       </c>
       <c r="B73">
-        <v>10</v>
-      </c>
-      <c r="C73">
         <v>1</v>
       </c>
       <c r="D73">
@@ -4246,26 +4430,23 @@
         <v>2</v>
       </c>
       <c r="F73">
-        <v>2910013</v>
+        <v>2500002</v>
       </c>
       <c r="G73" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K73">
-        <v>21010013</v>
+        <v>20100002</v>
       </c>
       <c r="L73" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74">
-        <v>21010014</v>
+        <v>20100003</v>
       </c>
       <c r="B74">
-        <v>10</v>
-      </c>
-      <c r="C74">
         <v>1</v>
       </c>
       <c r="D74">
@@ -4275,26 +4456,23 @@
         <v>2</v>
       </c>
       <c r="F74">
-        <v>2910014</v>
+        <v>2500003</v>
       </c>
       <c r="G74" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K74">
-        <v>21010014</v>
+        <v>20100003</v>
       </c>
       <c r="L74" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75">
-        <v>21010015</v>
+        <v>20100004</v>
       </c>
       <c r="B75">
-        <v>10</v>
-      </c>
-      <c r="C75">
         <v>1</v>
       </c>
       <c r="D75">
@@ -4304,26 +4482,23 @@
         <v>2</v>
       </c>
       <c r="F75">
-        <v>2910015</v>
+        <v>2500004</v>
       </c>
       <c r="G75" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K75">
-        <v>21010015</v>
+        <v>20100004</v>
       </c>
       <c r="L75" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76">
-        <v>21010016</v>
+        <v>20100005</v>
       </c>
       <c r="B76">
-        <v>10</v>
-      </c>
-      <c r="C76">
         <v>1</v>
       </c>
       <c r="D76">
@@ -4333,26 +4508,23 @@
         <v>2</v>
       </c>
       <c r="F76">
-        <v>2910016</v>
+        <v>2500005</v>
       </c>
       <c r="G76" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K76">
-        <v>21010016</v>
+        <v>20100005</v>
       </c>
       <c r="L76" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77">
-        <v>21010017</v>
+        <v>20100006</v>
       </c>
       <c r="B77">
-        <v>10</v>
-      </c>
-      <c r="C77">
         <v>1</v>
       </c>
       <c r="D77">
@@ -4362,26 +4534,23 @@
         <v>2</v>
       </c>
       <c r="F77">
-        <v>2910017</v>
+        <v>2500006</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K77">
-        <v>21010017</v>
+        <v>20100006</v>
       </c>
       <c r="L77" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78">
-        <v>21010018</v>
+        <v>20100007</v>
       </c>
       <c r="B78">
-        <v>10</v>
-      </c>
-      <c r="C78">
         <v>1</v>
       </c>
       <c r="D78">
@@ -4391,27 +4560,24 @@
         <v>2</v>
       </c>
       <c r="F78">
-        <v>2910018</v>
+        <v>2500007</v>
       </c>
       <c r="G78" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K78">
-        <v>21010018</v>
+        <v>20100007</v>
       </c>
       <c r="L78" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79">
-        <v>21010019</v>
+        <v>20200001</v>
       </c>
       <c r="B79">
-        <v>10</v>
-      </c>
-      <c r="C79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -4420,27 +4586,24 @@
         <v>2</v>
       </c>
       <c r="F79">
-        <v>2910019</v>
+        <v>2510001</v>
       </c>
       <c r="G79" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K79">
-        <v>21010019</v>
+        <v>20200001</v>
       </c>
       <c r="L79" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80">
-        <v>21010020</v>
+        <v>20200002</v>
       </c>
       <c r="B80">
-        <v>10</v>
-      </c>
-      <c r="C80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -4449,827 +4612,902 @@
         <v>2</v>
       </c>
       <c r="F80">
-        <v>2910020</v>
+        <v>2510002</v>
       </c>
       <c r="G80" t="s">
+        <v>178</v>
+      </c>
+      <c r="K80">
+        <v>20200002</v>
+      </c>
+      <c r="L80" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" spans="1:12">
+      <c r="A81">
+        <v>20200003</v>
+      </c>
+      <c r="B81">
+        <v>2</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="F81">
+        <v>2510003</v>
+      </c>
+      <c r="G81" t="s">
+        <v>180</v>
+      </c>
+      <c r="K81">
+        <v>20200003</v>
+      </c>
+      <c r="L81" t="s">
         <v>181</v>
-      </c>
-      <c r="K80">
-        <v>21010020</v>
-      </c>
-      <c r="L80" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="A81">
-        <v>30100001</v>
-      </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="D81">
-        <v>1</v>
-      </c>
-      <c r="E81">
-        <v>3</v>
-      </c>
-      <c r="F81">
-        <v>3020001</v>
-      </c>
-      <c r="G81" t="s">
-        <v>183</v>
-      </c>
-      <c r="K81">
-        <v>30100001</v>
-      </c>
-      <c r="L81" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82">
-        <v>30100002</v>
+        <v>20200004</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F82">
-        <v>3020002</v>
+        <v>2510004</v>
       </c>
       <c r="G82" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K82">
-        <v>30100002</v>
+        <v>20200004</v>
       </c>
       <c r="L82" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83">
-        <v>30100003</v>
+        <v>20200005</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83">
-        <v>3020003</v>
+        <v>2510005</v>
       </c>
       <c r="G83" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K83">
-        <v>30100003</v>
+        <v>20200005</v>
       </c>
       <c r="L83" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84">
-        <v>30100004</v>
+        <v>20200006</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F84">
-        <v>3020004</v>
+        <v>2510006</v>
       </c>
       <c r="G84" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K84">
-        <v>30100004</v>
+        <v>20200006</v>
       </c>
       <c r="L84" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85">
-        <v>30100005</v>
+        <v>20200007</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F85">
-        <v>3020005</v>
+        <v>2510007</v>
       </c>
       <c r="G85" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="K85">
-        <v>30100005</v>
+        <v>20200007</v>
       </c>
       <c r="L85" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86">
-        <v>30100006</v>
+        <v>20200008</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F86">
-        <v>3020006</v>
+        <v>2510008</v>
       </c>
       <c r="G86" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K86">
-        <v>30100006</v>
+        <v>20200008</v>
       </c>
       <c r="L86" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87">
-        <v>30100007</v>
+        <v>20200009</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87">
+        <v>2510009</v>
+      </c>
+      <c r="G87" t="s">
+        <v>192</v>
+      </c>
+      <c r="K87">
+        <v>20200009</v>
+      </c>
+      <c r="L87" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88">
+        <v>20200010</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88">
+        <v>2510010</v>
+      </c>
+      <c r="G88" t="s">
+        <v>194</v>
+      </c>
+      <c r="K88">
+        <v>20200010</v>
+      </c>
+      <c r="L88" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89">
+        <v>20200011</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89">
+        <v>2510011</v>
+      </c>
+      <c r="G89" t="s">
+        <v>196</v>
+      </c>
+      <c r="K89">
+        <v>20200011</v>
+      </c>
+      <c r="L89" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90">
+        <v>20300001</v>
+      </c>
+      <c r="B90">
         <v>3</v>
       </c>
-      <c r="F87">
-        <v>3020007</v>
-      </c>
-      <c r="G87" t="s">
-        <v>195</v>
-      </c>
-      <c r="K87">
-        <v>30100007</v>
-      </c>
-      <c r="L87" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" spans="1:12">
-      <c r="A88">
-        <v>30100008</v>
-      </c>
-      <c r="B88">
-        <v>1</v>
-      </c>
-      <c r="D88">
-        <v>1</v>
-      </c>
-      <c r="E88">
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="F90">
+        <v>2520001</v>
+      </c>
+      <c r="G90" t="s">
+        <v>198</v>
+      </c>
+      <c r="K90">
+        <v>20300001</v>
+      </c>
+      <c r="L90" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91">
+        <v>20300003</v>
+      </c>
+      <c r="B91">
         <v>3</v>
       </c>
-      <c r="F88">
-        <v>3020008</v>
-      </c>
-      <c r="G88" t="s">
-        <v>197</v>
-      </c>
-      <c r="K88">
-        <v>30100008</v>
-      </c>
-      <c r="L88" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" spans="1:12">
-      <c r="A89">
-        <v>30100009</v>
-      </c>
-      <c r="B89">
-        <v>1</v>
-      </c>
-      <c r="D89">
-        <v>1</v>
-      </c>
-      <c r="E89">
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="F91">
+        <v>2520003</v>
+      </c>
+      <c r="G91" t="s">
+        <v>200</v>
+      </c>
+      <c r="K91">
+        <v>20300003</v>
+      </c>
+      <c r="L91" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92">
+        <v>20300007</v>
+      </c>
+      <c r="B92">
         <v>3</v>
       </c>
-      <c r="F89">
-        <v>3020009</v>
-      </c>
-      <c r="G89" t="s">
-        <v>199</v>
-      </c>
-      <c r="K89">
-        <v>30100009</v>
-      </c>
-      <c r="L89" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1" spans="1:12">
-      <c r="A90">
-        <v>30100010</v>
-      </c>
-      <c r="B90">
-        <v>1</v>
-      </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90">
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="F92">
+        <v>2520007</v>
+      </c>
+      <c r="G92" t="s">
+        <v>202</v>
+      </c>
+      <c r="K92">
+        <v>20300007</v>
+      </c>
+      <c r="L92" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93">
+        <v>20300009</v>
+      </c>
+      <c r="B93">
         <v>3</v>
       </c>
-      <c r="F90">
-        <v>3020010</v>
-      </c>
-      <c r="G90" t="s">
-        <v>201</v>
-      </c>
-      <c r="K90">
-        <v>30100010</v>
-      </c>
-      <c r="L90" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" spans="1:12">
-      <c r="A91">
-        <v>30100011</v>
-      </c>
-      <c r="B91">
-        <v>1</v>
-      </c>
-      <c r="D91">
-        <v>1</v>
-      </c>
-      <c r="E91">
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="F93">
+        <v>2520009</v>
+      </c>
+      <c r="G93" t="s">
+        <v>204</v>
+      </c>
+      <c r="K93">
+        <v>20300009</v>
+      </c>
+      <c r="L93" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94">
+        <v>20300011</v>
+      </c>
+      <c r="B94">
         <v>3</v>
       </c>
-      <c r="F91">
-        <v>3020011</v>
-      </c>
-      <c r="G91" t="s">
-        <v>203</v>
-      </c>
-      <c r="K91">
-        <v>30100011</v>
-      </c>
-      <c r="L91" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1" spans="1:12">
-      <c r="A92">
-        <v>30100012</v>
-      </c>
-      <c r="B92">
-        <v>1</v>
-      </c>
-      <c r="D92">
-        <v>1</v>
-      </c>
-      <c r="E92">
-        <v>3</v>
-      </c>
-      <c r="F92">
-        <v>3020012</v>
-      </c>
-      <c r="G92" t="s">
-        <v>205</v>
-      </c>
-      <c r="K92">
-        <v>30100012</v>
-      </c>
-      <c r="L92" t="s">
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+      <c r="F94">
+        <v>2520011</v>
+      </c>
+      <c r="G94" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="93" ht="15" customHeight="1" spans="1:12">
-      <c r="A93">
-        <v>30100013</v>
-      </c>
-      <c r="B93">
-        <v>1</v>
-      </c>
-      <c r="D93">
-        <v>1</v>
-      </c>
-      <c r="E93">
-        <v>3</v>
-      </c>
-      <c r="F93">
-        <v>3020013</v>
-      </c>
-      <c r="G93" t="s">
+      <c r="K94">
+        <v>20300011</v>
+      </c>
+      <c r="L94" t="s">
         <v>207</v>
       </c>
-      <c r="K93">
-        <v>30100013</v>
-      </c>
-      <c r="L93" t="s">
+    </row>
+    <row r="95" ht="12" customHeight="1" spans="1:12">
+      <c r="A95">
+        <v>21000001</v>
+      </c>
+      <c r="B95">
+        <v>10</v>
+      </c>
+      <c r="C95">
+        <v>8</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="F95">
+        <v>2900001</v>
+      </c>
+      <c r="G95" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="94" ht="15" customHeight="1" spans="1:12">
-      <c r="A94">
-        <v>30100014</v>
-      </c>
-      <c r="B94">
-        <v>1</v>
-      </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-      <c r="E94">
-        <v>3</v>
-      </c>
-      <c r="F94">
-        <v>3020014</v>
-      </c>
-      <c r="G94" t="s">
+      <c r="H95">
+        <v>45</v>
+      </c>
+      <c r="I95" t="s">
         <v>209</v>
       </c>
-      <c r="K94">
-        <v>30100014</v>
-      </c>
-      <c r="L94" t="s">
+      <c r="K95">
+        <v>21000001</v>
+      </c>
+      <c r="L95" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:12">
-      <c r="A95">
-        <v>30100015</v>
-      </c>
-      <c r="B95">
-        <v>1</v>
-      </c>
-      <c r="D95">
-        <v>1</v>
-      </c>
-      <c r="E95">
-        <v>3</v>
-      </c>
-      <c r="F95">
-        <v>3020015</v>
-      </c>
-      <c r="G95" t="s">
+    <row r="96" spans="1:12">
+      <c r="A96">
+        <v>21000002</v>
+      </c>
+      <c r="B96">
+        <v>10</v>
+      </c>
+      <c r="C96">
+        <v>8</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="F96">
+        <v>2900002</v>
+      </c>
+      <c r="G96" t="s">
         <v>211</v>
       </c>
-      <c r="K95">
-        <v>30100015</v>
-      </c>
-      <c r="L95" t="s">
+      <c r="H96">
+        <v>45</v>
+      </c>
+      <c r="I96" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="96" ht="15" customHeight="1" spans="1:12">
-      <c r="A96">
-        <v>30100016</v>
-      </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="E96">
-        <v>3</v>
-      </c>
-      <c r="F96">
-        <v>3020016</v>
-      </c>
-      <c r="G96" t="s">
+      <c r="K96">
+        <v>21000002</v>
+      </c>
+      <c r="L96" t="s">
         <v>213</v>
       </c>
-      <c r="K96">
-        <v>30100016</v>
-      </c>
-      <c r="L96" t="s">
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97">
+        <v>21000003</v>
+      </c>
+      <c r="B97">
+        <v>10</v>
+      </c>
+      <c r="C97">
+        <v>8</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="F97">
+        <v>2900003</v>
+      </c>
+      <c r="G97" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" spans="1:12">
-      <c r="A97">
-        <v>30100017</v>
-      </c>
-      <c r="B97">
-        <v>1</v>
-      </c>
-      <c r="D97">
-        <v>1</v>
-      </c>
-      <c r="E97">
-        <v>3</v>
-      </c>
-      <c r="F97">
-        <v>3020017</v>
-      </c>
-      <c r="G97" t="s">
+      <c r="K97">
+        <v>21000003</v>
+      </c>
+      <c r="L97" t="s">
         <v>215</v>
       </c>
-      <c r="K97">
-        <v>30100017</v>
-      </c>
-      <c r="L97" t="s">
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98">
+        <v>21000004</v>
+      </c>
+      <c r="B98">
+        <v>10</v>
+      </c>
+      <c r="C98">
+        <v>8</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="F98">
+        <v>2900004</v>
+      </c>
+      <c r="G98" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" spans="1:12">
-      <c r="A98">
-        <v>30100018</v>
-      </c>
-      <c r="B98">
-        <v>1</v>
-      </c>
-      <c r="D98">
-        <v>1</v>
-      </c>
-      <c r="E98">
-        <v>3</v>
-      </c>
-      <c r="F98">
-        <v>3020018</v>
-      </c>
-      <c r="G98" t="s">
+      <c r="K98">
+        <v>21000004</v>
+      </c>
+      <c r="L98" t="s">
         <v>217</v>
-      </c>
-      <c r="K98">
-        <v>30100018</v>
-      </c>
-      <c r="L98" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99">
-        <v>30100019</v>
+        <v>21000005</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C99">
+        <v>8</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99">
-        <v>3020019</v>
+        <v>2900005</v>
       </c>
       <c r="G99" t="s">
+        <v>218</v>
+      </c>
+      <c r="K99">
+        <v>21000005</v>
+      </c>
+      <c r="L99" t="s">
         <v>219</v>
-      </c>
-      <c r="K99">
-        <v>30100019</v>
-      </c>
-      <c r="L99" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100">
-        <v>30100020</v>
+        <v>21000006</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C100">
+        <v>8</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100">
-        <v>3020020</v>
+        <v>2900006</v>
       </c>
       <c r="G100" t="s">
+        <v>220</v>
+      </c>
+      <c r="K100">
+        <v>21000006</v>
+      </c>
+      <c r="L100" t="s">
         <v>221</v>
-      </c>
-      <c r="K100">
-        <v>30100020</v>
-      </c>
-      <c r="L100" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101">
-        <v>40100001</v>
+        <v>21000007</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C101">
+        <v>8</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F101">
-        <v>4500003</v>
+        <v>2900007</v>
       </c>
       <c r="G101" t="s">
+        <v>222</v>
+      </c>
+      <c r="K101">
+        <v>21000007</v>
+      </c>
+      <c r="L101" t="s">
         <v>223</v>
       </c>
-      <c r="K101">
-        <v>40100001</v>
-      </c>
-      <c r="L101" t="s">
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102">
+        <v>21000008</v>
+      </c>
+      <c r="B102">
+        <v>10</v>
+      </c>
+      <c r="C102">
+        <v>8</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="F102">
+        <v>2900008</v>
+      </c>
+      <c r="G102" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="102" ht="12" customHeight="1" spans="1:12">
-      <c r="A102">
-        <v>40200001</v>
-      </c>
-      <c r="B102">
-        <v>2</v>
-      </c>
-      <c r="D102">
-        <v>1</v>
-      </c>
-      <c r="E102">
-        <v>4</v>
-      </c>
-      <c r="F102">
-        <v>4510001</v>
-      </c>
-      <c r="G102" t="s">
+      <c r="K102">
+        <v>21000008</v>
+      </c>
+      <c r="L102" t="s">
         <v>225</v>
-      </c>
-      <c r="K102">
-        <v>40200001</v>
-      </c>
-      <c r="L102" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103">
-        <v>40200002</v>
+        <v>21000009</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="C103">
+        <v>8</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F103">
-        <v>4510002</v>
+        <v>2900009</v>
       </c>
       <c r="G103" t="s">
+        <v>226</v>
+      </c>
+      <c r="K103">
+        <v>21000009</v>
+      </c>
+      <c r="L103" t="s">
         <v>227</v>
-      </c>
-      <c r="K103">
-        <v>40200002</v>
-      </c>
-      <c r="L103" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104">
-        <v>40200003</v>
+        <v>21000010</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="C104">
+        <v>8</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F104">
-        <v>4510003</v>
+        <v>2900010</v>
       </c>
       <c r="G104" t="s">
+        <v>228</v>
+      </c>
+      <c r="K104">
+        <v>21000010</v>
+      </c>
+      <c r="L104" t="s">
         <v>229</v>
-      </c>
-      <c r="K104">
-        <v>40200003</v>
-      </c>
-      <c r="L104" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105">
-        <v>40200004</v>
+        <v>21010001</v>
       </c>
       <c r="B105">
+        <v>10</v>
+      </c>
+      <c r="C105">
         <v>2</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F105">
-        <v>4510004</v>
+        <v>2910001</v>
       </c>
       <c r="G105" t="s">
+        <v>230</v>
+      </c>
+      <c r="H105">
+        <v>-45</v>
+      </c>
+      <c r="K105">
+        <v>21010001</v>
+      </c>
+      <c r="L105" t="s">
         <v>231</v>
-      </c>
-      <c r="K105">
-        <v>40200004</v>
-      </c>
-      <c r="L105" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106">
-        <v>40200005</v>
+        <v>21010002</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F106">
-        <v>4510005</v>
+        <v>2910002</v>
       </c>
       <c r="G106" t="s">
+        <v>232</v>
+      </c>
+      <c r="H106">
+        <v>-45</v>
+      </c>
+      <c r="K106">
+        <v>21010002</v>
+      </c>
+      <c r="L106" t="s">
         <v>233</v>
-      </c>
-      <c r="K106">
-        <v>40200005</v>
-      </c>
-      <c r="L106" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107">
-        <v>40200006</v>
+        <v>21010003</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F107">
-        <v>4510006</v>
+        <v>2910003</v>
       </c>
       <c r="G107" t="s">
+        <v>234</v>
+      </c>
+      <c r="H107">
+        <v>-45</v>
+      </c>
+      <c r="K107">
+        <v>21010003</v>
+      </c>
+      <c r="L107" t="s">
         <v>235</v>
-      </c>
-      <c r="K107">
-        <v>40200006</v>
-      </c>
-      <c r="L107" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108">
-        <v>40300001</v>
+        <v>21010004</v>
       </c>
       <c r="B108">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F108">
-        <v>4520001</v>
+        <v>2910004</v>
       </c>
       <c r="G108" t="s">
+        <v>236</v>
+      </c>
+      <c r="H108">
+        <v>-45</v>
+      </c>
+      <c r="K108">
+        <v>21010004</v>
+      </c>
+      <c r="L108" t="s">
         <v>237</v>
-      </c>
-      <c r="K108">
-        <v>40300001</v>
-      </c>
-      <c r="L108" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109">
-        <v>40300002</v>
+        <v>21010005</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C109">
+        <v>2</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F109">
-        <v>4520002</v>
+        <v>2910005</v>
       </c>
       <c r="G109" t="s">
+        <v>238</v>
+      </c>
+      <c r="K109">
+        <v>21010005</v>
+      </c>
+      <c r="L109" t="s">
         <v>239</v>
-      </c>
-      <c r="K109">
-        <v>40300002</v>
-      </c>
-      <c r="L109" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110">
-        <v>40300003</v>
+        <v>21010006</v>
       </c>
       <c r="B110">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F110">
-        <v>4520003</v>
+        <v>2910006</v>
       </c>
       <c r="G110" t="s">
+        <v>240</v>
+      </c>
+      <c r="K110">
+        <v>21010006</v>
+      </c>
+      <c r="L110" t="s">
         <v>241</v>
-      </c>
-      <c r="K110">
-        <v>40300003</v>
-      </c>
-      <c r="L110" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111">
-        <v>40300004</v>
+        <v>21010007</v>
       </c>
       <c r="B111">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F111">
-        <v>4520004</v>
+        <v>2910007</v>
       </c>
       <c r="G111" t="s">
+        <v>242</v>
+      </c>
+      <c r="K111">
+        <v>21010007</v>
+      </c>
+      <c r="L111" t="s">
         <v>243</v>
-      </c>
-      <c r="K111">
-        <v>40300004</v>
-      </c>
-      <c r="L111" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112">
-        <v>41000001</v>
+        <v>21010008</v>
       </c>
       <c r="B112">
         <v>10</v>
@@ -5281,24 +5519,24 @@
         <v>1</v>
       </c>
       <c r="E112">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F112">
-        <v>4900001</v>
+        <v>2910008</v>
       </c>
       <c r="G112" t="s">
+        <v>244</v>
+      </c>
+      <c r="K112">
+        <v>21010008</v>
+      </c>
+      <c r="L112" t="s">
         <v>245</v>
-      </c>
-      <c r="K112">
-        <v>41000001</v>
-      </c>
-      <c r="L112" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113">
-        <v>41000002</v>
+        <v>21010009</v>
       </c>
       <c r="B113">
         <v>10</v>
@@ -5310,24 +5548,24 @@
         <v>1</v>
       </c>
       <c r="E113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F113">
-        <v>4900002</v>
+        <v>2910009</v>
       </c>
       <c r="G113" t="s">
+        <v>246</v>
+      </c>
+      <c r="K113">
+        <v>21010009</v>
+      </c>
+      <c r="L113" t="s">
         <v>247</v>
-      </c>
-      <c r="K113">
-        <v>41000002</v>
-      </c>
-      <c r="L113" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114">
-        <v>41000003</v>
+        <v>21010010</v>
       </c>
       <c r="B114">
         <v>10</v>
@@ -5339,1203 +5577,1184 @@
         <v>1</v>
       </c>
       <c r="E114">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F114">
-        <v>4900003</v>
+        <v>2910010</v>
       </c>
       <c r="G114" t="s">
+        <v>248</v>
+      </c>
+      <c r="K114">
+        <v>21010010</v>
+      </c>
+      <c r="L114" t="s">
         <v>249</v>
-      </c>
-      <c r="K114">
-        <v>41000003</v>
-      </c>
-      <c r="L114" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115">
-        <v>41000004</v>
+        <v>21010011</v>
       </c>
       <c r="B115">
         <v>10</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>1</v>
       </c>
       <c r="E115">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F115">
-        <v>4900004</v>
+        <v>2910011</v>
       </c>
       <c r="G115" t="s">
+        <v>250</v>
+      </c>
+      <c r="H115">
+        <v>-45</v>
+      </c>
+      <c r="K115">
+        <v>21010011</v>
+      </c>
+      <c r="L115" t="s">
         <v>251</v>
-      </c>
-      <c r="K115">
-        <v>41000004</v>
-      </c>
-      <c r="L115" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116">
-        <v>41000005</v>
+        <v>21010012</v>
       </c>
       <c r="B116">
         <v>10</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116">
         <v>1</v>
       </c>
       <c r="E116">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F116">
-        <v>4900005</v>
+        <v>2910012</v>
       </c>
       <c r="G116" t="s">
+        <v>252</v>
+      </c>
+      <c r="H116">
+        <v>-45</v>
+      </c>
+      <c r="K116">
+        <v>21010012</v>
+      </c>
+      <c r="L116" t="s">
         <v>253</v>
       </c>
-      <c r="K116">
-        <v>41000005</v>
-      </c>
-      <c r="L116" t="s">
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117">
+        <v>21010013</v>
+      </c>
+      <c r="B117">
+        <v>10</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+      <c r="E117">
+        <v>2</v>
+      </c>
+      <c r="F117">
+        <v>2910013</v>
+      </c>
+      <c r="G117" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="117" customFormat="1" spans="1:12">
-      <c r="A117">
-        <v>50100001</v>
-      </c>
-      <c r="B117">
-        <v>1</v>
-      </c>
-      <c r="D117">
-        <v>1</v>
-      </c>
-      <c r="E117">
-        <v>5</v>
-      </c>
-      <c r="F117">
-        <v>5500001</v>
-      </c>
-      <c r="G117" t="s">
+      <c r="K117">
+        <v>21010013</v>
+      </c>
+      <c r="L117" t="s">
         <v>255</v>
-      </c>
-      <c r="K117">
-        <v>50100001</v>
-      </c>
-      <c r="L117" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118">
-        <v>50100002</v>
+        <v>21010014</v>
       </c>
       <c r="B118">
+        <v>10</v>
+      </c>
+      <c r="C118">
         <v>1</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F118">
-        <v>5500002</v>
+        <v>2910014</v>
       </c>
       <c r="G118" t="s">
+        <v>256</v>
+      </c>
+      <c r="K118">
+        <v>21010014</v>
+      </c>
+      <c r="L118" t="s">
         <v>257</v>
-      </c>
-      <c r="K118">
-        <v>50100002</v>
-      </c>
-      <c r="L118" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119">
-        <v>50100003</v>
+        <v>21010015</v>
       </c>
       <c r="B119">
+        <v>10</v>
+      </c>
+      <c r="C119">
         <v>1</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F119">
-        <v>5500003</v>
+        <v>2910015</v>
       </c>
       <c r="G119" t="s">
+        <v>258</v>
+      </c>
+      <c r="K119">
+        <v>21010015</v>
+      </c>
+      <c r="L119" t="s">
         <v>259</v>
       </c>
-      <c r="K119">
-        <v>50100003</v>
-      </c>
-      <c r="L119" t="s">
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120">
+        <v>21010016</v>
+      </c>
+      <c r="B120">
+        <v>10</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>2</v>
+      </c>
+      <c r="F120">
+        <v>2910016</v>
+      </c>
+      <c r="G120" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="120" customFormat="1" spans="1:12">
-      <c r="A120">
-        <v>50200001</v>
-      </c>
-      <c r="B120">
-        <v>2</v>
-      </c>
-      <c r="D120">
-        <v>1</v>
-      </c>
-      <c r="E120">
-        <v>5</v>
-      </c>
-      <c r="F120">
-        <v>5510001</v>
-      </c>
-      <c r="G120" t="s">
+      <c r="K120">
+        <v>21010016</v>
+      </c>
+      <c r="L120" t="s">
         <v>261</v>
-      </c>
-      <c r="K120">
-        <v>50200001</v>
-      </c>
-      <c r="L120" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121">
-        <v>50200002</v>
+        <v>21010017</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F121">
-        <v>5510002</v>
+        <v>2910017</v>
       </c>
       <c r="G121" t="s">
+        <v>262</v>
+      </c>
+      <c r="K121">
+        <v>21010017</v>
+      </c>
+      <c r="L121" t="s">
         <v>263</v>
-      </c>
-      <c r="K121">
-        <v>50200002</v>
-      </c>
-      <c r="L121" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122">
-        <v>50200003</v>
+        <v>21010018</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
       </c>
       <c r="D122">
         <v>1</v>
       </c>
       <c r="E122">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F122">
-        <v>5510003</v>
+        <v>2910018</v>
       </c>
       <c r="G122" t="s">
+        <v>264</v>
+      </c>
+      <c r="K122">
+        <v>21010018</v>
+      </c>
+      <c r="L122" t="s">
         <v>265</v>
       </c>
-      <c r="K122">
-        <v>50200003</v>
-      </c>
-      <c r="L122" t="s">
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123">
+        <v>21010019</v>
+      </c>
+      <c r="B123">
+        <v>10</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123">
+        <v>2910019</v>
+      </c>
+      <c r="G123" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="123" customFormat="1" ht="12" customHeight="1" spans="1:12">
-      <c r="A123">
-        <v>50300001</v>
-      </c>
-      <c r="B123">
-        <v>3</v>
-      </c>
-      <c r="D123">
-        <v>1</v>
-      </c>
-      <c r="E123">
-        <v>5</v>
-      </c>
-      <c r="F123">
-        <v>5520001</v>
-      </c>
-      <c r="G123" t="s">
+      <c r="K123">
+        <v>21010019</v>
+      </c>
+      <c r="L123" t="s">
         <v>267</v>
-      </c>
-      <c r="K123">
-        <v>50300001</v>
-      </c>
-      <c r="L123" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="124" spans="1:12">
       <c r="A124">
-        <v>50300002</v>
+        <v>21010020</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
       </c>
       <c r="D124">
         <v>1</v>
       </c>
       <c r="E124">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F124">
-        <v>5520002</v>
+        <v>2910020</v>
       </c>
       <c r="G124" t="s">
+        <v>268</v>
+      </c>
+      <c r="K124">
+        <v>21010020</v>
+      </c>
+      <c r="L124" t="s">
         <v>269</v>
-      </c>
-      <c r="K124">
-        <v>50300002</v>
-      </c>
-      <c r="L124" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:12">
       <c r="A125">
-        <v>50500001</v>
+        <v>30100001</v>
       </c>
       <c r="B125">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F125">
-        <v>5090001</v>
+        <v>3020001</v>
       </c>
       <c r="G125" t="s">
+        <v>270</v>
+      </c>
+      <c r="K125">
+        <v>30100001</v>
+      </c>
+      <c r="L125" t="s">
         <v>271</v>
-      </c>
-      <c r="K125">
-        <v>50500001</v>
-      </c>
-      <c r="L125" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="126" spans="1:12">
       <c r="A126">
-        <v>50500002</v>
+        <v>30100002</v>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F126">
-        <v>5090002</v>
+        <v>3020002</v>
       </c>
       <c r="G126" t="s">
+        <v>272</v>
+      </c>
+      <c r="K126">
+        <v>30100002</v>
+      </c>
+      <c r="L126" t="s">
         <v>273</v>
-      </c>
-      <c r="K126">
-        <v>50500002</v>
-      </c>
-      <c r="L126" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127">
-        <v>50500003</v>
+        <v>30100003</v>
       </c>
       <c r="B127">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D127">
         <v>1</v>
       </c>
       <c r="E127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F127">
-        <v>5090003</v>
+        <v>3020003</v>
       </c>
       <c r="G127" t="s">
+        <v>274</v>
+      </c>
+      <c r="K127">
+        <v>30100003</v>
+      </c>
+      <c r="L127" t="s">
         <v>275</v>
-      </c>
-      <c r="K127">
-        <v>50500003</v>
-      </c>
-      <c r="L127" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128">
-        <v>50500004</v>
+        <v>30100004</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F128">
-        <v>5090004</v>
+        <v>3020004</v>
       </c>
       <c r="G128" t="s">
+        <v>276</v>
+      </c>
+      <c r="K128">
+        <v>30100004</v>
+      </c>
+      <c r="L128" t="s">
         <v>277</v>
-      </c>
-      <c r="K128">
-        <v>50500004</v>
-      </c>
-      <c r="L128" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="129" spans="1:12">
       <c r="A129">
-        <v>50500005</v>
+        <v>30100005</v>
       </c>
       <c r="B129">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F129">
-        <v>5090005</v>
+        <v>3020005</v>
       </c>
       <c r="G129" t="s">
+        <v>278</v>
+      </c>
+      <c r="K129">
+        <v>30100005</v>
+      </c>
+      <c r="L129" t="s">
         <v>279</v>
       </c>
-      <c r="K129">
-        <v>50500005</v>
-      </c>
-      <c r="L129" t="s">
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130">
+        <v>30100006</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>3</v>
+      </c>
+      <c r="F130">
+        <v>3020006</v>
+      </c>
+      <c r="G130" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="130" customFormat="1" spans="1:12">
-      <c r="A130">
-        <v>51010001</v>
-      </c>
-      <c r="B130">
-        <v>10</v>
-      </c>
-      <c r="C130">
-        <v>8</v>
-      </c>
-      <c r="D130">
-        <v>1</v>
-      </c>
-      <c r="E130">
-        <v>5</v>
-      </c>
-      <c r="F130">
-        <v>5910001</v>
-      </c>
-      <c r="G130" t="s">
+      <c r="K130">
+        <v>30100006</v>
+      </c>
+      <c r="L130" t="s">
         <v>281</v>
       </c>
-      <c r="I130" t="s">
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131">
+        <v>30100007</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+      <c r="E131">
+        <v>3</v>
+      </c>
+      <c r="F131">
+        <v>3020007</v>
+      </c>
+      <c r="G131" t="s">
         <v>282</v>
       </c>
-      <c r="K130">
-        <v>51010001</v>
-      </c>
-      <c r="L130" t="s">
+      <c r="K131">
+        <v>30100007</v>
+      </c>
+      <c r="L131" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="131" customFormat="1" spans="1:12">
-      <c r="A131">
-        <v>51010002</v>
-      </c>
-      <c r="B131">
-        <v>10</v>
-      </c>
-      <c r="C131">
-        <v>8</v>
-      </c>
-      <c r="D131">
-        <v>1</v>
-      </c>
-      <c r="E131">
-        <v>5</v>
-      </c>
-      <c r="F131">
-        <v>5910002</v>
-      </c>
-      <c r="G131" t="s">
+    <row r="132" ht="15" customHeight="1" spans="1:12">
+      <c r="A132">
+        <v>30100008</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>3</v>
+      </c>
+      <c r="F132">
+        <v>3020008</v>
+      </c>
+      <c r="G132" t="s">
         <v>284</v>
       </c>
-      <c r="I131" t="s">
+      <c r="K132">
+        <v>30100008</v>
+      </c>
+      <c r="L132" t="s">
         <v>285</v>
       </c>
-      <c r="K131">
-        <v>51010002</v>
-      </c>
-      <c r="L131" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="132" customFormat="1" spans="1:12">
-      <c r="A132">
-        <v>51010003</v>
-      </c>
-      <c r="B132">
-        <v>10</v>
-      </c>
-      <c r="C132">
-        <v>8</v>
-      </c>
-      <c r="D132">
-        <v>1</v>
-      </c>
-      <c r="E132">
-        <v>5</v>
-      </c>
-      <c r="F132">
-        <v>5910003</v>
-      </c>
-      <c r="G132" t="s">
+    </row>
+    <row r="133" ht="15" customHeight="1" spans="1:12">
+      <c r="A133">
+        <v>30100009</v>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>3</v>
+      </c>
+      <c r="F133">
+        <v>3020009</v>
+      </c>
+      <c r="G133" t="s">
         <v>286</v>
       </c>
-      <c r="I132" t="s">
+      <c r="K133">
+        <v>30100009</v>
+      </c>
+      <c r="L133" t="s">
         <v>287</v>
       </c>
-      <c r="K132">
-        <v>51010003</v>
-      </c>
-      <c r="L132" t="s">
+    </row>
+    <row r="134" ht="15" customHeight="1" spans="1:12">
+      <c r="A134">
+        <v>30100010</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>3</v>
+      </c>
+      <c r="F134">
+        <v>3020010</v>
+      </c>
+      <c r="G134" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="133" customFormat="1" spans="1:12">
-      <c r="A133">
-        <v>60100001</v>
-      </c>
-      <c r="B133">
-        <v>1</v>
-      </c>
-      <c r="D133">
-        <v>1</v>
-      </c>
-      <c r="E133">
-        <v>6</v>
-      </c>
-      <c r="F133">
-        <v>6500001</v>
-      </c>
-      <c r="G133" t="s">
+      <c r="K134">
+        <v>30100010</v>
+      </c>
+      <c r="L134" t="s">
         <v>289</v>
       </c>
-      <c r="K133">
-        <v>60100001</v>
-      </c>
-      <c r="L133" t="s">
+    </row>
+    <row r="135" ht="15" customHeight="1" spans="1:12">
+      <c r="A135">
+        <v>30100011</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>3</v>
+      </c>
+      <c r="F135">
+        <v>3020011</v>
+      </c>
+      <c r="G135" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="134" spans="1:12">
-      <c r="A134">
-        <v>60100002</v>
-      </c>
-      <c r="B134">
-        <v>1</v>
-      </c>
-      <c r="D134">
-        <v>1</v>
-      </c>
-      <c r="E134">
-        <v>6</v>
-      </c>
-      <c r="F134">
-        <v>6500002</v>
-      </c>
-      <c r="G134" t="s">
+      <c r="K135">
+        <v>30100011</v>
+      </c>
+      <c r="L135" t="s">
         <v>291</v>
       </c>
-      <c r="K134">
-        <v>60100002</v>
-      </c>
-      <c r="L134" t="s">
+    </row>
+    <row r="136" ht="15" customHeight="1" spans="1:12">
+      <c r="A136">
+        <v>30100012</v>
+      </c>
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>3</v>
+      </c>
+      <c r="F136">
+        <v>3020012</v>
+      </c>
+      <c r="G136" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="135" spans="1:12">
-      <c r="A135">
-        <v>60100003</v>
-      </c>
-      <c r="B135">
-        <v>1</v>
-      </c>
-      <c r="D135">
-        <v>1</v>
-      </c>
-      <c r="E135">
-        <v>6</v>
-      </c>
-      <c r="F135">
-        <v>6500003</v>
-      </c>
-      <c r="G135" t="s">
+      <c r="K136">
+        <v>30100012</v>
+      </c>
+      <c r="L136" t="s">
         <v>293</v>
       </c>
-      <c r="K135">
-        <v>60100003</v>
-      </c>
-      <c r="L135" t="s">
+    </row>
+    <row r="137" ht="15" customHeight="1" spans="1:12">
+      <c r="A137">
+        <v>30100013</v>
+      </c>
+      <c r="B137">
+        <v>1</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>3</v>
+      </c>
+      <c r="F137">
+        <v>3020013</v>
+      </c>
+      <c r="G137" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="136" spans="1:12">
-      <c r="A136">
-        <v>60100004</v>
-      </c>
-      <c r="B136">
-        <v>1</v>
-      </c>
-      <c r="D136">
-        <v>1</v>
-      </c>
-      <c r="E136">
-        <v>6</v>
-      </c>
-      <c r="F136">
-        <v>6500004</v>
-      </c>
-      <c r="G136" t="s">
+      <c r="K137">
+        <v>30100013</v>
+      </c>
+      <c r="L137" t="s">
         <v>295</v>
       </c>
-      <c r="K136">
-        <v>60100004</v>
-      </c>
-      <c r="L136" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12">
-      <c r="A137">
-        <v>60100005</v>
-      </c>
-      <c r="B137">
-        <v>1</v>
-      </c>
-      <c r="D137">
-        <v>1</v>
-      </c>
-      <c r="E137">
-        <v>6</v>
-      </c>
-      <c r="F137">
-        <v>6500005</v>
-      </c>
-      <c r="G137" t="s">
+    </row>
+    <row r="138" ht="15" customHeight="1" spans="1:12">
+      <c r="A138">
+        <v>30100014</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138">
+        <v>3</v>
+      </c>
+      <c r="F138">
+        <v>3020014</v>
+      </c>
+      <c r="G138" t="s">
         <v>296</v>
       </c>
-      <c r="K137">
-        <v>60100005</v>
-      </c>
-      <c r="L137" t="s">
+      <c r="K138">
+        <v>30100014</v>
+      </c>
+      <c r="L138" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="138" ht="12" customHeight="1" spans="1:12">
-      <c r="A138">
-        <v>60100006</v>
-      </c>
-      <c r="B138">
-        <v>1</v>
-      </c>
-      <c r="D138">
-        <v>1</v>
-      </c>
-      <c r="E138">
-        <v>6</v>
-      </c>
-      <c r="F138">
-        <v>6500006</v>
-      </c>
-      <c r="G138" t="s">
+    <row r="139" ht="15" customHeight="1" spans="1:12">
+      <c r="A139">
+        <v>30100015</v>
+      </c>
+      <c r="B139">
+        <v>1</v>
+      </c>
+      <c r="D139">
+        <v>1</v>
+      </c>
+      <c r="E139">
+        <v>3</v>
+      </c>
+      <c r="F139">
+        <v>3020015</v>
+      </c>
+      <c r="G139" t="s">
         <v>298</v>
       </c>
-      <c r="K138">
-        <v>60100006</v>
-      </c>
-      <c r="L138" t="s">
+      <c r="K139">
+        <v>30100015</v>
+      </c>
+      <c r="L139" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="139" ht="12" customHeight="1" spans="1:12">
-      <c r="A139">
-        <v>60100007</v>
-      </c>
-      <c r="B139">
-        <v>1</v>
-      </c>
-      <c r="D139">
-        <v>1</v>
-      </c>
-      <c r="E139">
-        <v>6</v>
-      </c>
-      <c r="F139">
-        <v>6500007</v>
-      </c>
-      <c r="G139" t="s">
+    <row r="140" ht="15" customHeight="1" spans="1:12">
+      <c r="A140">
+        <v>30100016</v>
+      </c>
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="D140">
+        <v>1</v>
+      </c>
+      <c r="E140">
+        <v>3</v>
+      </c>
+      <c r="F140">
+        <v>3020016</v>
+      </c>
+      <c r="G140" t="s">
         <v>300</v>
       </c>
-      <c r="K139">
-        <v>60100007</v>
-      </c>
-      <c r="L139" t="s">
+      <c r="K140">
+        <v>30100016</v>
+      </c>
+      <c r="L140" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="140" ht="12" customHeight="1" spans="1:12">
-      <c r="A140">
-        <v>60100008</v>
-      </c>
-      <c r="B140">
-        <v>1</v>
-      </c>
-      <c r="D140">
-        <v>1</v>
-      </c>
-      <c r="E140">
-        <v>6</v>
-      </c>
-      <c r="F140">
-        <v>6500008</v>
-      </c>
-      <c r="G140" t="s">
+    <row r="141" ht="15" customHeight="1" spans="1:12">
+      <c r="A141">
+        <v>30100017</v>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="D141">
+        <v>1</v>
+      </c>
+      <c r="E141">
+        <v>3</v>
+      </c>
+      <c r="F141">
+        <v>3020017</v>
+      </c>
+      <c r="G141" t="s">
         <v>302</v>
       </c>
-      <c r="K140">
-        <v>60100008</v>
-      </c>
-      <c r="L140" t="s">
+      <c r="K141">
+        <v>30100017</v>
+      </c>
+      <c r="L141" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="141" ht="12" customHeight="1" spans="1:12">
-      <c r="A141">
-        <v>60100009</v>
-      </c>
-      <c r="B141">
-        <v>1</v>
-      </c>
-      <c r="D141">
-        <v>1</v>
-      </c>
-      <c r="E141">
-        <v>6</v>
-      </c>
-      <c r="F141">
-        <v>6500009</v>
-      </c>
-      <c r="G141" t="s">
+    <row r="142" ht="15" customHeight="1" spans="1:12">
+      <c r="A142">
+        <v>30100018</v>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142">
+        <v>3</v>
+      </c>
+      <c r="F142">
+        <v>3020018</v>
+      </c>
+      <c r="G142" t="s">
         <v>304</v>
       </c>
-      <c r="K141">
-        <v>60100009</v>
-      </c>
-      <c r="L141" t="s">
+      <c r="K142">
+        <v>30100018</v>
+      </c>
+      <c r="L142" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="142" ht="12" customHeight="1" spans="1:12">
-      <c r="A142">
-        <v>60100010</v>
-      </c>
-      <c r="B142">
-        <v>1</v>
-      </c>
-      <c r="D142">
-        <v>1</v>
-      </c>
-      <c r="E142">
-        <v>6</v>
-      </c>
-      <c r="F142">
-        <v>6500010</v>
-      </c>
-      <c r="G142" t="s">
+    <row r="143" spans="1:12">
+      <c r="A143">
+        <v>30100019</v>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>3</v>
+      </c>
+      <c r="F143">
+        <v>3020019</v>
+      </c>
+      <c r="G143" t="s">
         <v>306</v>
       </c>
-      <c r="K142">
-        <v>60100010</v>
-      </c>
-      <c r="L142" t="s">
+      <c r="K143">
+        <v>30100019</v>
+      </c>
+      <c r="L143" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="143" customFormat="1" ht="12" customHeight="1" spans="1:12">
-      <c r="A143">
-        <v>60200001</v>
-      </c>
-      <c r="B143">
-        <v>2</v>
-      </c>
-      <c r="D143">
-        <v>1</v>
-      </c>
-      <c r="E143">
-        <v>6</v>
-      </c>
-      <c r="F143">
-        <v>6510001</v>
-      </c>
-      <c r="G143" t="s">
+    <row r="144" spans="1:12">
+      <c r="A144">
+        <v>30100020</v>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144">
+        <v>3</v>
+      </c>
+      <c r="F144">
+        <v>3020020</v>
+      </c>
+      <c r="G144" t="s">
         <v>308</v>
       </c>
-      <c r="K143">
-        <v>60200001</v>
-      </c>
-      <c r="L143" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="144" ht="12" customHeight="1" spans="1:12">
-      <c r="A144">
-        <v>60200002</v>
-      </c>
-      <c r="B144">
-        <v>2</v>
-      </c>
-      <c r="D144">
-        <v>1</v>
-      </c>
-      <c r="E144">
-        <v>6</v>
-      </c>
-      <c r="F144">
-        <v>6510002</v>
-      </c>
-      <c r="G144" t="s">
+      <c r="K144">
+        <v>30100020</v>
+      </c>
+      <c r="L144" t="s">
         <v>309</v>
       </c>
-      <c r="K144">
-        <v>60200002</v>
-      </c>
-      <c r="L144" t="s">
+    </row>
+    <row r="145" spans="1:12">
+      <c r="A145">
+        <v>40100001</v>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="D145">
+        <v>1</v>
+      </c>
+      <c r="E145">
+        <v>4</v>
+      </c>
+      <c r="F145">
+        <v>4500003</v>
+      </c>
+      <c r="G145" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="145" customFormat="1" spans="1:12">
-      <c r="A145">
-        <v>60300001</v>
-      </c>
-      <c r="B145">
-        <v>3</v>
-      </c>
-      <c r="D145">
-        <v>1</v>
-      </c>
-      <c r="E145">
-        <v>6</v>
-      </c>
-      <c r="F145">
-        <v>6520001</v>
-      </c>
-      <c r="G145" t="s">
+      <c r="K145">
+        <v>40100001</v>
+      </c>
+      <c r="L145" t="s">
         <v>311</v>
       </c>
-      <c r="K145">
-        <v>60300001</v>
-      </c>
-      <c r="L145" t="s">
+    </row>
+    <row r="146" ht="12" customHeight="1" spans="1:12">
+      <c r="A146">
+        <v>40200001</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146">
+        <v>4</v>
+      </c>
+      <c r="F146">
+        <v>4510001</v>
+      </c>
+      <c r="G146" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="146" spans="1:12">
-      <c r="A146">
-        <v>60300002</v>
-      </c>
-      <c r="B146">
-        <v>3</v>
-      </c>
-      <c r="D146">
-        <v>1</v>
-      </c>
-      <c r="E146">
-        <v>6</v>
-      </c>
-      <c r="F146">
-        <v>6520002</v>
-      </c>
-      <c r="G146" t="s">
+      <c r="K146">
+        <v>40200001</v>
+      </c>
+      <c r="L146" t="s">
         <v>313</v>
-      </c>
-      <c r="K146">
-        <v>60300002</v>
-      </c>
-      <c r="L146" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="147" spans="1:12">
       <c r="A147">
-        <v>60300003</v>
+        <v>40200002</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D147">
         <v>1</v>
       </c>
       <c r="E147">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F147">
-        <v>6520003</v>
+        <v>4510002</v>
       </c>
       <c r="G147" t="s">
+        <v>314</v>
+      </c>
+      <c r="K147">
+        <v>40200002</v>
+      </c>
+      <c r="L147" t="s">
         <v>315</v>
-      </c>
-      <c r="K147">
-        <v>60300003</v>
-      </c>
-      <c r="L147" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="148" spans="1:12">
       <c r="A148">
-        <v>60300004</v>
+        <v>40200003</v>
       </c>
       <c r="B148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F148">
-        <v>6520004</v>
+        <v>4510003</v>
       </c>
       <c r="G148" t="s">
+        <v>316</v>
+      </c>
+      <c r="K148">
+        <v>40200003</v>
+      </c>
+      <c r="L148" t="s">
         <v>317</v>
-      </c>
-      <c r="K148">
-        <v>60300004</v>
-      </c>
-      <c r="L148" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="149" spans="1:12">
       <c r="A149">
-        <v>60300005</v>
+        <v>40200004</v>
       </c>
       <c r="B149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F149">
-        <v>6520005</v>
+        <v>4510004</v>
       </c>
       <c r="G149" t="s">
+        <v>318</v>
+      </c>
+      <c r="K149">
+        <v>40200004</v>
+      </c>
+      <c r="L149" t="s">
         <v>319</v>
       </c>
-      <c r="K149">
-        <v>60300005</v>
-      </c>
-      <c r="L149" t="s">
+    </row>
+    <row r="150" spans="1:12">
+      <c r="A150">
+        <v>40200005</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="D150">
+        <v>1</v>
+      </c>
+      <c r="E150">
+        <v>4</v>
+      </c>
+      <c r="F150">
+        <v>4510005</v>
+      </c>
+      <c r="G150" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="150" customFormat="1" spans="1:12">
-      <c r="A150">
-        <v>61010001</v>
-      </c>
-      <c r="B150">
-        <v>10</v>
-      </c>
-      <c r="C150">
-        <v>2</v>
-      </c>
-      <c r="D150">
-        <v>1</v>
-      </c>
-      <c r="E150">
-        <v>6</v>
-      </c>
-      <c r="F150">
-        <v>6910001</v>
-      </c>
-      <c r="G150" t="s">
+      <c r="K150">
+        <v>40200005</v>
+      </c>
+      <c r="L150" t="s">
         <v>321</v>
-      </c>
-      <c r="H150"/>
-      <c r="K150">
-        <v>61010001</v>
-      </c>
-      <c r="L150" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="151" spans="1:12">
       <c r="A151">
-        <v>61010002</v>
+        <v>40200006</v>
       </c>
       <c r="B151">
-        <v>10</v>
-      </c>
-      <c r="C151">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D151">
         <v>1</v>
       </c>
       <c r="E151">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F151">
-        <v>6910002</v>
+        <v>4510006</v>
       </c>
       <c r="G151" t="s">
+        <v>322</v>
+      </c>
+      <c r="K151">
+        <v>40200006</v>
+      </c>
+      <c r="L151" t="s">
         <v>323</v>
-      </c>
-      <c r="I151" t="s">
-        <v>324</v>
-      </c>
-      <c r="K151">
-        <v>61010002</v>
-      </c>
-      <c r="L151" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="152" spans="1:12">
       <c r="A152">
-        <v>61010003</v>
+        <v>40300001</v>
       </c>
       <c r="B152">
-        <v>10</v>
-      </c>
-      <c r="C152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
       <c r="E152">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F152">
-        <v>6910003</v>
+        <v>4520001</v>
       </c>
       <c r="G152" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="K152">
-        <v>61010003</v>
+        <v>40300001</v>
       </c>
       <c r="L152" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="153" spans="1:12">
       <c r="A153">
-        <v>61010004</v>
+        <v>40300002</v>
       </c>
       <c r="B153">
-        <v>10</v>
-      </c>
-      <c r="C153">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153">
         <v>1</v>
       </c>
       <c r="E153">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F153">
-        <v>6910004</v>
+        <v>4520002</v>
       </c>
       <c r="G153" t="s">
-        <v>328</v>
-      </c>
-      <c r="H153">
-        <v>-45</v>
+        <v>326</v>
       </c>
       <c r="K153">
-        <v>61010004</v>
+        <v>40300002</v>
       </c>
       <c r="L153" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="154" spans="1:12">
       <c r="A154">
-        <v>61010005</v>
+        <v>40300003</v>
       </c>
       <c r="B154">
-        <v>10</v>
-      </c>
-      <c r="C154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D154">
         <v>1</v>
       </c>
       <c r="E154">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F154">
-        <v>6910005</v>
+        <v>4520003</v>
       </c>
       <c r="G154" t="s">
-        <v>330</v>
-      </c>
-      <c r="H154">
-        <v>-45</v>
+        <v>328</v>
       </c>
       <c r="K154">
-        <v>61010005</v>
+        <v>40300003</v>
       </c>
       <c r="L154" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="155" spans="1:12">
       <c r="A155">
-        <v>61010006</v>
+        <v>40300004</v>
       </c>
       <c r="B155">
-        <v>10</v>
-      </c>
-      <c r="C155">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F155">
-        <v>6910006</v>
+        <v>4520004</v>
       </c>
       <c r="G155" t="s">
-        <v>332</v>
-      </c>
-      <c r="H155">
-        <v>-45</v>
+        <v>330</v>
       </c>
       <c r="K155">
-        <v>61010006</v>
+        <v>40300004</v>
       </c>
       <c r="L155" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="156" spans="1:12">
       <c r="A156">
-        <v>61010007</v>
+        <v>41000001</v>
       </c>
       <c r="B156">
         <v>10</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F156">
-        <v>6910007</v>
+        <v>4900001</v>
       </c>
       <c r="G156" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K156">
-        <v>61010007</v>
+        <v>41000001</v>
       </c>
       <c r="L156" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="157" spans="1:12">
       <c r="A157">
-        <v>61010008</v>
+        <v>41000002</v>
       </c>
       <c r="B157">
         <v>10</v>
       </c>
       <c r="C157">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D157">
         <v>1</v>
       </c>
       <c r="E157">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F157">
-        <v>6910008</v>
+        <v>4900002</v>
       </c>
       <c r="G157" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="K157">
-        <v>61010008</v>
+        <v>41000002</v>
       </c>
       <c r="L157" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="158" spans="1:12">
       <c r="A158">
-        <v>61010009</v>
+        <v>41000003</v>
       </c>
       <c r="B158">
         <v>10</v>
@@ -6547,24 +6766,24 @@
         <v>1</v>
       </c>
       <c r="E158">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F158">
-        <v>6910009</v>
+        <v>4900003</v>
       </c>
       <c r="G158" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K158">
-        <v>61010009</v>
+        <v>41000003</v>
       </c>
       <c r="L158" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159">
-        <v>61010010</v>
+        <v>41000004</v>
       </c>
       <c r="B159">
         <v>10</v>
@@ -6576,24 +6795,24 @@
         <v>1</v>
       </c>
       <c r="E159">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F159">
-        <v>6910010</v>
+        <v>4900004</v>
       </c>
       <c r="G159" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="K159">
-        <v>61010010</v>
+        <v>41000004</v>
       </c>
       <c r="L159" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="160" spans="1:12">
       <c r="A160">
-        <v>61010011</v>
+        <v>41000005</v>
       </c>
       <c r="B160">
         <v>10</v>
@@ -6605,503 +6824,476 @@
         <v>1</v>
       </c>
       <c r="E160">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F160">
-        <v>6910011</v>
+        <v>4900005</v>
       </c>
       <c r="G160" t="s">
+        <v>340</v>
+      </c>
+      <c r="K160">
+        <v>41000005</v>
+      </c>
+      <c r="L160" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" spans="1:12">
+      <c r="A161">
+        <v>50100001</v>
+      </c>
+      <c r="B161">
+        <v>1</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+      <c r="E161">
+        <v>5</v>
+      </c>
+      <c r="F161">
+        <v>5500001</v>
+      </c>
+      <c r="G161" t="s">
         <v>342</v>
       </c>
-      <c r="K160">
-        <v>61010011</v>
-      </c>
-      <c r="L160" t="s">
+      <c r="K161">
+        <v>50100001</v>
+      </c>
+      <c r="L161" t="s">
         <v>343</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12">
-      <c r="A161">
-        <v>61010012</v>
-      </c>
-      <c r="B161">
-        <v>10</v>
-      </c>
-      <c r="C161">
-        <v>2</v>
-      </c>
-      <c r="D161">
-        <v>1</v>
-      </c>
-      <c r="E161">
-        <v>6</v>
-      </c>
-      <c r="F161">
-        <v>6910012</v>
-      </c>
-      <c r="G161" t="s">
-        <v>344</v>
-      </c>
-      <c r="K161">
-        <v>61010012</v>
-      </c>
-      <c r="L161" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="162" spans="1:12">
       <c r="A162">
-        <v>61010013</v>
+        <v>50100002</v>
       </c>
       <c r="B162">
-        <v>10</v>
-      </c>
-      <c r="C162">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F162">
-        <v>6910013</v>
+        <v>5500002</v>
       </c>
       <c r="G162" t="s">
-        <v>346</v>
-      </c>
-      <c r="I162" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="K162">
-        <v>61010013</v>
+        <v>50100002</v>
       </c>
       <c r="L162" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="163" spans="1:12">
       <c r="A163">
-        <v>61010014</v>
+        <v>50100003</v>
       </c>
       <c r="B163">
-        <v>10</v>
-      </c>
-      <c r="C163">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F163">
-        <v>6910014</v>
+        <v>5500003</v>
       </c>
       <c r="G163" t="s">
+        <v>346</v>
+      </c>
+      <c r="K163">
+        <v>50100003</v>
+      </c>
+      <c r="L163" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" spans="1:12">
+      <c r="A164">
+        <v>50200001</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+      <c r="E164">
+        <v>5</v>
+      </c>
+      <c r="F164">
+        <v>5510001</v>
+      </c>
+      <c r="G164" t="s">
         <v>348</v>
       </c>
-      <c r="I163" t="s">
-        <v>324</v>
-      </c>
-      <c r="K163">
-        <v>61010014</v>
-      </c>
-      <c r="L163" t="s">
+      <c r="K164">
+        <v>50200001</v>
+      </c>
+      <c r="L164" t="s">
         <v>349</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12">
-      <c r="A164">
-        <v>61010015</v>
-      </c>
-      <c r="B164">
-        <v>10</v>
-      </c>
-      <c r="C164">
-        <v>7</v>
-      </c>
-      <c r="D164">
-        <v>1</v>
-      </c>
-      <c r="E164">
-        <v>6</v>
-      </c>
-      <c r="F164">
-        <v>6910015</v>
-      </c>
-      <c r="G164" t="s">
-        <v>350</v>
-      </c>
-      <c r="I164" t="s">
-        <v>324</v>
-      </c>
-      <c r="K164">
-        <v>61010015</v>
-      </c>
-      <c r="L164" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="165" spans="1:12">
       <c r="A165">
-        <v>61010016</v>
+        <v>50200002</v>
       </c>
       <c r="B165">
-        <v>10</v>
-      </c>
-      <c r="C165">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D165">
         <v>1</v>
       </c>
       <c r="E165">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F165">
-        <v>6910016</v>
+        <v>5510002</v>
       </c>
       <c r="G165" t="s">
-        <v>352</v>
-      </c>
-      <c r="I165" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="K165">
-        <v>61010016</v>
+        <v>50200002</v>
       </c>
       <c r="L165" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="166" spans="1:12">
       <c r="A166">
-        <v>61010017</v>
+        <v>50200003</v>
       </c>
       <c r="B166">
-        <v>10</v>
-      </c>
-      <c r="C166">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D166">
         <v>1</v>
       </c>
       <c r="E166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F166">
-        <v>6910017</v>
+        <v>5510003</v>
       </c>
       <c r="G166" t="s">
+        <v>352</v>
+      </c>
+      <c r="K166">
+        <v>50200003</v>
+      </c>
+      <c r="L166" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" ht="12" customHeight="1" spans="1:12">
+      <c r="A167">
+        <v>50300001</v>
+      </c>
+      <c r="B167">
+        <v>3</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+      <c r="E167">
+        <v>5</v>
+      </c>
+      <c r="F167">
+        <v>5520001</v>
+      </c>
+      <c r="G167" t="s">
         <v>354</v>
       </c>
-      <c r="K166">
-        <v>61010017</v>
-      </c>
-      <c r="L166" t="s">
+      <c r="K167">
+        <v>50300001</v>
+      </c>
+      <c r="L167" t="s">
         <v>355</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12">
-      <c r="A167">
-        <v>61010018</v>
-      </c>
-      <c r="B167">
-        <v>10</v>
-      </c>
-      <c r="C167">
-        <v>8</v>
-      </c>
-      <c r="D167">
-        <v>1</v>
-      </c>
-      <c r="E167">
-        <v>6</v>
-      </c>
-      <c r="F167">
-        <v>6910018</v>
-      </c>
-      <c r="G167" t="s">
-        <v>356</v>
-      </c>
-      <c r="K167">
-        <v>61010018</v>
-      </c>
-      <c r="L167" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="168" spans="1:12">
       <c r="A168">
-        <v>61010019</v>
+        <v>50300002</v>
       </c>
       <c r="B168">
-        <v>10</v>
-      </c>
-      <c r="C168">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D168">
         <v>1</v>
       </c>
       <c r="E168">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F168">
-        <v>6910019</v>
+        <v>5520002</v>
       </c>
       <c r="G168" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K168">
-        <v>61010019</v>
+        <v>50300002</v>
       </c>
       <c r="L168" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="169" spans="1:12">
       <c r="A169">
-        <v>61010020</v>
+        <v>50500001</v>
       </c>
       <c r="B169">
-        <v>10</v>
-      </c>
-      <c r="C169">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D169">
         <v>1</v>
       </c>
       <c r="E169">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F169">
-        <v>6910020</v>
+        <v>5090001</v>
       </c>
       <c r="G169" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K169">
-        <v>61010020</v>
+        <v>50500001</v>
       </c>
       <c r="L169" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="170" spans="1:12">
       <c r="A170">
-        <v>70100001</v>
+        <v>50500002</v>
       </c>
       <c r="B170">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F170">
-        <v>7500001</v>
+        <v>5090002</v>
       </c>
       <c r="G170" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="K170">
-        <v>70100001</v>
+        <v>50500002</v>
       </c>
       <c r="L170" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="171" spans="1:12">
       <c r="A171">
-        <v>70200001</v>
+        <v>50500003</v>
       </c>
       <c r="B171">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F171">
-        <v>7510001</v>
+        <v>5090003</v>
       </c>
       <c r="G171" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K171">
-        <v>70200001</v>
+        <v>50500003</v>
       </c>
       <c r="L171" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="172" spans="1:12">
       <c r="A172">
-        <v>70200002</v>
+        <v>50500004</v>
       </c>
       <c r="B172">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D172">
         <v>1</v>
       </c>
       <c r="E172">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F172">
-        <v>7510002</v>
+        <v>5090004</v>
       </c>
       <c r="G172" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K172">
-        <v>70200002</v>
+        <v>50500004</v>
       </c>
       <c r="L172" t="s">
-        <v>264</v>
+        <v>365</v>
       </c>
     </row>
     <row r="173" spans="1:12">
       <c r="A173">
-        <v>70300001</v>
+        <v>50500005</v>
       </c>
       <c r="B173">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F173">
-        <v>7520001</v>
+        <v>5090005</v>
       </c>
       <c r="G173" t="s">
+        <v>366</v>
+      </c>
+      <c r="K173">
+        <v>50500005</v>
+      </c>
+      <c r="L173" t="s">
         <v>367</v>
       </c>
-      <c r="K173">
-        <v>70300001</v>
-      </c>
-      <c r="L173" t="s">
+    </row>
+    <row r="174" customFormat="1" spans="1:12">
+      <c r="A174">
+        <v>51010001</v>
+      </c>
+      <c r="B174">
+        <v>10</v>
+      </c>
+      <c r="C174">
+        <v>8</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174">
+        <v>5</v>
+      </c>
+      <c r="F174">
+        <v>5910001</v>
+      </c>
+      <c r="G174" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="174" spans="1:12">
-      <c r="A174">
-        <v>70300002</v>
-      </c>
-      <c r="B174">
-        <v>3</v>
-      </c>
-      <c r="D174">
-        <v>1</v>
-      </c>
-      <c r="E174">
-        <v>7</v>
-      </c>
-      <c r="F174">
-        <v>7520002</v>
-      </c>
-      <c r="G174" t="s">
+      <c r="I174" t="s">
         <v>369</v>
       </c>
       <c r="K174">
-        <v>70300002</v>
+        <v>51010001</v>
       </c>
       <c r="L174" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="175" spans="1:12">
+    <row r="175" customFormat="1" spans="1:12">
       <c r="A175">
-        <v>70300003</v>
+        <v>51010002</v>
       </c>
       <c r="B175">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C175">
+        <v>8</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F175">
-        <v>7520003</v>
+        <v>5910002</v>
       </c>
       <c r="G175" t="s">
         <v>371</v>
       </c>
+      <c r="I175" t="s">
+        <v>372</v>
+      </c>
       <c r="K175">
-        <v>70300003</v>
+        <v>51010002</v>
       </c>
       <c r="L175" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176" customFormat="1" spans="1:12">
       <c r="A176">
-        <v>70300004</v>
+        <v>51010003</v>
       </c>
       <c r="B176">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C176">
+        <v>8</v>
       </c>
       <c r="D176">
         <v>1</v>
       </c>
       <c r="E176">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F176">
-        <v>7520004</v>
+        <v>5910003</v>
       </c>
       <c r="G176" t="s">
         <v>373</v>
       </c>
+      <c r="I176" t="s">
+        <v>374</v>
+      </c>
       <c r="K176">
-        <v>70300004</v>
+        <v>51010003</v>
       </c>
       <c r="L176" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="177" customFormat="1" spans="1:12">
       <c r="A177">
-        <v>71000001</v>
+        <v>60100001</v>
       </c>
       <c r="B177">
-        <v>10</v>
-      </c>
-      <c r="C177">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D177">
         <v>1</v>
       </c>
       <c r="E177">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F177">
-        <v>7900001</v>
+        <v>6500001</v>
       </c>
       <c r="G177" t="s">
-        <v>375</v>
-      </c>
-      <c r="I177" t="s">
         <v>376</v>
       </c>
       <c r="K177">
-        <v>71000001</v>
+        <v>60100001</v>
       </c>
       <c r="L177" t="s">
         <v>377</v>
@@ -7109,240 +7301,1475 @@
     </row>
     <row r="178" spans="1:12">
       <c r="A178">
-        <v>71000002</v>
+        <v>60100002</v>
       </c>
       <c r="B178">
-        <v>10</v>
-      </c>
-      <c r="C178">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D178">
         <v>1</v>
       </c>
       <c r="E178">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F178">
-        <v>7900002</v>
+        <v>6500002</v>
       </c>
       <c r="G178" t="s">
         <v>378</v>
       </c>
-      <c r="I178" t="s">
+      <c r="K178">
+        <v>60100002</v>
+      </c>
+      <c r="L178" t="s">
         <v>379</v>
-      </c>
-      <c r="K178">
-        <v>71000002</v>
-      </c>
-      <c r="L178" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="179" spans="1:12">
       <c r="A179">
-        <v>71000003</v>
+        <v>60100003</v>
       </c>
       <c r="B179">
-        <v>10</v>
-      </c>
-      <c r="C179">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F179">
-        <v>7900003</v>
+        <v>6500003</v>
       </c>
       <c r="G179" t="s">
+        <v>380</v>
+      </c>
+      <c r="K179">
+        <v>60100003</v>
+      </c>
+      <c r="L179" t="s">
         <v>381</v>
-      </c>
-      <c r="I179" t="s">
-        <v>382</v>
-      </c>
-      <c r="K179">
-        <v>71000003</v>
-      </c>
-      <c r="L179" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="180" spans="1:12">
       <c r="A180">
-        <v>71010001</v>
+        <v>60100004</v>
       </c>
       <c r="B180">
-        <v>10</v>
-      </c>
-      <c r="C180">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D180">
         <v>1</v>
       </c>
       <c r="E180">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F180">
-        <v>7910001</v>
+        <v>6500004</v>
       </c>
       <c r="G180" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="K180">
-        <v>71010001</v>
+        <v>60100004</v>
       </c>
       <c r="L180" t="s">
-        <v>385</v>
+        <v>343</v>
       </c>
     </row>
     <row r="181" spans="1:12">
       <c r="A181">
+        <v>60100005</v>
+      </c>
+      <c r="B181">
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
+      <c r="E181">
+        <v>6</v>
+      </c>
+      <c r="F181">
+        <v>6500005</v>
+      </c>
+      <c r="G181" t="s">
+        <v>383</v>
+      </c>
+      <c r="K181">
+        <v>60100005</v>
+      </c>
+      <c r="L181" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="182" ht="12" customHeight="1" spans="1:12">
+      <c r="A182">
+        <v>60100006</v>
+      </c>
+      <c r="B182">
+        <v>1</v>
+      </c>
+      <c r="D182">
+        <v>1</v>
+      </c>
+      <c r="E182">
+        <v>6</v>
+      </c>
+      <c r="F182">
+        <v>6500006</v>
+      </c>
+      <c r="G182" t="s">
+        <v>385</v>
+      </c>
+      <c r="K182">
+        <v>60100006</v>
+      </c>
+      <c r="L182" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="183" ht="12" customHeight="1" spans="1:12">
+      <c r="A183">
+        <v>60100007</v>
+      </c>
+      <c r="B183">
+        <v>1</v>
+      </c>
+      <c r="D183">
+        <v>1</v>
+      </c>
+      <c r="E183">
+        <v>6</v>
+      </c>
+      <c r="F183">
+        <v>6500007</v>
+      </c>
+      <c r="G183" t="s">
+        <v>387</v>
+      </c>
+      <c r="K183">
+        <v>60100007</v>
+      </c>
+      <c r="L183" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="184" ht="12" customHeight="1" spans="1:12">
+      <c r="A184">
+        <v>60100008</v>
+      </c>
+      <c r="B184">
+        <v>1</v>
+      </c>
+      <c r="D184">
+        <v>1</v>
+      </c>
+      <c r="E184">
+        <v>6</v>
+      </c>
+      <c r="F184">
+        <v>6500008</v>
+      </c>
+      <c r="G184" t="s">
+        <v>389</v>
+      </c>
+      <c r="K184">
+        <v>60100008</v>
+      </c>
+      <c r="L184" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="185" ht="12" customHeight="1" spans="1:12">
+      <c r="A185">
+        <v>60100009</v>
+      </c>
+      <c r="B185">
+        <v>1</v>
+      </c>
+      <c r="D185">
+        <v>1</v>
+      </c>
+      <c r="E185">
+        <v>6</v>
+      </c>
+      <c r="F185">
+        <v>6500009</v>
+      </c>
+      <c r="G185" t="s">
+        <v>391</v>
+      </c>
+      <c r="K185">
+        <v>60100009</v>
+      </c>
+      <c r="L185" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="186" ht="12" customHeight="1" spans="1:12">
+      <c r="A186">
+        <v>60100010</v>
+      </c>
+      <c r="B186">
+        <v>1</v>
+      </c>
+      <c r="D186">
+        <v>1</v>
+      </c>
+      <c r="E186">
+        <v>6</v>
+      </c>
+      <c r="F186">
+        <v>6500010</v>
+      </c>
+      <c r="G186" t="s">
+        <v>393</v>
+      </c>
+      <c r="K186">
+        <v>60100010</v>
+      </c>
+      <c r="L186" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="187" customFormat="1" ht="12" customHeight="1" spans="1:12">
+      <c r="A187">
+        <v>60200001</v>
+      </c>
+      <c r="B187">
+        <v>2</v>
+      </c>
+      <c r="D187">
+        <v>1</v>
+      </c>
+      <c r="E187">
+        <v>6</v>
+      </c>
+      <c r="F187">
+        <v>6510001</v>
+      </c>
+      <c r="G187" t="s">
+        <v>395</v>
+      </c>
+      <c r="K187">
+        <v>60200001</v>
+      </c>
+      <c r="L187" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="188" ht="12" customHeight="1" spans="1:12">
+      <c r="A188">
+        <v>60200002</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="D188">
+        <v>1</v>
+      </c>
+      <c r="E188">
+        <v>6</v>
+      </c>
+      <c r="F188">
+        <v>6510002</v>
+      </c>
+      <c r="G188" t="s">
+        <v>396</v>
+      </c>
+      <c r="K188">
+        <v>60200002</v>
+      </c>
+      <c r="L188" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="189" customFormat="1" spans="1:12">
+      <c r="A189">
+        <v>60300001</v>
+      </c>
+      <c r="B189">
+        <v>3</v>
+      </c>
+      <c r="D189">
+        <v>1</v>
+      </c>
+      <c r="E189">
+        <v>6</v>
+      </c>
+      <c r="F189">
+        <v>6520001</v>
+      </c>
+      <c r="G189" t="s">
+        <v>398</v>
+      </c>
+      <c r="K189">
+        <v>60300001</v>
+      </c>
+      <c r="L189" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12">
+      <c r="A190">
+        <v>60300002</v>
+      </c>
+      <c r="B190">
+        <v>3</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190">
+        <v>6</v>
+      </c>
+      <c r="F190">
+        <v>6520002</v>
+      </c>
+      <c r="G190" t="s">
+        <v>400</v>
+      </c>
+      <c r="K190">
+        <v>60300002</v>
+      </c>
+      <c r="L190" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12">
+      <c r="A191">
+        <v>60300003</v>
+      </c>
+      <c r="B191">
+        <v>3</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="E191">
+        <v>6</v>
+      </c>
+      <c r="F191">
+        <v>6520003</v>
+      </c>
+      <c r="G191" t="s">
+        <v>402</v>
+      </c>
+      <c r="K191">
+        <v>60300003</v>
+      </c>
+      <c r="L191" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12">
+      <c r="A192">
+        <v>60300004</v>
+      </c>
+      <c r="B192">
+        <v>3</v>
+      </c>
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="E192">
+        <v>6</v>
+      </c>
+      <c r="F192">
+        <v>6520004</v>
+      </c>
+      <c r="G192" t="s">
+        <v>404</v>
+      </c>
+      <c r="K192">
+        <v>60300004</v>
+      </c>
+      <c r="L192" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12">
+      <c r="A193">
+        <v>60300005</v>
+      </c>
+      <c r="B193">
+        <v>3</v>
+      </c>
+      <c r="D193">
+        <v>1</v>
+      </c>
+      <c r="E193">
+        <v>6</v>
+      </c>
+      <c r="F193">
+        <v>6520005</v>
+      </c>
+      <c r="G193" t="s">
+        <v>406</v>
+      </c>
+      <c r="K193">
+        <v>60300005</v>
+      </c>
+      <c r="L193" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="194" customFormat="1" spans="1:12">
+      <c r="A194">
+        <v>61010001</v>
+      </c>
+      <c r="B194">
+        <v>10</v>
+      </c>
+      <c r="C194">
+        <v>2</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194">
+        <v>6</v>
+      </c>
+      <c r="F194">
+        <v>6910001</v>
+      </c>
+      <c r="G194" t="s">
+        <v>408</v>
+      </c>
+      <c r="H194"/>
+      <c r="K194">
+        <v>61010001</v>
+      </c>
+      <c r="L194" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12">
+      <c r="A195">
+        <v>61010002</v>
+      </c>
+      <c r="B195">
+        <v>10</v>
+      </c>
+      <c r="C195">
+        <v>7</v>
+      </c>
+      <c r="D195">
+        <v>1</v>
+      </c>
+      <c r="E195">
+        <v>6</v>
+      </c>
+      <c r="F195">
+        <v>6910002</v>
+      </c>
+      <c r="G195" t="s">
+        <v>410</v>
+      </c>
+      <c r="I195" t="s">
+        <v>411</v>
+      </c>
+      <c r="K195">
+        <v>61010002</v>
+      </c>
+      <c r="L195" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12">
+      <c r="A196">
+        <v>61010003</v>
+      </c>
+      <c r="B196">
+        <v>10</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="D196">
+        <v>1</v>
+      </c>
+      <c r="E196">
+        <v>6</v>
+      </c>
+      <c r="F196">
+        <v>6910003</v>
+      </c>
+      <c r="G196" t="s">
+        <v>412</v>
+      </c>
+      <c r="K196">
+        <v>61010003</v>
+      </c>
+      <c r="L196" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12">
+      <c r="A197">
+        <v>61010004</v>
+      </c>
+      <c r="B197">
+        <v>10</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197">
+        <v>1</v>
+      </c>
+      <c r="E197">
+        <v>6</v>
+      </c>
+      <c r="F197">
+        <v>6910004</v>
+      </c>
+      <c r="G197" t="s">
+        <v>414</v>
+      </c>
+      <c r="H197">
+        <v>-45</v>
+      </c>
+      <c r="K197">
+        <v>61010004</v>
+      </c>
+      <c r="L197" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12">
+      <c r="A198">
+        <v>61010005</v>
+      </c>
+      <c r="B198">
+        <v>10</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
+      </c>
+      <c r="D198">
+        <v>1</v>
+      </c>
+      <c r="E198">
+        <v>6</v>
+      </c>
+      <c r="F198">
+        <v>6910005</v>
+      </c>
+      <c r="G198" t="s">
+        <v>416</v>
+      </c>
+      <c r="H198">
+        <v>-45</v>
+      </c>
+      <c r="K198">
+        <v>61010005</v>
+      </c>
+      <c r="L198" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12">
+      <c r="A199">
+        <v>61010006</v>
+      </c>
+      <c r="B199">
+        <v>10</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199">
+        <v>1</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199">
+        <v>6910006</v>
+      </c>
+      <c r="G199" t="s">
+        <v>418</v>
+      </c>
+      <c r="H199">
+        <v>-45</v>
+      </c>
+      <c r="K199">
+        <v>61010006</v>
+      </c>
+      <c r="L199" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12">
+      <c r="A200">
+        <v>61010007</v>
+      </c>
+      <c r="B200">
+        <v>10</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200">
+        <v>1</v>
+      </c>
+      <c r="E200">
+        <v>6</v>
+      </c>
+      <c r="F200">
+        <v>6910007</v>
+      </c>
+      <c r="G200" t="s">
+        <v>420</v>
+      </c>
+      <c r="K200">
+        <v>61010007</v>
+      </c>
+      <c r="L200" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12">
+      <c r="A201">
+        <v>61010008</v>
+      </c>
+      <c r="B201">
+        <v>10</v>
+      </c>
+      <c r="C201">
+        <v>8</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
+      </c>
+      <c r="E201">
+        <v>6</v>
+      </c>
+      <c r="F201">
+        <v>6910008</v>
+      </c>
+      <c r="G201" t="s">
+        <v>422</v>
+      </c>
+      <c r="K201">
+        <v>61010008</v>
+      </c>
+      <c r="L201" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12">
+      <c r="A202">
+        <v>61010009</v>
+      </c>
+      <c r="B202">
+        <v>10</v>
+      </c>
+      <c r="C202">
+        <v>2</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202">
+        <v>6</v>
+      </c>
+      <c r="F202">
+        <v>6910009</v>
+      </c>
+      <c r="G202" t="s">
+        <v>424</v>
+      </c>
+      <c r="K202">
+        <v>61010009</v>
+      </c>
+      <c r="L202" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12">
+      <c r="A203">
+        <v>61010010</v>
+      </c>
+      <c r="B203">
+        <v>10</v>
+      </c>
+      <c r="C203">
+        <v>2</v>
+      </c>
+      <c r="D203">
+        <v>1</v>
+      </c>
+      <c r="E203">
+        <v>6</v>
+      </c>
+      <c r="F203">
+        <v>6910010</v>
+      </c>
+      <c r="G203" t="s">
+        <v>425</v>
+      </c>
+      <c r="K203">
+        <v>61010010</v>
+      </c>
+      <c r="L203" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12">
+      <c r="A204">
+        <v>61010011</v>
+      </c>
+      <c r="B204">
+        <v>10</v>
+      </c>
+      <c r="C204">
+        <v>2</v>
+      </c>
+      <c r="D204">
+        <v>1</v>
+      </c>
+      <c r="E204">
+        <v>6</v>
+      </c>
+      <c r="F204">
+        <v>6910011</v>
+      </c>
+      <c r="G204" t="s">
+        <v>427</v>
+      </c>
+      <c r="K204">
+        <v>61010011</v>
+      </c>
+      <c r="L204" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12">
+      <c r="A205">
+        <v>61010012</v>
+      </c>
+      <c r="B205">
+        <v>10</v>
+      </c>
+      <c r="C205">
+        <v>2</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+      <c r="E205">
+        <v>6</v>
+      </c>
+      <c r="F205">
+        <v>6910012</v>
+      </c>
+      <c r="G205" t="s">
+        <v>429</v>
+      </c>
+      <c r="K205">
+        <v>61010012</v>
+      </c>
+      <c r="L205" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12">
+      <c r="A206">
+        <v>61010013</v>
+      </c>
+      <c r="B206">
+        <v>10</v>
+      </c>
+      <c r="C206">
+        <v>7</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+      <c r="E206">
+        <v>6</v>
+      </c>
+      <c r="F206">
+        <v>6910013</v>
+      </c>
+      <c r="G206" t="s">
+        <v>431</v>
+      </c>
+      <c r="I206" t="s">
+        <v>411</v>
+      </c>
+      <c r="K206">
+        <v>61010013</v>
+      </c>
+      <c r="L206" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12">
+      <c r="A207">
+        <v>61010014</v>
+      </c>
+      <c r="B207">
+        <v>10</v>
+      </c>
+      <c r="C207">
+        <v>7</v>
+      </c>
+      <c r="D207">
+        <v>1</v>
+      </c>
+      <c r="E207">
+        <v>6</v>
+      </c>
+      <c r="F207">
+        <v>6910014</v>
+      </c>
+      <c r="G207" t="s">
+        <v>433</v>
+      </c>
+      <c r="I207" t="s">
+        <v>411</v>
+      </c>
+      <c r="K207">
+        <v>61010014</v>
+      </c>
+      <c r="L207" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12">
+      <c r="A208">
+        <v>61010015</v>
+      </c>
+      <c r="B208">
+        <v>10</v>
+      </c>
+      <c r="C208">
+        <v>7</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+      <c r="E208">
+        <v>6</v>
+      </c>
+      <c r="F208">
+        <v>6910015</v>
+      </c>
+      <c r="G208" t="s">
+        <v>435</v>
+      </c>
+      <c r="I208" t="s">
+        <v>411</v>
+      </c>
+      <c r="K208">
+        <v>61010015</v>
+      </c>
+      <c r="L208" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12">
+      <c r="A209">
+        <v>61010016</v>
+      </c>
+      <c r="B209">
+        <v>10</v>
+      </c>
+      <c r="C209">
+        <v>7</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209">
+        <v>6</v>
+      </c>
+      <c r="F209">
+        <v>6910016</v>
+      </c>
+      <c r="G209" t="s">
+        <v>437</v>
+      </c>
+      <c r="I209" t="s">
+        <v>411</v>
+      </c>
+      <c r="K209">
+        <v>61010016</v>
+      </c>
+      <c r="L209" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12">
+      <c r="A210">
+        <v>61010017</v>
+      </c>
+      <c r="B210">
+        <v>10</v>
+      </c>
+      <c r="C210">
+        <v>8</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+      <c r="E210">
+        <v>6</v>
+      </c>
+      <c r="F210">
+        <v>6910017</v>
+      </c>
+      <c r="G210" t="s">
+        <v>439</v>
+      </c>
+      <c r="K210">
+        <v>61010017</v>
+      </c>
+      <c r="L210" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12">
+      <c r="A211">
+        <v>61010018</v>
+      </c>
+      <c r="B211">
+        <v>10</v>
+      </c>
+      <c r="C211">
+        <v>8</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+      <c r="E211">
+        <v>6</v>
+      </c>
+      <c r="F211">
+        <v>6910018</v>
+      </c>
+      <c r="G211" t="s">
+        <v>441</v>
+      </c>
+      <c r="K211">
+        <v>61010018</v>
+      </c>
+      <c r="L211" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12">
+      <c r="A212">
+        <v>61010019</v>
+      </c>
+      <c r="B212">
+        <v>10</v>
+      </c>
+      <c r="C212">
+        <v>8</v>
+      </c>
+      <c r="D212">
+        <v>1</v>
+      </c>
+      <c r="E212">
+        <v>6</v>
+      </c>
+      <c r="F212">
+        <v>6910019</v>
+      </c>
+      <c r="G212" t="s">
+        <v>443</v>
+      </c>
+      <c r="K212">
+        <v>61010019</v>
+      </c>
+      <c r="L212" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12">
+      <c r="A213">
+        <v>61010020</v>
+      </c>
+      <c r="B213">
+        <v>10</v>
+      </c>
+      <c r="C213">
+        <v>8</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+      <c r="E213">
+        <v>6</v>
+      </c>
+      <c r="F213">
+        <v>6910020</v>
+      </c>
+      <c r="G213" t="s">
+        <v>445</v>
+      </c>
+      <c r="K213">
+        <v>61010020</v>
+      </c>
+      <c r="L213" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12">
+      <c r="A214">
+        <v>70100001</v>
+      </c>
+      <c r="B214">
+        <v>1</v>
+      </c>
+      <c r="D214">
+        <v>1</v>
+      </c>
+      <c r="E214">
+        <v>7</v>
+      </c>
+      <c r="F214">
+        <v>7500001</v>
+      </c>
+      <c r="G214" t="s">
+        <v>447</v>
+      </c>
+      <c r="K214">
+        <v>70100001</v>
+      </c>
+      <c r="L214" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12">
+      <c r="A215">
+        <v>70200001</v>
+      </c>
+      <c r="B215">
+        <v>2</v>
+      </c>
+      <c r="D215">
+        <v>1</v>
+      </c>
+      <c r="E215">
+        <v>7</v>
+      </c>
+      <c r="F215">
+        <v>7510001</v>
+      </c>
+      <c r="G215" t="s">
+        <v>449</v>
+      </c>
+      <c r="K215">
+        <v>70200001</v>
+      </c>
+      <c r="L215" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12">
+      <c r="A216">
+        <v>70200002</v>
+      </c>
+      <c r="B216">
+        <v>2</v>
+      </c>
+      <c r="D216">
+        <v>1</v>
+      </c>
+      <c r="E216">
+        <v>7</v>
+      </c>
+      <c r="F216">
+        <v>7510002</v>
+      </c>
+      <c r="G216" t="s">
+        <v>451</v>
+      </c>
+      <c r="K216">
+        <v>70200002</v>
+      </c>
+      <c r="L216" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12">
+      <c r="A217">
+        <v>70300001</v>
+      </c>
+      <c r="B217">
+        <v>3</v>
+      </c>
+      <c r="D217">
+        <v>1</v>
+      </c>
+      <c r="E217">
+        <v>7</v>
+      </c>
+      <c r="F217">
+        <v>7520001</v>
+      </c>
+      <c r="G217" t="s">
+        <v>452</v>
+      </c>
+      <c r="K217">
+        <v>70300001</v>
+      </c>
+      <c r="L217" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12">
+      <c r="A218">
+        <v>70300002</v>
+      </c>
+      <c r="B218">
+        <v>3</v>
+      </c>
+      <c r="D218">
+        <v>1</v>
+      </c>
+      <c r="E218">
+        <v>7</v>
+      </c>
+      <c r="F218">
+        <v>7520002</v>
+      </c>
+      <c r="G218" t="s">
+        <v>454</v>
+      </c>
+      <c r="K218">
+        <v>70300002</v>
+      </c>
+      <c r="L218" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12">
+      <c r="A219">
+        <v>70300003</v>
+      </c>
+      <c r="B219">
+        <v>3</v>
+      </c>
+      <c r="D219">
+        <v>1</v>
+      </c>
+      <c r="E219">
+        <v>7</v>
+      </c>
+      <c r="F219">
+        <v>7520003</v>
+      </c>
+      <c r="G219" t="s">
+        <v>456</v>
+      </c>
+      <c r="K219">
+        <v>70300003</v>
+      </c>
+      <c r="L219" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12">
+      <c r="A220">
+        <v>70300004</v>
+      </c>
+      <c r="B220">
+        <v>3</v>
+      </c>
+      <c r="D220">
+        <v>1</v>
+      </c>
+      <c r="E220">
+        <v>7</v>
+      </c>
+      <c r="F220">
+        <v>7520004</v>
+      </c>
+      <c r="G220" t="s">
+        <v>458</v>
+      </c>
+      <c r="K220">
+        <v>70300004</v>
+      </c>
+      <c r="L220" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12">
+      <c r="A221">
+        <v>71000001</v>
+      </c>
+      <c r="B221">
+        <v>10</v>
+      </c>
+      <c r="C221">
+        <v>8</v>
+      </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+      <c r="E221">
+        <v>7</v>
+      </c>
+      <c r="F221">
+        <v>7900001</v>
+      </c>
+      <c r="G221" t="s">
+        <v>460</v>
+      </c>
+      <c r="I221" t="s">
+        <v>461</v>
+      </c>
+      <c r="K221">
+        <v>71000001</v>
+      </c>
+      <c r="L221" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12">
+      <c r="A222">
+        <v>71000002</v>
+      </c>
+      <c r="B222">
+        <v>10</v>
+      </c>
+      <c r="C222">
+        <v>8</v>
+      </c>
+      <c r="D222">
+        <v>1</v>
+      </c>
+      <c r="E222">
+        <v>7</v>
+      </c>
+      <c r="F222">
+        <v>7900002</v>
+      </c>
+      <c r="G222" t="s">
+        <v>463</v>
+      </c>
+      <c r="I222" t="s">
+        <v>464</v>
+      </c>
+      <c r="K222">
+        <v>71000002</v>
+      </c>
+      <c r="L222" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12">
+      <c r="A223">
+        <v>71000003</v>
+      </c>
+      <c r="B223">
+        <v>10</v>
+      </c>
+      <c r="C223">
+        <v>8</v>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223">
+        <v>7</v>
+      </c>
+      <c r="F223">
+        <v>7900003</v>
+      </c>
+      <c r="G223" t="s">
+        <v>466</v>
+      </c>
+      <c r="I223" t="s">
+        <v>467</v>
+      </c>
+      <c r="K223">
+        <v>71000003</v>
+      </c>
+      <c r="L223" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12">
+      <c r="A224">
+        <v>71010001</v>
+      </c>
+      <c r="B224">
+        <v>10</v>
+      </c>
+      <c r="C224">
+        <v>8</v>
+      </c>
+      <c r="D224">
+        <v>1</v>
+      </c>
+      <c r="E224">
+        <v>7</v>
+      </c>
+      <c r="F224">
+        <v>7910001</v>
+      </c>
+      <c r="G224" t="s">
+        <v>469</v>
+      </c>
+      <c r="K224">
+        <v>71010001</v>
+      </c>
+      <c r="L224" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12">
+      <c r="A225">
         <v>71010002</v>
       </c>
-      <c r="B181">
+      <c r="B225">
         <v>10</v>
       </c>
-      <c r="C181">
+      <c r="C225">
         <v>8</v>
       </c>
-      <c r="D181">
-        <v>1</v>
-      </c>
-      <c r="E181">
+      <c r="D225">
+        <v>1</v>
+      </c>
+      <c r="E225">
         <v>7</v>
       </c>
-      <c r="F181">
+      <c r="F225">
         <v>7910002</v>
       </c>
-      <c r="G181" t="s">
-        <v>386</v>
-      </c>
-      <c r="K181">
+      <c r="G225" t="s">
+        <v>471</v>
+      </c>
+      <c r="K225">
         <v>71010002</v>
       </c>
-      <c r="L181" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12">
-      <c r="A182">
+      <c r="L225" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12">
+      <c r="A226">
         <v>71010003</v>
       </c>
-      <c r="B182">
+      <c r="B226">
         <v>10</v>
       </c>
-      <c r="C182">
+      <c r="C226">
         <v>8</v>
       </c>
-      <c r="D182">
-        <v>1</v>
-      </c>
-      <c r="E182">
+      <c r="D226">
+        <v>1</v>
+      </c>
+      <c r="E226">
         <v>7</v>
       </c>
-      <c r="F182">
+      <c r="F226">
         <v>7910003</v>
       </c>
-      <c r="G182" t="s">
-        <v>388</v>
-      </c>
-      <c r="K182">
+      <c r="G226" t="s">
+        <v>473</v>
+      </c>
+      <c r="K226">
         <v>71010003</v>
       </c>
-      <c r="L182" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12">
-      <c r="A183">
+      <c r="L226" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12">
+      <c r="A227">
         <v>71010004</v>
       </c>
-      <c r="B183">
+      <c r="B227">
         <v>10</v>
       </c>
-      <c r="C183">
-        <v>1</v>
-      </c>
-      <c r="D183">
-        <v>1</v>
-      </c>
-      <c r="E183">
+      <c r="C227">
+        <v>1</v>
+      </c>
+      <c r="D227">
+        <v>1</v>
+      </c>
+      <c r="E227">
         <v>7</v>
       </c>
-      <c r="F183">
+      <c r="F227">
         <v>7910004</v>
       </c>
-      <c r="G183" t="s">
-        <v>390</v>
-      </c>
-      <c r="K183">
+      <c r="G227" t="s">
+        <v>475</v>
+      </c>
+      <c r="K227">
         <v>71010004</v>
       </c>
-      <c r="L183" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12">
-      <c r="A184">
+      <c r="L227" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12">
+      <c r="A228">
         <v>71010005</v>
       </c>
-      <c r="B184">
+      <c r="B228">
         <v>10</v>
       </c>
-      <c r="C184">
-        <v>1</v>
-      </c>
-      <c r="D184">
-        <v>1</v>
-      </c>
-      <c r="E184">
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228">
+        <v>1</v>
+      </c>
+      <c r="E228">
         <v>7</v>
       </c>
-      <c r="F184">
+      <c r="F228">
         <v>7910005</v>
       </c>
-      <c r="G184" t="s">
-        <v>392</v>
-      </c>
-      <c r="K184">
+      <c r="G228" t="s">
+        <v>477</v>
+      </c>
+      <c r="K228">
         <v>71010005</v>
       </c>
-      <c r="L184" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12">
-      <c r="A185">
+      <c r="L228" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12">
+      <c r="A229">
         <v>71010006</v>
       </c>
-      <c r="B185">
+      <c r="B229">
         <v>10</v>
       </c>
-      <c r="C185">
-        <v>1</v>
-      </c>
-      <c r="D185">
-        <v>1</v>
-      </c>
-      <c r="E185">
+      <c r="C229">
+        <v>1</v>
+      </c>
+      <c r="D229">
+        <v>1</v>
+      </c>
+      <c r="E229">
         <v>7</v>
       </c>
-      <c r="F185">
+      <c r="F229">
         <v>7910006</v>
       </c>
-      <c r="G185" t="s">
-        <v>394</v>
-      </c>
-      <c r="K185">
+      <c r="G229" t="s">
+        <v>479</v>
+      </c>
+      <c r="K229">
         <v>71010006</v>
       </c>
-      <c r="L185" t="s">
-        <v>395</v>
+      <c r="L229" t="s">
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="482">
   <si>
     <t>id</t>
   </si>
@@ -488,6 +488,9 @@
     <t>Human_Atlas_Weapon_Weapon_R_1</t>
   </si>
   <si>
+    <t>ShowSprite:Human_Atlas_Other_Arrow_1&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180</t>
+  </si>
+  <si>
     <t>木弓</t>
   </si>
   <si>
@@ -656,7 +659,7 @@
     <t>Skeleton_Atlas_Weapon_Weapon_L_1</t>
   </si>
   <si>
-    <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:10&amp;VertexRotateAxis:0,0,-1</t>
+    <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
   </si>
   <si>
     <t>骷髅-武器-骨头</t>
@@ -665,7 +668,7 @@
     <t>Skeleton_Atlas_Weapon_Weapon_L_2</t>
   </si>
   <si>
-    <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:10&amp;VertexRotateAxis:0,0,-1</t>
+    <t>ShowSprite:Skeleton_Atlas_Weapon_Weapon_L_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1</t>
   </si>
   <si>
     <t>骷髅-武器-鸡腿</t>
@@ -1136,7 +1139,7 @@
     <t>Minotaur_Atlas_Weapon_Weapon_R_1</t>
   </si>
   <si>
-    <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_1&amp;VertexRotateSpeed:5&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
+    <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_1&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
   </si>
   <si>
     <t>石头</t>
@@ -1145,13 +1148,13 @@
     <t>Minotaur_Atlas_Weapon_Weapon_R_2</t>
   </si>
   <si>
-    <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_2&amp;VertexRotateSpeed:5&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
+    <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_2&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
   </si>
   <si>
     <t>Minotaur_Atlas_Weapon_Weapon_R_3</t>
   </si>
   <si>
-    <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_3&amp;VertexRotateSpeed:5&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
+    <t>ShowSprite:Minotaur_Atlas_Weapon_Weapon_R_3&amp;VertexRotateSpeed:360&amp;VertexRotateAxis:0,0,-1&amp;StartSize:2</t>
   </si>
   <si>
     <t>宝箱</t>
@@ -2451,7 +2454,7 @@
     <col min="6" max="6" width="24.875" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="14.875" customWidth="1"/>
-    <col min="9" max="9" width="20.375" customWidth="1"/>
+    <col min="9" max="9" width="21.25" customWidth="1"/>
     <col min="10" max="10" width="14.875" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="12" width="42.875" customWidth="1"/>
@@ -4267,11 +4270,14 @@
       <c r="G67" t="s">
         <v>152</v>
       </c>
+      <c r="I67" t="s">
+        <v>153</v>
+      </c>
       <c r="K67">
         <v>11010001</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:12">
@@ -4294,13 +4300,16 @@
         <v>1910002</v>
       </c>
       <c r="G68" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="I68" t="s">
+        <v>153</v>
       </c>
       <c r="K68">
         <v>11010002</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:12">
@@ -4323,13 +4332,16 @@
         <v>1910003</v>
       </c>
       <c r="G69" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="I69" t="s">
+        <v>153</v>
       </c>
       <c r="K69">
         <v>11010003</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:12">
@@ -4352,13 +4364,13 @@
         <v>1920021</v>
       </c>
       <c r="G70" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K70">
         <v>11020021</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:12">
@@ -4381,13 +4393,13 @@
         <v>1920022</v>
       </c>
       <c r="G71" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K71">
         <v>11020022</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -4407,13 +4419,13 @@
         <v>2500001</v>
       </c>
       <c r="G72" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K72">
         <v>20100001</v>
       </c>
       <c r="L72" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -4433,13 +4445,13 @@
         <v>2500002</v>
       </c>
       <c r="G73" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K73">
         <v>20100002</v>
       </c>
       <c r="L73" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -4459,13 +4471,13 @@
         <v>2500003</v>
       </c>
       <c r="G74" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K74">
         <v>20100003</v>
       </c>
       <c r="L74" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -4485,13 +4497,13 @@
         <v>2500004</v>
       </c>
       <c r="G75" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K75">
         <v>20100004</v>
       </c>
       <c r="L75" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4511,13 +4523,13 @@
         <v>2500005</v>
       </c>
       <c r="G76" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K76">
         <v>20100005</v>
       </c>
       <c r="L76" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4537,13 +4549,13 @@
         <v>2500006</v>
       </c>
       <c r="G77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K77">
         <v>20100006</v>
       </c>
       <c r="L77" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4563,13 +4575,13 @@
         <v>2500007</v>
       </c>
       <c r="G78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K78">
         <v>20100007</v>
       </c>
       <c r="L78" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4589,13 +4601,13 @@
         <v>2510001</v>
       </c>
       <c r="G79" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K79">
         <v>20200001</v>
       </c>
       <c r="L79" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4615,13 +4627,13 @@
         <v>2510002</v>
       </c>
       <c r="G80" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K80">
         <v>20200002</v>
       </c>
       <c r="L80" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:12">
@@ -4641,13 +4653,13 @@
         <v>2510003</v>
       </c>
       <c r="G81" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K81">
         <v>20200003</v>
       </c>
       <c r="L81" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4667,13 +4679,13 @@
         <v>2510004</v>
       </c>
       <c r="G82" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K82">
         <v>20200004</v>
       </c>
       <c r="L82" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4693,13 +4705,13 @@
         <v>2510005</v>
       </c>
       <c r="G83" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K83">
         <v>20200005</v>
       </c>
       <c r="L83" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4719,13 +4731,13 @@
         <v>2510006</v>
       </c>
       <c r="G84" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K84">
         <v>20200006</v>
       </c>
       <c r="L84" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4745,13 +4757,13 @@
         <v>2510007</v>
       </c>
       <c r="G85" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K85">
         <v>20200007</v>
       </c>
       <c r="L85" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4771,13 +4783,13 @@
         <v>2510008</v>
       </c>
       <c r="G86" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K86">
         <v>20200008</v>
       </c>
       <c r="L86" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4797,13 +4809,13 @@
         <v>2510009</v>
       </c>
       <c r="G87" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K87">
         <v>20200009</v>
       </c>
       <c r="L87" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4823,13 +4835,13 @@
         <v>2510010</v>
       </c>
       <c r="G88" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K88">
         <v>20200010</v>
       </c>
       <c r="L88" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4849,13 +4861,13 @@
         <v>2510011</v>
       </c>
       <c r="G89" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K89">
         <v>20200011</v>
       </c>
       <c r="L89" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4875,13 +4887,13 @@
         <v>2520001</v>
       </c>
       <c r="G90" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K90">
         <v>20300001</v>
       </c>
       <c r="L90" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4901,13 +4913,13 @@
         <v>2520003</v>
       </c>
       <c r="G91" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K91">
         <v>20300003</v>
       </c>
       <c r="L91" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4927,13 +4939,13 @@
         <v>2520007</v>
       </c>
       <c r="G92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K92">
         <v>20300007</v>
       </c>
       <c r="L92" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4953,13 +4965,13 @@
         <v>2520009</v>
       </c>
       <c r="G93" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K93">
         <v>20300009</v>
       </c>
       <c r="L93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4979,13 +4991,13 @@
         <v>2520011</v>
       </c>
       <c r="G94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K94">
         <v>20300011</v>
       </c>
       <c r="L94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="95" ht="12" customHeight="1" spans="1:12">
@@ -5008,19 +5020,19 @@
         <v>2900001</v>
       </c>
       <c r="G95" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H95">
         <v>45</v>
       </c>
       <c r="I95" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K95">
         <v>21000001</v>
       </c>
       <c r="L95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -5043,19 +5055,19 @@
         <v>2900002</v>
       </c>
       <c r="G96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H96">
         <v>45</v>
       </c>
       <c r="I96" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K96">
         <v>21000002</v>
       </c>
       <c r="L96" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -5078,13 +5090,13 @@
         <v>2900003</v>
       </c>
       <c r="G97" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K97">
         <v>21000003</v>
       </c>
       <c r="L97" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -5107,13 +5119,13 @@
         <v>2900004</v>
       </c>
       <c r="G98" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K98">
         <v>21000004</v>
       </c>
       <c r="L98" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -5136,13 +5148,13 @@
         <v>2900005</v>
       </c>
       <c r="G99" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K99">
         <v>21000005</v>
       </c>
       <c r="L99" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -5165,13 +5177,13 @@
         <v>2900006</v>
       </c>
       <c r="G100" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K100">
         <v>21000006</v>
       </c>
       <c r="L100" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -5194,13 +5206,13 @@
         <v>2900007</v>
       </c>
       <c r="G101" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K101">
         <v>21000007</v>
       </c>
       <c r="L101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -5223,13 +5235,13 @@
         <v>2900008</v>
       </c>
       <c r="G102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K102">
         <v>21000008</v>
       </c>
       <c r="L102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -5252,13 +5264,13 @@
         <v>2900009</v>
       </c>
       <c r="G103" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K103">
         <v>21000009</v>
       </c>
       <c r="L103" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -5281,13 +5293,13 @@
         <v>2900010</v>
       </c>
       <c r="G104" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K104">
         <v>21000010</v>
       </c>
       <c r="L104" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -5310,7 +5322,7 @@
         <v>2910001</v>
       </c>
       <c r="G105" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H105">
         <v>-45</v>
@@ -5319,7 +5331,7 @@
         <v>21010001</v>
       </c>
       <c r="L105" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -5342,7 +5354,7 @@
         <v>2910002</v>
       </c>
       <c r="G106" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H106">
         <v>-45</v>
@@ -5351,7 +5363,7 @@
         <v>21010002</v>
       </c>
       <c r="L106" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -5374,7 +5386,7 @@
         <v>2910003</v>
       </c>
       <c r="G107" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H107">
         <v>-45</v>
@@ -5383,7 +5395,7 @@
         <v>21010003</v>
       </c>
       <c r="L107" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -5406,7 +5418,7 @@
         <v>2910004</v>
       </c>
       <c r="G108" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H108">
         <v>-45</v>
@@ -5415,7 +5427,7 @@
         <v>21010004</v>
       </c>
       <c r="L108" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -5438,13 +5450,13 @@
         <v>2910005</v>
       </c>
       <c r="G109" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K109">
         <v>21010005</v>
       </c>
       <c r="L109" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -5467,13 +5479,13 @@
         <v>2910006</v>
       </c>
       <c r="G110" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K110">
         <v>21010006</v>
       </c>
       <c r="L110" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -5496,13 +5508,13 @@
         <v>2910007</v>
       </c>
       <c r="G111" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K111">
         <v>21010007</v>
       </c>
       <c r="L111" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -5525,13 +5537,13 @@
         <v>2910008</v>
       </c>
       <c r="G112" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K112">
         <v>21010008</v>
       </c>
       <c r="L112" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -5554,13 +5566,13 @@
         <v>2910009</v>
       </c>
       <c r="G113" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K113">
         <v>21010009</v>
       </c>
       <c r="L113" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -5583,13 +5595,13 @@
         <v>2910010</v>
       </c>
       <c r="G114" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K114">
         <v>21010010</v>
       </c>
       <c r="L114" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -5612,7 +5624,7 @@
         <v>2910011</v>
       </c>
       <c r="G115" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H115">
         <v>-45</v>
@@ -5621,7 +5633,7 @@
         <v>21010011</v>
       </c>
       <c r="L115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5644,7 +5656,7 @@
         <v>2910012</v>
       </c>
       <c r="G116" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H116">
         <v>-45</v>
@@ -5653,7 +5665,7 @@
         <v>21010012</v>
       </c>
       <c r="L116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -5676,13 +5688,13 @@
         <v>2910013</v>
       </c>
       <c r="G117" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K117">
         <v>21010013</v>
       </c>
       <c r="L117" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -5705,13 +5717,13 @@
         <v>2910014</v>
       </c>
       <c r="G118" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K118">
         <v>21010014</v>
       </c>
       <c r="L118" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5734,13 +5746,13 @@
         <v>2910015</v>
       </c>
       <c r="G119" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K119">
         <v>21010015</v>
       </c>
       <c r="L119" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -5763,13 +5775,13 @@
         <v>2910016</v>
       </c>
       <c r="G120" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K120">
         <v>21010016</v>
       </c>
       <c r="L120" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5792,13 +5804,13 @@
         <v>2910017</v>
       </c>
       <c r="G121" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K121">
         <v>21010017</v>
       </c>
       <c r="L121" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5821,13 +5833,13 @@
         <v>2910018</v>
       </c>
       <c r="G122" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K122">
         <v>21010018</v>
       </c>
       <c r="L122" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5850,13 +5862,13 @@
         <v>2910019</v>
       </c>
       <c r="G123" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K123">
         <v>21010019</v>
       </c>
       <c r="L123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5879,13 +5891,13 @@
         <v>2910020</v>
       </c>
       <c r="G124" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K124">
         <v>21010020</v>
       </c>
       <c r="L124" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5905,13 +5917,13 @@
         <v>3020001</v>
       </c>
       <c r="G125" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K125">
         <v>30100001</v>
       </c>
       <c r="L125" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5931,13 +5943,13 @@
         <v>3020002</v>
       </c>
       <c r="G126" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K126">
         <v>30100002</v>
       </c>
       <c r="L126" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5957,13 +5969,13 @@
         <v>3020003</v>
       </c>
       <c r="G127" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K127">
         <v>30100003</v>
       </c>
       <c r="L127" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5983,13 +5995,13 @@
         <v>3020004</v>
       </c>
       <c r="G128" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K128">
         <v>30100004</v>
       </c>
       <c r="L128" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -6009,13 +6021,13 @@
         <v>3020005</v>
       </c>
       <c r="G129" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K129">
         <v>30100005</v>
       </c>
       <c r="L129" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -6035,13 +6047,13 @@
         <v>3020006</v>
       </c>
       <c r="G130" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K130">
         <v>30100006</v>
       </c>
       <c r="L130" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -6061,13 +6073,13 @@
         <v>3020007</v>
       </c>
       <c r="G131" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K131">
         <v>30100007</v>
       </c>
       <c r="L131" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" spans="1:12">
@@ -6087,13 +6099,13 @@
         <v>3020008</v>
       </c>
       <c r="G132" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K132">
         <v>30100008</v>
       </c>
       <c r="L132" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" spans="1:12">
@@ -6113,13 +6125,13 @@
         <v>3020009</v>
       </c>
       <c r="G133" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K133">
         <v>30100009</v>
       </c>
       <c r="L133" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" spans="1:12">
@@ -6139,13 +6151,13 @@
         <v>3020010</v>
       </c>
       <c r="G134" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K134">
         <v>30100010</v>
       </c>
       <c r="L134" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:12">
@@ -6165,13 +6177,13 @@
         <v>3020011</v>
       </c>
       <c r="G135" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K135">
         <v>30100011</v>
       </c>
       <c r="L135" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:12">
@@ -6191,13 +6203,13 @@
         <v>3020012</v>
       </c>
       <c r="G136" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K136">
         <v>30100012</v>
       </c>
       <c r="L136" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:12">
@@ -6217,13 +6229,13 @@
         <v>3020013</v>
       </c>
       <c r="G137" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K137">
         <v>30100013</v>
       </c>
       <c r="L137" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" spans="1:12">
@@ -6243,13 +6255,13 @@
         <v>3020014</v>
       </c>
       <c r="G138" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K138">
         <v>30100014</v>
       </c>
       <c r="L138" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" spans="1:12">
@@ -6269,13 +6281,13 @@
         <v>3020015</v>
       </c>
       <c r="G139" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K139">
         <v>30100015</v>
       </c>
       <c r="L139" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" spans="1:12">
@@ -6295,13 +6307,13 @@
         <v>3020016</v>
       </c>
       <c r="G140" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K140">
         <v>30100016</v>
       </c>
       <c r="L140" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:12">
@@ -6321,13 +6333,13 @@
         <v>3020017</v>
       </c>
       <c r="G141" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K141">
         <v>30100017</v>
       </c>
       <c r="L141" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:12">
@@ -6347,13 +6359,13 @@
         <v>3020018</v>
       </c>
       <c r="G142" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K142">
         <v>30100018</v>
       </c>
       <c r="L142" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="143" spans="1:12">
@@ -6373,13 +6385,13 @@
         <v>3020019</v>
       </c>
       <c r="G143" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K143">
         <v>30100019</v>
       </c>
       <c r="L143" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -6399,13 +6411,13 @@
         <v>3020020</v>
       </c>
       <c r="G144" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K144">
         <v>30100020</v>
       </c>
       <c r="L144" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -6425,13 +6437,13 @@
         <v>4500003</v>
       </c>
       <c r="G145" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K145">
         <v>40100001</v>
       </c>
       <c r="L145" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="146" ht="12" customHeight="1" spans="1:12">
@@ -6451,13 +6463,13 @@
         <v>4510001</v>
       </c>
       <c r="G146" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K146">
         <v>40200001</v>
       </c>
       <c r="L146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -6477,13 +6489,13 @@
         <v>4510002</v>
       </c>
       <c r="G147" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K147">
         <v>40200002</v>
       </c>
       <c r="L147" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -6503,13 +6515,13 @@
         <v>4510003</v>
       </c>
       <c r="G148" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K148">
         <v>40200003</v>
       </c>
       <c r="L148" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -6529,13 +6541,13 @@
         <v>4510004</v>
       </c>
       <c r="G149" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K149">
         <v>40200004</v>
       </c>
       <c r="L149" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -6555,13 +6567,13 @@
         <v>4510005</v>
       </c>
       <c r="G150" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K150">
         <v>40200005</v>
       </c>
       <c r="L150" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -6581,13 +6593,13 @@
         <v>4510006</v>
       </c>
       <c r="G151" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K151">
         <v>40200006</v>
       </c>
       <c r="L151" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -6607,13 +6619,13 @@
         <v>4520001</v>
       </c>
       <c r="G152" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K152">
         <v>40300001</v>
       </c>
       <c r="L152" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -6633,13 +6645,13 @@
         <v>4520002</v>
       </c>
       <c r="G153" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K153">
         <v>40300002</v>
       </c>
       <c r="L153" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -6659,13 +6671,13 @@
         <v>4520003</v>
       </c>
       <c r="G154" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K154">
         <v>40300003</v>
       </c>
       <c r="L154" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="155" spans="1:12">
@@ -6685,13 +6697,13 @@
         <v>4520004</v>
       </c>
       <c r="G155" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K155">
         <v>40300004</v>
       </c>
       <c r="L155" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -6714,13 +6726,13 @@
         <v>4900001</v>
       </c>
       <c r="G156" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K156">
         <v>41000001</v>
       </c>
       <c r="L156" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="157" spans="1:12">
@@ -6743,13 +6755,13 @@
         <v>4900002</v>
       </c>
       <c r="G157" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K157">
         <v>41000002</v>
       </c>
       <c r="L157" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -6772,13 +6784,13 @@
         <v>4900003</v>
       </c>
       <c r="G158" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K158">
         <v>41000003</v>
       </c>
       <c r="L158" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -6801,13 +6813,13 @@
         <v>4900004</v>
       </c>
       <c r="G159" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K159">
         <v>41000004</v>
       </c>
       <c r="L159" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -6830,13 +6842,13 @@
         <v>4900005</v>
       </c>
       <c r="G160" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K160">
         <v>41000005</v>
       </c>
       <c r="L160" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="161" customFormat="1" spans="1:12">
@@ -6856,13 +6868,13 @@
         <v>5500001</v>
       </c>
       <c r="G161" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K161">
         <v>50100001</v>
       </c>
       <c r="L161" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -6882,13 +6894,13 @@
         <v>5500002</v>
       </c>
       <c r="G162" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K162">
         <v>50100002</v>
       </c>
       <c r="L162" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -6908,13 +6920,13 @@
         <v>5500003</v>
       </c>
       <c r="G163" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K163">
         <v>50100003</v>
       </c>
       <c r="L163" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="164" customFormat="1" spans="1:12">
@@ -6934,13 +6946,13 @@
         <v>5510001</v>
       </c>
       <c r="G164" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K164">
         <v>50200001</v>
       </c>
       <c r="L164" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -6960,13 +6972,13 @@
         <v>5510002</v>
       </c>
       <c r="G165" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K165">
         <v>50200002</v>
       </c>
       <c r="L165" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -6986,13 +6998,13 @@
         <v>5510003</v>
       </c>
       <c r="G166" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K166">
         <v>50200003</v>
       </c>
       <c r="L166" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" customFormat="1" ht="12" customHeight="1" spans="1:12">
@@ -7012,13 +7024,13 @@
         <v>5520001</v>
       </c>
       <c r="G167" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K167">
         <v>50300001</v>
       </c>
       <c r="L167" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="168" spans="1:12">
@@ -7038,13 +7050,13 @@
         <v>5520002</v>
       </c>
       <c r="G168" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K168">
         <v>50300002</v>
       </c>
       <c r="L168" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -7064,13 +7076,13 @@
         <v>5090001</v>
       </c>
       <c r="G169" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K169">
         <v>50500001</v>
       </c>
       <c r="L169" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="170" spans="1:12">
@@ -7090,13 +7102,13 @@
         <v>5090002</v>
       </c>
       <c r="G170" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K170">
         <v>50500002</v>
       </c>
       <c r="L170" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -7116,13 +7128,13 @@
         <v>5090003</v>
       </c>
       <c r="G171" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K171">
         <v>50500003</v>
       </c>
       <c r="L171" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -7142,13 +7154,13 @@
         <v>5090004</v>
       </c>
       <c r="G172" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K172">
         <v>50500004</v>
       </c>
       <c r="L172" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -7168,13 +7180,13 @@
         <v>5090005</v>
       </c>
       <c r="G173" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K173">
         <v>50500005</v>
       </c>
       <c r="L173" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="174" customFormat="1" spans="1:12">
@@ -7197,16 +7209,16 @@
         <v>5910001</v>
       </c>
       <c r="G174" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I174" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K174">
         <v>51010001</v>
       </c>
       <c r="L174" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="175" customFormat="1" spans="1:12">
@@ -7229,10 +7241,10 @@
         <v>5910002</v>
       </c>
       <c r="G175" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I175" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K175">
         <v>51010002</v>
@@ -7261,16 +7273,16 @@
         <v>5910003</v>
       </c>
       <c r="G176" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I176" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K176">
         <v>51010003</v>
       </c>
       <c r="L176" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" customFormat="1" spans="1:12">
@@ -7290,13 +7302,13 @@
         <v>6500001</v>
       </c>
       <c r="G177" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K177">
         <v>60100001</v>
       </c>
       <c r="L177" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -7316,13 +7328,13 @@
         <v>6500002</v>
       </c>
       <c r="G178" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K178">
         <v>60100002</v>
       </c>
       <c r="L178" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -7342,13 +7354,13 @@
         <v>6500003</v>
       </c>
       <c r="G179" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K179">
         <v>60100003</v>
       </c>
       <c r="L179" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -7368,13 +7380,13 @@
         <v>6500004</v>
       </c>
       <c r="G180" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K180">
         <v>60100004</v>
       </c>
       <c r="L180" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -7394,13 +7406,13 @@
         <v>6500005</v>
       </c>
       <c r="G181" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K181">
         <v>60100005</v>
       </c>
       <c r="L181" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="182" ht="12" customHeight="1" spans="1:12">
@@ -7420,13 +7432,13 @@
         <v>6500006</v>
       </c>
       <c r="G182" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K182">
         <v>60100006</v>
       </c>
       <c r="L182" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="183" ht="12" customHeight="1" spans="1:12">
@@ -7446,13 +7458,13 @@
         <v>6500007</v>
       </c>
       <c r="G183" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K183">
         <v>60100007</v>
       </c>
       <c r="L183" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="184" ht="12" customHeight="1" spans="1:12">
@@ -7472,13 +7484,13 @@
         <v>6500008</v>
       </c>
       <c r="G184" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K184">
         <v>60100008</v>
       </c>
       <c r="L184" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="185" ht="12" customHeight="1" spans="1:12">
@@ -7498,13 +7510,13 @@
         <v>6500009</v>
       </c>
       <c r="G185" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K185">
         <v>60100009</v>
       </c>
       <c r="L185" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="186" ht="12" customHeight="1" spans="1:12">
@@ -7524,13 +7536,13 @@
         <v>6500010</v>
       </c>
       <c r="G186" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K186">
         <v>60100010</v>
       </c>
       <c r="L186" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="187" customFormat="1" ht="12" customHeight="1" spans="1:12">
@@ -7550,13 +7562,13 @@
         <v>6510001</v>
       </c>
       <c r="G187" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K187">
         <v>60200001</v>
       </c>
       <c r="L187" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="188" ht="12" customHeight="1" spans="1:12">
@@ -7576,13 +7588,13 @@
         <v>6510002</v>
       </c>
       <c r="G188" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K188">
         <v>60200002</v>
       </c>
       <c r="L188" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="189" customFormat="1" spans="1:12">
@@ -7602,13 +7614,13 @@
         <v>6520001</v>
       </c>
       <c r="G189" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K189">
         <v>60300001</v>
       </c>
       <c r="L189" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -7628,13 +7640,13 @@
         <v>6520002</v>
       </c>
       <c r="G190" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K190">
         <v>60300002</v>
       </c>
       <c r="L190" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -7654,13 +7666,13 @@
         <v>6520003</v>
       </c>
       <c r="G191" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K191">
         <v>60300003</v>
       </c>
       <c r="L191" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -7680,13 +7692,13 @@
         <v>6520004</v>
       </c>
       <c r="G192" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K192">
         <v>60300004</v>
       </c>
       <c r="L192" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -7706,13 +7718,13 @@
         <v>6520005</v>
       </c>
       <c r="G193" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K193">
         <v>60300005</v>
       </c>
       <c r="L193" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="194" customFormat="1" spans="1:12">
@@ -7735,14 +7747,14 @@
         <v>6910001</v>
       </c>
       <c r="G194" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H194"/>
       <c r="K194">
         <v>61010001</v>
       </c>
       <c r="L194" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -7765,16 +7777,16 @@
         <v>6910002</v>
       </c>
       <c r="G195" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I195" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K195">
         <v>61010002</v>
       </c>
       <c r="L195" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -7797,13 +7809,13 @@
         <v>6910003</v>
       </c>
       <c r="G196" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K196">
         <v>61010003</v>
       </c>
       <c r="L196" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -7826,7 +7838,7 @@
         <v>6910004</v>
       </c>
       <c r="G197" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H197">
         <v>-45</v>
@@ -7835,7 +7847,7 @@
         <v>61010004</v>
       </c>
       <c r="L197" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -7858,7 +7870,7 @@
         <v>6910005</v>
       </c>
       <c r="G198" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H198">
         <v>-45</v>
@@ -7867,7 +7879,7 @@
         <v>61010005</v>
       </c>
       <c r="L198" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -7890,7 +7902,7 @@
         <v>6910006</v>
       </c>
       <c r="G199" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H199">
         <v>-45</v>
@@ -7899,7 +7911,7 @@
         <v>61010006</v>
       </c>
       <c r="L199" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -7922,13 +7934,13 @@
         <v>6910007</v>
       </c>
       <c r="G200" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K200">
         <v>61010007</v>
       </c>
       <c r="L200" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -7951,13 +7963,13 @@
         <v>6910008</v>
       </c>
       <c r="G201" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K201">
         <v>61010008</v>
       </c>
       <c r="L201" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -7980,7 +7992,7 @@
         <v>6910009</v>
       </c>
       <c r="G202" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K202">
         <v>61010009</v>
@@ -8009,13 +8021,13 @@
         <v>6910010</v>
       </c>
       <c r="G203" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K203">
         <v>61010010</v>
       </c>
       <c r="L203" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -8038,13 +8050,13 @@
         <v>6910011</v>
       </c>
       <c r="G204" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K204">
         <v>61010011</v>
       </c>
       <c r="L204" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -8067,13 +8079,13 @@
         <v>6910012</v>
       </c>
       <c r="G205" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K205">
         <v>61010012</v>
       </c>
       <c r="L205" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -8096,16 +8108,16 @@
         <v>6910013</v>
       </c>
       <c r="G206" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I206" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K206">
         <v>61010013</v>
       </c>
       <c r="L206" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -8128,16 +8140,16 @@
         <v>6910014</v>
       </c>
       <c r="G207" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I207" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K207">
         <v>61010014</v>
       </c>
       <c r="L207" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -8160,16 +8172,16 @@
         <v>6910015</v>
       </c>
       <c r="G208" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I208" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K208">
         <v>61010015</v>
       </c>
       <c r="L208" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -8192,16 +8204,16 @@
         <v>6910016</v>
       </c>
       <c r="G209" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I209" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K209">
         <v>61010016</v>
       </c>
       <c r="L209" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -8224,13 +8236,13 @@
         <v>6910017</v>
       </c>
       <c r="G210" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K210">
         <v>61010017</v>
       </c>
       <c r="L210" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -8253,13 +8265,13 @@
         <v>6910018</v>
       </c>
       <c r="G211" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K211">
         <v>61010018</v>
       </c>
       <c r="L211" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -8282,13 +8294,13 @@
         <v>6910019</v>
       </c>
       <c r="G212" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K212">
         <v>61010019</v>
       </c>
       <c r="L212" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -8311,13 +8323,13 @@
         <v>6910020</v>
       </c>
       <c r="G213" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K213">
         <v>61010020</v>
       </c>
       <c r="L213" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -8337,13 +8349,13 @@
         <v>7500001</v>
       </c>
       <c r="G214" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K214">
         <v>70100001</v>
       </c>
       <c r="L214" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -8363,13 +8375,13 @@
         <v>7510001</v>
       </c>
       <c r="G215" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K215">
         <v>70200001</v>
       </c>
       <c r="L215" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -8389,13 +8401,13 @@
         <v>7510002</v>
       </c>
       <c r="G216" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K216">
         <v>70200002</v>
       </c>
       <c r="L216" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -8415,13 +8427,13 @@
         <v>7520001</v>
       </c>
       <c r="G217" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K217">
         <v>70300001</v>
       </c>
       <c r="L217" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -8441,13 +8453,13 @@
         <v>7520002</v>
       </c>
       <c r="G218" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K218">
         <v>70300002</v>
       </c>
       <c r="L218" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -8467,13 +8479,13 @@
         <v>7520003</v>
       </c>
       <c r="G219" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K219">
         <v>70300003</v>
       </c>
       <c r="L219" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -8493,13 +8505,13 @@
         <v>7520004</v>
       </c>
       <c r="G220" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K220">
         <v>70300004</v>
       </c>
       <c r="L220" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -8522,16 +8534,16 @@
         <v>7900001</v>
       </c>
       <c r="G221" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I221" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K221">
         <v>71000001</v>
       </c>
       <c r="L221" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -8554,16 +8566,16 @@
         <v>7900002</v>
       </c>
       <c r="G222" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I222" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K222">
         <v>71000002</v>
       </c>
       <c r="L222" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -8586,16 +8598,16 @@
         <v>7900003</v>
       </c>
       <c r="G223" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I223" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K223">
         <v>71000003</v>
       </c>
       <c r="L223" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -8618,13 +8630,13 @@
         <v>7910001</v>
       </c>
       <c r="G224" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K224">
         <v>71010001</v>
       </c>
       <c r="L224" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -8647,13 +8659,13 @@
         <v>7910002</v>
       </c>
       <c r="G225" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K225">
         <v>71010002</v>
       </c>
       <c r="L225" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -8676,13 +8688,13 @@
         <v>7910003</v>
       </c>
       <c r="G226" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K226">
         <v>71010003</v>
       </c>
       <c r="L226" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -8705,13 +8717,13 @@
         <v>7910004</v>
       </c>
       <c r="G227" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K227">
         <v>71010004</v>
       </c>
       <c r="L227" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -8734,13 +8746,13 @@
         <v>7910005</v>
       </c>
       <c r="G228" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K228">
         <v>71010005</v>
       </c>
       <c r="L228" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -8763,13 +8775,13 @@
         <v>7910006</v>
       </c>
       <c r="G229" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K229">
         <v>71010006</v>
       </c>
       <c r="L229" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -3383,7 +3383,7 @@
       </c>
       <c r="I68" s="53" t="inlineStr">
         <is>
-          <t>ShowSprite:Human_Atlas_Other_Arrow_2&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180</t>
+          <t>ShowSprite:Human_Atlas_Other_Arrow_2&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
         </is>
       </c>
       <c r="K68" s="53" t="n">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="I69" s="53" t="inlineStr">
         <is>
-          <t>ShowSprite:Human_Atlas_Other_Arrow_3&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180</t>
+          <t>ShowSprite:Human_Atlas_Other_Arrow_3&amp;VertexRotateAxis:0,0,1&amp;StartRotate:0,0,180&amp;StartSize:1.25</t>
         </is>
       </c>
       <c r="K69" s="53" t="n">
@@ -5662,7 +5662,7 @@
           <t>史莱姆-帽子-8</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
+      <c r="M132" s="53" t="inlineStr">
         <is>
           <t>4,5,6</t>
         </is>
@@ -5697,7 +5697,7 @@
           <t>史莱姆-帽子-9</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
+      <c r="M133" s="53" t="inlineStr">
         <is>
           <t>3,4,5,6</t>
         </is>
@@ -5732,7 +5732,7 @@
           <t>史莱姆-帽子-10</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
+      <c r="M134" s="53" t="inlineStr">
         <is>
           <t>4,5,6</t>
         </is>
@@ -5767,7 +5767,7 @@
           <t>史莱姆-帽子-11</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
+      <c r="M135" s="53" t="inlineStr">
         <is>
           <t>4,5,6</t>
         </is>
@@ -5802,7 +5802,7 @@
           <t>史莱姆-帽子-12</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
+      <c r="M136" s="53" t="inlineStr">
         <is>
           <t>2,3,4,5,6</t>
         </is>
@@ -5837,7 +5837,7 @@
           <t>史莱姆-帽子-13</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr">
+      <c r="M137" s="53" t="inlineStr">
         <is>
           <t>3,4,5,6</t>
         </is>
@@ -5872,7 +5872,7 @@
           <t>史莱姆-帽子-14</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
+      <c r="M138" s="53" t="inlineStr">
         <is>
           <t>4,5,6</t>
         </is>
@@ -5907,7 +5907,7 @@
           <t>史莱姆-帽子-15</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
+      <c r="M139" s="53" t="inlineStr">
         <is>
           <t>4,5,6</t>
         </is>
@@ -5942,7 +5942,7 @@
           <t>史莱姆-帽子-16</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr">
+      <c r="M140" s="53" t="inlineStr">
         <is>
           <t>3,4,5,6</t>
         </is>
@@ -5977,7 +5977,7 @@
           <t>史莱姆-帽子-17</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr">
+      <c r="M141" s="53" t="inlineStr">
         <is>
           <t>3,4,5,6</t>
         </is>
@@ -6012,7 +6012,7 @@
           <t>史莱姆-帽子-18</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
+      <c r="M142" s="53" t="inlineStr">
         <is>
           <t>3,4,5,6</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -1177,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M229"/>
+  <dimension ref="A1:M230"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="10.75" customWidth="1" style="54" min="1" max="1"/>
@@ -8814,6 +8814,36 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" s="53" t="n">
+        <v>200001</v>
+      </c>
+      <c r="B230" s="53" t="n">
+        <v>11</v>
+      </c>
+      <c r="D230" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="53" t="inlineStr">
+        <is>
+          <t>Item_Juicer_1</t>
+        </is>
+      </c>
+      <c r="K230" s="53" t="n">
+        <v>200001</v>
+      </c>
+      <c r="L230" s="53" t="inlineStr">
+        <is>
+          <t>魔汁(榨汁产物,对魔物使用后增加经验)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_items_info[道具信息].xlsx
@@ -7710,7 +7710,7 @@
         <v>10</v>
       </c>
       <c r="C201" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D201" s="0" t="n">
         <v>1</v>
@@ -8027,7 +8027,7 @@
         <v>10</v>
       </c>
       <c r="C210" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D210" s="0" t="n">
         <v>1</v>
@@ -8060,7 +8060,7 @@
         <v>10</v>
       </c>
       <c r="C211" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D211" s="0" t="n">
         <v>1</v>
@@ -8093,7 +8093,7 @@
         <v>10</v>
       </c>
       <c r="C212" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D212" s="0" t="n">
         <v>1</v>
@@ -8126,7 +8126,7 @@
         <v>10</v>
       </c>
       <c r="C213" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D213" s="0" t="n">
         <v>1</v>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="I221" s="0" t="inlineStr">
         <is>
-          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1</t>
+          <t>ShowSprite:Orc_Atlas_Weapon_Weapon_L_1&amp;VertexRotateSpeed:0&amp;VertexRotateAxis:0,0,-1&amp;StartSize:1.5</t>
         </is>
       </c>
       <c r="K221" s="0" t="n">
